--- a/output/2024-04-30.xlsx
+++ b/output/2024-04-30.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.13</v>
+        <v>4.18</v>
       </c>
       <c r="F14" t="n">
-        <v>14.02</v>
+        <v>13.54</v>
       </c>
       <c r="G14" t="n">
-        <v>230.2</v>
+        <v>246.2</v>
       </c>
       <c r="H14" t="n">
-        <v>81</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>34.15</v>
+        <v>-45.52</v>
       </c>
       <c r="K14" t="n">
-        <v>-166.88</v>
+        <v>127.52</v>
       </c>
       <c r="L14" t="n">
-        <v>170.33</v>
+        <v>135.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:32:46</t>
+          <t>05:32:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.47</v>
+        <v>4.73</v>
       </c>
       <c r="F15" t="n">
-        <v>14.21</v>
+        <v>13.92</v>
       </c>
       <c r="G15" t="n">
-        <v>246.3</v>
+        <v>270.3</v>
       </c>
       <c r="H15" t="n">
-        <v>75.09999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.78</v>
+        <v>-256.55</v>
       </c>
       <c r="K15" t="n">
-        <v>-182.84</v>
+        <v>-0.18</v>
       </c>
       <c r="L15" t="n">
-        <v>182.9</v>
+        <v>256.55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:34:31</t>
+          <t>05:34:43</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1</v>
+        <v>4.39</v>
       </c>
       <c r="F16" t="n">
-        <v>13.84</v>
+        <v>13.42</v>
       </c>
       <c r="G16" t="n">
-        <v>258.1</v>
+        <v>272.6</v>
       </c>
       <c r="H16" t="n">
-        <v>73.3</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>40.71</v>
+        <v>-164.8</v>
       </c>
       <c r="K16" t="n">
-        <v>158.65</v>
+        <v>291.11</v>
       </c>
       <c r="L16" t="n">
-        <v>163.79</v>
+        <v>334.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:39:13</t>
+          <t>05:39:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.82</v>
+        <v>4.65</v>
       </c>
       <c r="F17" t="n">
-        <v>14.02</v>
+        <v>13.65</v>
       </c>
       <c r="G17" t="n">
-        <v>251.7</v>
+        <v>261.2</v>
       </c>
       <c r="H17" t="n">
-        <v>76.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-4.5</v>
+        <v>148.45</v>
       </c>
       <c r="K17" t="n">
-        <v>-208.58</v>
+        <v>-52.89</v>
       </c>
       <c r="L17" t="n">
-        <v>208.62</v>
+        <v>157.59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:40:27</t>
+          <t>05:41:51</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.6</v>
+        <v>4.09</v>
       </c>
       <c r="F18" t="n">
-        <v>13.59</v>
+        <v>14.03</v>
       </c>
       <c r="G18" t="n">
-        <v>261.1</v>
+        <v>267.3</v>
       </c>
       <c r="H18" t="n">
-        <v>78.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-54.49</v>
+        <v>-56.56</v>
       </c>
       <c r="K18" t="n">
-        <v>-163.37</v>
+        <v>-160.57</v>
       </c>
       <c r="L18" t="n">
-        <v>172.22</v>
+        <v>170.24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:42:30</t>
+          <t>05:43:37</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>5.08</v>
+        <v>4.49</v>
       </c>
       <c r="F19" t="n">
-        <v>13.59</v>
+        <v>13.6</v>
       </c>
       <c r="G19" t="n">
-        <v>259.3</v>
+        <v>253.4</v>
       </c>
       <c r="H19" t="n">
-        <v>81.09999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>-89.31999999999999</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-136.14</v>
+        <v>280.58</v>
       </c>
       <c r="L19" t="n">
-        <v>162.83</v>
+        <v>294.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:46:47</t>
+          <t>05:48:10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.29</v>
+        <v>4.34</v>
       </c>
       <c r="F20" t="n">
-        <v>14.46</v>
+        <v>13.81</v>
       </c>
       <c r="G20" t="n">
-        <v>258.1</v>
+        <v>254.2</v>
       </c>
       <c r="H20" t="n">
-        <v>79</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>-219.41</v>
+        <v>-209.94</v>
       </c>
       <c r="K20" t="n">
-        <v>-181.03</v>
+        <v>-115.17</v>
       </c>
       <c r="L20" t="n">
-        <v>284.45</v>
+        <v>239.46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:48:51</t>
+          <t>05:49:51</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.75</v>
+        <v>4.42</v>
       </c>
       <c r="F21" t="n">
-        <v>12.76</v>
+        <v>12.65</v>
       </c>
       <c r="G21" t="n">
-        <v>254.7</v>
+        <v>252.6</v>
       </c>
       <c r="H21" t="n">
-        <v>79.8</v>
+        <v>80.5</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-301.23</v>
+        <v>290.59</v>
       </c>
       <c r="K21" t="n">
-        <v>-142.98</v>
+        <v>-510.85</v>
       </c>
       <c r="L21" t="n">
-        <v>333.44</v>
+        <v>587.71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:51:00</t>
+          <t>05:51:06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.27</v>
+        <v>4.29</v>
       </c>
       <c r="F22" t="n">
-        <v>13.25</v>
+        <v>13.28</v>
       </c>
       <c r="G22" t="n">
-        <v>245.5</v>
+        <v>254.1</v>
       </c>
       <c r="H22" t="n">
-        <v>74.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-115.51</v>
+        <v>-91.33</v>
       </c>
       <c r="K22" t="n">
-        <v>54.42</v>
+        <v>8.74</v>
       </c>
       <c r="L22" t="n">
-        <v>127.69</v>
+        <v>91.75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:55:31</t>
+          <t>05:54:57</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.69</v>
+        <v>4.86</v>
       </c>
       <c r="F23" t="n">
-        <v>13.46</v>
+        <v>13.55</v>
       </c>
       <c r="G23" t="n">
-        <v>262</v>
+        <v>258.1</v>
       </c>
       <c r="H23" t="n">
-        <v>82.7</v>
+        <v>76</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-229.87</v>
+        <v>-96.56999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-185.42</v>
+        <v>-640.29</v>
       </c>
       <c r="L23" t="n">
-        <v>295.33</v>
+        <v>647.54</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:57:24</t>
+          <t>05:56:15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>5.04</v>
+        <v>4.98</v>
       </c>
       <c r="F24" t="n">
-        <v>14.78</v>
+        <v>13.04</v>
       </c>
       <c r="G24" t="n">
-        <v>252</v>
+        <v>248.5</v>
       </c>
       <c r="H24" t="n">
-        <v>79.3</v>
+        <v>75</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-82.95999999999999</v>
+        <v>375.63</v>
       </c>
       <c r="K24" t="n">
-        <v>42.59</v>
+        <v>961.88</v>
       </c>
       <c r="L24" t="n">
-        <v>93.25</v>
+        <v>1032.63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:58:43</t>
+          <t>05:57:24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.97</v>
+        <v>4.59</v>
       </c>
       <c r="F25" t="n">
-        <v>13.61</v>
+        <v>13.72</v>
       </c>
       <c r="G25" t="n">
-        <v>245.1</v>
+        <v>270.6</v>
       </c>
       <c r="H25" t="n">
-        <v>73.3</v>
+        <v>74.8</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>306.97</v>
+        <v>466.82</v>
       </c>
       <c r="K25" t="n">
-        <v>-63.71</v>
+        <v>-663.22</v>
       </c>
       <c r="L25" t="n">
-        <v>313.51</v>
+        <v>811.04</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:02:06</t>
+          <t>06:01:37</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>14.31</v>
+        <v>15</v>
       </c>
       <c r="G26" t="n">
-        <v>258</v>
+        <v>253.6</v>
       </c>
       <c r="H26" t="n">
-        <v>81.7</v>
+        <v>78.3</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>314.39</v>
+        <v>22.69</v>
       </c>
       <c r="K26" t="n">
-        <v>-522.41</v>
+        <v>317.69</v>
       </c>
       <c r="L26" t="n">
-        <v>609.71</v>
+        <v>318.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:04:34</t>
+          <t>06:03:06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.63</v>
+        <v>4.3</v>
       </c>
       <c r="F27" t="n">
-        <v>14.38</v>
+        <v>13.93</v>
       </c>
       <c r="G27" t="n">
-        <v>253</v>
+        <v>258.2</v>
       </c>
       <c r="H27" t="n">
-        <v>70.3</v>
+        <v>79</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>-11.57</v>
+        <v>610.77</v>
       </c>
       <c r="K27" t="n">
-        <v>408.91</v>
+        <v>452.82</v>
       </c>
       <c r="L27" t="n">
-        <v>409.08</v>
+        <v>760.3200000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:05:41</t>
+          <t>06:04:38</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.11</v>
+        <v>4.34</v>
       </c>
       <c r="F28" t="n">
-        <v>14.31</v>
+        <v>13.9</v>
       </c>
       <c r="G28" t="n">
-        <v>237.6</v>
+        <v>252.3</v>
       </c>
       <c r="H28" t="n">
-        <v>75.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-284.16</v>
+        <v>-598.9400000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>-420.7</v>
+        <v>-658.8099999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>507.68</v>
+        <v>890.37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:17:48</t>
+          <t>06:13:35</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.27</v>
+        <v>3.62</v>
       </c>
       <c r="F29" t="n">
-        <v>13.39</v>
+        <v>13.27</v>
       </c>
       <c r="G29" t="n">
-        <v>251.3</v>
+        <v>250.9</v>
       </c>
       <c r="H29" t="n">
-        <v>72</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>9.51</v>
+        <v>114.69</v>
       </c>
       <c r="K29" t="n">
-        <v>-57.21</v>
+        <v>-89.54000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>58</v>
+        <v>145.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:19:49</t>
+          <t>06:14:31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>5.09</v>
+        <v>4.16</v>
       </c>
       <c r="F30" t="n">
-        <v>13.77</v>
+        <v>14.28</v>
       </c>
       <c r="G30" t="n">
-        <v>232.8</v>
+        <v>247.8</v>
       </c>
       <c r="H30" t="n">
-        <v>81.3</v>
+        <v>75.7</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>-31.31</v>
+        <v>95.02</v>
       </c>
       <c r="K30" t="n">
-        <v>-162.83</v>
+        <v>151.55</v>
       </c>
       <c r="L30" t="n">
-        <v>165.81</v>
+        <v>178.88</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:22:05</t>
+          <t>06:16:08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>5.14</v>
+        <v>3.48</v>
       </c>
       <c r="F31" t="n">
-        <v>13.81</v>
+        <v>13.82</v>
       </c>
       <c r="G31" t="n">
-        <v>248</v>
+        <v>257.2</v>
       </c>
       <c r="H31" t="n">
-        <v>80</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>109.92</v>
+        <v>60.94</v>
       </c>
       <c r="K31" t="n">
-        <v>-270.2</v>
+        <v>-56.55</v>
       </c>
       <c r="L31" t="n">
-        <v>291.71</v>
+        <v>83.14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:25:47</t>
+          <t>06:21:05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.23</v>
+        <v>4.76</v>
       </c>
       <c r="F32" t="n">
-        <v>13.83</v>
+        <v>13.55</v>
       </c>
       <c r="G32" t="n">
-        <v>255.9</v>
+        <v>270.5</v>
       </c>
       <c r="H32" t="n">
-        <v>72.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>126.25</v>
+        <v>-212.76</v>
       </c>
       <c r="K32" t="n">
-        <v>-200.56</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>236.99</v>
+        <v>225.94</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:26:38</t>
+          <t>06:22:52</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.31</v>
+        <v>4.06</v>
       </c>
       <c r="F33" t="n">
-        <v>13.5</v>
+        <v>14.13</v>
       </c>
       <c r="G33" t="n">
-        <v>258.5</v>
+        <v>260.4</v>
       </c>
       <c r="H33" t="n">
-        <v>82</v>
+        <v>75.8</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>34.41</v>
+        <v>16.64</v>
       </c>
       <c r="K33" t="n">
-        <v>-37.3</v>
+        <v>589.52</v>
       </c>
       <c r="L33" t="n">
-        <v>50.75</v>
+        <v>589.76</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:28:35</t>
+          <t>06:23:34</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.39</v>
+        <v>4.86</v>
       </c>
       <c r="F34" t="n">
-        <v>14.21</v>
+        <v>14.37</v>
       </c>
       <c r="G34" t="n">
-        <v>247.9</v>
+        <v>253.3</v>
       </c>
       <c r="H34" t="n">
-        <v>84.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>122.75</v>
+        <v>295.98</v>
       </c>
       <c r="K34" t="n">
-        <v>34.29</v>
+        <v>159.96</v>
       </c>
       <c r="L34" t="n">
-        <v>127.45</v>
+        <v>336.44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:34:31</t>
+          <t>06:27:16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.78</v>
+        <v>3.85</v>
       </c>
       <c r="F35" t="n">
-        <v>13.52</v>
+        <v>14.01</v>
       </c>
       <c r="G35" t="n">
-        <v>261.3</v>
+        <v>256</v>
       </c>
       <c r="H35" t="n">
-        <v>76</v>
+        <v>72.7</v>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>149.14</v>
+        <v>110.49</v>
       </c>
       <c r="K35" t="n">
-        <v>4.88</v>
+        <v>138.7</v>
       </c>
       <c r="L35" t="n">
-        <v>149.22</v>
+        <v>177.33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:36:32</t>
+          <t>06:29:49</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.32</v>
+        <v>3.98</v>
       </c>
       <c r="F36" t="n">
-        <v>13.75</v>
+        <v>14.1</v>
       </c>
       <c r="G36" t="n">
-        <v>248.8</v>
+        <v>238.1</v>
       </c>
       <c r="H36" t="n">
-        <v>82.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>323.25</v>
+        <v>214.91</v>
       </c>
       <c r="K36" t="n">
-        <v>-28.58</v>
+        <v>287.67</v>
       </c>
       <c r="L36" t="n">
-        <v>324.51</v>
+        <v>359.08</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:37:21</t>
+          <t>06:31:37</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.35</v>
+        <v>4.15</v>
       </c>
       <c r="F37" t="n">
-        <v>14.25</v>
+        <v>13.61</v>
       </c>
       <c r="G37" t="n">
-        <v>249.9</v>
+        <v>255.1</v>
       </c>
       <c r="H37" t="n">
-        <v>74.5</v>
+        <v>71.2</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>414.4</v>
+        <v>488.05</v>
       </c>
       <c r="K37" t="n">
-        <v>357.75</v>
+        <v>-403.66</v>
       </c>
       <c r="L37" t="n">
-        <v>547.46</v>
+        <v>633.35</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:40:16</t>
+          <t>06:35:53</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.09</v>
+        <v>4.62</v>
       </c>
       <c r="F38" t="n">
-        <v>13.69</v>
+        <v>13.95</v>
       </c>
       <c r="G38" t="n">
-        <v>256</v>
+        <v>256.5</v>
       </c>
       <c r="H38" t="n">
-        <v>85.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>78.56999999999999</v>
+        <v>-370.71</v>
       </c>
       <c r="K38" t="n">
-        <v>265.17</v>
+        <v>353.19</v>
       </c>
       <c r="L38" t="n">
-        <v>276.57</v>
+        <v>512.03</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:42:46</t>
+          <t>06:37:22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.96</v>
+        <v>6.38</v>
       </c>
       <c r="F39" t="n">
-        <v>13.99</v>
+        <v>14.38</v>
       </c>
       <c r="G39" t="n">
-        <v>249.6</v>
+        <v>254.9</v>
       </c>
       <c r="H39" t="n">
-        <v>74.7</v>
+        <v>88.3</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>-336.28</v>
+        <v>-163.83</v>
       </c>
       <c r="K39" t="n">
-        <v>122.18</v>
+        <v>339.31</v>
       </c>
       <c r="L39" t="n">
-        <v>357.79</v>
+        <v>376.79</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:45:18</t>
+          <t>06:39:19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.99</v>
+        <v>4.64</v>
       </c>
       <c r="F40" t="n">
-        <v>12.99</v>
+        <v>14.28</v>
       </c>
       <c r="G40" t="n">
-        <v>257.1</v>
+        <v>262</v>
       </c>
       <c r="H40" t="n">
-        <v>77.8</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>9.65</v>
+        <v>664.12</v>
       </c>
       <c r="K40" t="n">
-        <v>227.34</v>
+        <v>45.02</v>
       </c>
       <c r="L40" t="n">
-        <v>227.54</v>
+        <v>665.64</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:49:50</t>
+          <t>06:43:04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.24</v>
+        <v>4.34</v>
       </c>
       <c r="F41" t="n">
-        <v>14.05</v>
+        <v>14</v>
       </c>
       <c r="G41" t="n">
-        <v>274.7</v>
+        <v>245.8</v>
       </c>
       <c r="H41" t="n">
-        <v>80.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>476.84</v>
+        <v>-116.96</v>
       </c>
       <c r="K41" t="n">
-        <v>-391.58</v>
+        <v>520.55</v>
       </c>
       <c r="L41" t="n">
-        <v>617.02</v>
+        <v>533.52</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:52:04</t>
+          <t>06:44:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.55</v>
+        <v>4.82</v>
       </c>
       <c r="F42" t="n">
-        <v>13.84</v>
+        <v>14.08</v>
       </c>
       <c r="G42" t="n">
-        <v>266</v>
+        <v>256.1</v>
       </c>
       <c r="H42" t="n">
-        <v>76.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-503.09</v>
+        <v>-487.45</v>
       </c>
       <c r="K42" t="n">
-        <v>6.91</v>
+        <v>-494.2</v>
       </c>
       <c r="L42" t="n">
-        <v>503.14</v>
+        <v>694.15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:52:46</t>
+          <t>06:45:50</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="F43" t="n">
-        <v>13.37</v>
+        <v>14.02</v>
       </c>
       <c r="G43" t="n">
-        <v>252.2</v>
+        <v>258.3</v>
       </c>
       <c r="H43" t="n">
-        <v>75.7</v>
+        <v>75.3</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-97.47</v>
+        <v>127.08</v>
       </c>
       <c r="K43" t="n">
-        <v>465.54</v>
+        <v>180.67</v>
       </c>
       <c r="L43" t="n">
-        <v>475.63</v>
+        <v>220.89</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:02:43</t>
+          <t>06:57:04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.93</v>
+        <v>5.29</v>
       </c>
       <c r="F44" t="n">
-        <v>14.02</v>
+        <v>14.16</v>
       </c>
       <c r="G44" t="n">
-        <v>254.7</v>
+        <v>260.5</v>
       </c>
       <c r="H44" t="n">
-        <v>83.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-34.64</v>
+        <v>233.19</v>
       </c>
       <c r="K44" t="n">
-        <v>-73.09</v>
+        <v>38.75</v>
       </c>
       <c r="L44" t="n">
-        <v>80.89</v>
+        <v>236.39</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:03:32</t>
+          <t>06:59:12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>5</v>
+        <v>4.64</v>
       </c>
       <c r="F45" t="n">
-        <v>13.91</v>
+        <v>13.33</v>
       </c>
       <c r="G45" t="n">
-        <v>250.1</v>
+        <v>248.8</v>
       </c>
       <c r="H45" t="n">
-        <v>79</v>
+        <v>78.3</v>
       </c>
       <c r="I45" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>100.81</v>
+        <v>107.74</v>
       </c>
       <c r="K45" t="n">
-        <v>21.72</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>103.13</v>
+        <v>108.17</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:06:27</t>
+          <t>07:01:32</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>5.91</v>
+        <v>4.31</v>
       </c>
       <c r="F46" t="n">
-        <v>13.07</v>
+        <v>13.8</v>
       </c>
       <c r="G46" t="n">
-        <v>241.1</v>
+        <v>247.5</v>
       </c>
       <c r="H46" t="n">
-        <v>71.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.11</v>
+        <v>-349.81</v>
       </c>
       <c r="K46" t="n">
-        <v>-23.17</v>
+        <v>-12.41</v>
       </c>
       <c r="L46" t="n">
-        <v>23.73</v>
+        <v>350.03</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:11:03</t>
+          <t>07:06:36</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.23</v>
+        <v>4.39</v>
       </c>
       <c r="F47" t="n">
-        <v>13.94</v>
+        <v>13.67</v>
       </c>
       <c r="G47" t="n">
-        <v>263.6</v>
+        <v>269.5</v>
       </c>
       <c r="H47" t="n">
-        <v>74.7</v>
+        <v>79.2</v>
       </c>
       <c r="I47" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>59.73</v>
+        <v>382.5</v>
       </c>
       <c r="K47" t="n">
-        <v>-118.35</v>
+        <v>-108.5</v>
       </c>
       <c r="L47" t="n">
-        <v>132.56</v>
+        <v>397.59</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:12:43</t>
+          <t>07:08:22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>5.52</v>
+        <v>5.39</v>
       </c>
       <c r="F48" t="n">
-        <v>14.12</v>
+        <v>13.92</v>
       </c>
       <c r="G48" t="n">
-        <v>252.6</v>
+        <v>260.1</v>
       </c>
       <c r="H48" t="n">
-        <v>84.8</v>
+        <v>85.7</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>223.09</v>
+        <v>-201.37</v>
       </c>
       <c r="K48" t="n">
-        <v>355.97</v>
+        <v>18.81</v>
       </c>
       <c r="L48" t="n">
-        <v>420.1</v>
+        <v>202.25</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:13:43</t>
+          <t>07:09:59</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.5</v>
+        <v>4.99</v>
       </c>
       <c r="F49" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="G49" t="n">
-        <v>267.8</v>
+        <v>251.6</v>
       </c>
       <c r="H49" t="n">
-        <v>77.2</v>
+        <v>84.2</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>334.64</v>
+        <v>287.78</v>
       </c>
       <c r="K49" t="n">
-        <v>-63.84</v>
+        <v>-169.31</v>
       </c>
       <c r="L49" t="n">
-        <v>340.68</v>
+        <v>333.89</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:19:04</t>
+          <t>07:15:38</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.69</v>
+        <v>4.32</v>
       </c>
       <c r="F50" t="n">
-        <v>14.07</v>
+        <v>13.3</v>
       </c>
       <c r="G50" t="n">
-        <v>239.9</v>
+        <v>263.3</v>
       </c>
       <c r="H50" t="n">
-        <v>79.2</v>
+        <v>84.7</v>
       </c>
       <c r="I50" t="n">
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-202.56</v>
+        <v>-292.17</v>
       </c>
       <c r="K50" t="n">
-        <v>158.7</v>
+        <v>-78.92</v>
       </c>
       <c r="L50" t="n">
-        <v>257.32</v>
+        <v>302.64</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:20:25</t>
+          <t>07:17:07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.12</v>
+        <v>5.33</v>
       </c>
       <c r="F51" t="n">
-        <v>13.59</v>
+        <v>13.91</v>
       </c>
       <c r="G51" t="n">
-        <v>242.1</v>
+        <v>247.5</v>
       </c>
       <c r="H51" t="n">
-        <v>84.5</v>
+        <v>76</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>75.65000000000001</v>
+        <v>112.21</v>
       </c>
       <c r="K51" t="n">
-        <v>-16.39</v>
+        <v>399.37</v>
       </c>
       <c r="L51" t="n">
-        <v>77.40000000000001</v>
+        <v>414.83</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:21:54</t>
+          <t>07:18:09</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.49</v>
+        <v>3.85</v>
       </c>
       <c r="F52" t="n">
-        <v>13.39</v>
+        <v>13.27</v>
       </c>
       <c r="G52" t="n">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="H52" t="n">
-        <v>83.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>15.43</v>
+        <v>40.2</v>
       </c>
       <c r="K52" t="n">
-        <v>-300.3</v>
+        <v>320.39</v>
       </c>
       <c r="L52" t="n">
-        <v>300.69</v>
+        <v>322.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:26:43</t>
+          <t>07:23:02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.59</v>
+        <v>5.1</v>
       </c>
       <c r="F53" t="n">
-        <v>13.54</v>
+        <v>13.59</v>
       </c>
       <c r="G53" t="n">
-        <v>245.1</v>
+        <v>264.4</v>
       </c>
       <c r="H53" t="n">
-        <v>77.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>-307.39</v>
+        <v>507.11</v>
       </c>
       <c r="K53" t="n">
-        <v>-100.09</v>
+        <v>-718.04</v>
       </c>
       <c r="L53" t="n">
-        <v>323.27</v>
+        <v>879.0599999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:27:31</t>
+          <t>07:24:31</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.96</v>
+        <v>4.93</v>
       </c>
       <c r="F54" t="n">
-        <v>14.56</v>
+        <v>14.18</v>
       </c>
       <c r="G54" t="n">
-        <v>253</v>
+        <v>244.4</v>
       </c>
       <c r="H54" t="n">
-        <v>84</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>-767.1799999999999</v>
+        <v>-199.11</v>
       </c>
       <c r="K54" t="n">
-        <v>67.53</v>
+        <v>-69.05</v>
       </c>
       <c r="L54" t="n">
-        <v>770.15</v>
+        <v>210.75</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:28:28</t>
+          <t>07:26:35</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.65</v>
+        <v>4.98</v>
       </c>
       <c r="F55" t="n">
-        <v>13.7</v>
+        <v>14.71</v>
       </c>
       <c r="G55" t="n">
-        <v>264</v>
+        <v>262.2</v>
       </c>
       <c r="H55" t="n">
-        <v>74.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>474.94</v>
+        <v>62.5</v>
       </c>
       <c r="K55" t="n">
-        <v>101.52</v>
+        <v>-521.63</v>
       </c>
       <c r="L55" t="n">
-        <v>485.67</v>
+        <v>525.36</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:34:14</t>
+          <t>07:32:19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.79</v>
+        <v>5.14</v>
       </c>
       <c r="F56" t="n">
-        <v>14.37</v>
+        <v>13.77</v>
       </c>
       <c r="G56" t="n">
-        <v>260.4</v>
+        <v>249.4</v>
       </c>
       <c r="H56" t="n">
-        <v>83</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>-33.5</v>
+        <v>207.03</v>
       </c>
       <c r="K56" t="n">
-        <v>36.16</v>
+        <v>-77.70999999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>49.29</v>
+        <v>221.13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:35:53</t>
+          <t>07:33:20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.46</v>
+        <v>4.11</v>
       </c>
       <c r="F57" t="n">
-        <v>14.12</v>
+        <v>13.16</v>
       </c>
       <c r="G57" t="n">
-        <v>265.8</v>
+        <v>248.4</v>
       </c>
       <c r="H57" t="n">
-        <v>76.8</v>
+        <v>83.2</v>
       </c>
       <c r="I57" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-16.69</v>
+        <v>579.66</v>
       </c>
       <c r="K57" t="n">
-        <v>-248.79</v>
+        <v>45.24</v>
       </c>
       <c r="L57" t="n">
-        <v>249.35</v>
+        <v>581.42</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:36:59</t>
+          <t>07:35:06</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.76</v>
+        <v>4.61</v>
       </c>
       <c r="F58" t="n">
-        <v>14.32</v>
+        <v>13.51</v>
       </c>
       <c r="G58" t="n">
-        <v>261.3</v>
+        <v>245.9</v>
       </c>
       <c r="H58" t="n">
-        <v>77.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>23.41</v>
+        <v>-1081.11</v>
       </c>
       <c r="K58" t="n">
-        <v>-472.63</v>
+        <v>619.3200000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>473.21</v>
+        <v>1245.94</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:47:37</t>
+          <t>07:45:02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.05</v>
+        <v>5.02</v>
       </c>
       <c r="F59" t="n">
-        <v>13.9</v>
+        <v>13.74</v>
       </c>
       <c r="G59" t="n">
-        <v>259.8</v>
+        <v>245.6</v>
       </c>
       <c r="H59" t="n">
-        <v>84.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="I59" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-100.55</v>
+        <v>97.95</v>
       </c>
       <c r="K59" t="n">
-        <v>-14.68</v>
+        <v>171.36</v>
       </c>
       <c r="L59" t="n">
-        <v>101.61</v>
+        <v>197.37</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:48:53</t>
+          <t>07:46:43</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.83</v>
+        <v>5.4</v>
       </c>
       <c r="F60" t="n">
-        <v>13.54</v>
+        <v>13.61</v>
       </c>
       <c r="G60" t="n">
-        <v>252.4</v>
+        <v>251.7</v>
       </c>
       <c r="H60" t="n">
-        <v>77.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-45.7</v>
+        <v>-106.62</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.45</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>45.83</v>
+        <v>124.61</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:51:13</t>
+          <t>07:48:13</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.75</v>
+        <v>4.28</v>
       </c>
       <c r="F61" t="n">
-        <v>13.36</v>
+        <v>14.07</v>
       </c>
       <c r="G61" t="n">
-        <v>250.7</v>
+        <v>246.2</v>
       </c>
       <c r="H61" t="n">
-        <v>82.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-3.26</v>
+        <v>-2.2</v>
       </c>
       <c r="K61" t="n">
-        <v>66.01000000000001</v>
+        <v>248.69</v>
       </c>
       <c r="L61" t="n">
-        <v>66.09</v>
+        <v>248.69</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:54:49</t>
+          <t>07:52:39</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.98</v>
+        <v>5.13</v>
       </c>
       <c r="F62" t="n">
-        <v>14.92</v>
+        <v>13.41</v>
       </c>
       <c r="G62" t="n">
-        <v>265.7</v>
+        <v>248.5</v>
       </c>
       <c r="H62" t="n">
-        <v>83.59999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-70.87</v>
+        <v>-70.15000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>19.93</v>
+        <v>-532.4400000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>73.62</v>
+        <v>537.04</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:56:26</t>
+          <t>07:54:48</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.5</v>
+        <v>4.69</v>
       </c>
       <c r="F63" t="n">
-        <v>13.74</v>
+        <v>14.04</v>
       </c>
       <c r="G63" t="n">
-        <v>257.4</v>
+        <v>249.3</v>
       </c>
       <c r="H63" t="n">
-        <v>75.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-121.77</v>
+        <v>-193.74</v>
       </c>
       <c r="K63" t="n">
-        <v>45.23</v>
+        <v>-120.93</v>
       </c>
       <c r="L63" t="n">
-        <v>129.9</v>
+        <v>228.39</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:57:35</t>
+          <t>07:55:53</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.89</v>
+        <v>3.8</v>
       </c>
       <c r="F64" t="n">
-        <v>14.04</v>
+        <v>13.42</v>
       </c>
       <c r="G64" t="n">
-        <v>262.7</v>
+        <v>254.7</v>
       </c>
       <c r="H64" t="n">
-        <v>81.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>70.61</v>
+        <v>-221.45</v>
       </c>
       <c r="K64" t="n">
-        <v>217.16</v>
+        <v>27.68</v>
       </c>
       <c r="L64" t="n">
-        <v>228.35</v>
+        <v>223.17</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:02:12</t>
+          <t>08:01:24</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.77</v>
+        <v>4.99</v>
       </c>
       <c r="F65" t="n">
-        <v>13.22</v>
+        <v>13.64</v>
       </c>
       <c r="G65" t="n">
-        <v>266.7</v>
+        <v>249.1</v>
       </c>
       <c r="H65" t="n">
-        <v>83.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-50.64</v>
+        <v>-12.77</v>
       </c>
       <c r="K65" t="n">
-        <v>-63.97</v>
+        <v>443.77</v>
       </c>
       <c r="L65" t="n">
-        <v>81.58</v>
+        <v>443.96</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:04:01</t>
+          <t>08:02:06</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.13</v>
+        <v>5.16</v>
       </c>
       <c r="F66" t="n">
-        <v>13.63</v>
+        <v>13.48</v>
       </c>
       <c r="G66" t="n">
-        <v>262.5</v>
+        <v>259.2</v>
       </c>
       <c r="H66" t="n">
         <v>81.3</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-524.6900000000001</v>
+        <v>-93.34</v>
       </c>
       <c r="K66" t="n">
-        <v>-161.3</v>
+        <v>-469.32</v>
       </c>
       <c r="L66" t="n">
-        <v>548.92</v>
+        <v>478.51</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:05:22</t>
+          <t>08:03:43</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.82</v>
+        <v>5.78</v>
       </c>
       <c r="F67" t="n">
-        <v>13.83</v>
+        <v>13.78</v>
       </c>
       <c r="G67" t="n">
-        <v>248.8</v>
+        <v>259</v>
       </c>
       <c r="H67" t="n">
-        <v>78.09999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="I67" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>-33.09</v>
+        <v>79.41</v>
       </c>
       <c r="K67" t="n">
-        <v>-5.8</v>
+        <v>-431.5</v>
       </c>
       <c r="L67" t="n">
-        <v>33.6</v>
+        <v>438.75</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:09:17</t>
+          <t>08:08:27</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.06</v>
+        <v>4.44</v>
       </c>
       <c r="F68" t="n">
-        <v>14.04</v>
+        <v>13.85</v>
       </c>
       <c r="G68" t="n">
-        <v>264.2</v>
+        <v>244.4</v>
       </c>
       <c r="H68" t="n">
-        <v>76.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-374.95</v>
+        <v>182.75</v>
       </c>
       <c r="K68" t="n">
-        <v>-209.32</v>
+        <v>-512.58</v>
       </c>
       <c r="L68" t="n">
-        <v>429.42</v>
+        <v>544.1799999999999</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:11:11</t>
+          <t>08:10:50</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.39</v>
+        <v>4.81</v>
       </c>
       <c r="F69" t="n">
-        <v>14.03</v>
+        <v>13.4</v>
       </c>
       <c r="G69" t="n">
-        <v>253.5</v>
+        <v>256.8</v>
       </c>
       <c r="H69" t="n">
-        <v>76.8</v>
+        <v>82.5</v>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-681.04</v>
+        <v>-151.76</v>
       </c>
       <c r="K69" t="n">
-        <v>-141.88</v>
+        <v>238.46</v>
       </c>
       <c r="L69" t="n">
-        <v>695.66</v>
+        <v>282.65</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:12:29</t>
+          <t>08:13:20</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.92</v>
+        <v>4.57</v>
       </c>
       <c r="F70" t="n">
-        <v>14.14</v>
+        <v>14</v>
       </c>
       <c r="G70" t="n">
-        <v>251.2</v>
+        <v>256.1</v>
       </c>
       <c r="H70" t="n">
-        <v>78</v>
+        <v>79.3</v>
       </c>
       <c r="I70" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>106.89</v>
+        <v>-545.26</v>
       </c>
       <c r="K70" t="n">
-        <v>530.48</v>
+        <v>573.1799999999999</v>
       </c>
       <c r="L70" t="n">
-        <v>541.14</v>
+        <v>791.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:18:09</t>
+          <t>08:18:28</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.21</v>
+        <v>5.97</v>
       </c>
       <c r="F71" t="n">
-        <v>13.74</v>
+        <v>14.34</v>
       </c>
       <c r="G71" t="n">
-        <v>252.2</v>
+        <v>258.2</v>
       </c>
       <c r="H71" t="n">
-        <v>76.5</v>
+        <v>75.5</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-94.23999999999999</v>
+        <v>-296.67</v>
       </c>
       <c r="K71" t="n">
-        <v>260.42</v>
+        <v>116.41</v>
       </c>
       <c r="L71" t="n">
-        <v>276.94</v>
+        <v>318.69</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:19:11</t>
+          <t>08:20:18</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.97</v>
+        <v>5.26</v>
       </c>
       <c r="F72" t="n">
-        <v>13.78</v>
+        <v>14.25</v>
       </c>
       <c r="G72" t="n">
-        <v>252.9</v>
+        <v>259.1</v>
       </c>
       <c r="H72" t="n">
-        <v>73.2</v>
+        <v>72.3</v>
       </c>
       <c r="I72" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>-404.27</v>
+        <v>102.71</v>
       </c>
       <c r="K72" t="n">
-        <v>-67.84</v>
+        <v>-335.46</v>
       </c>
       <c r="L72" t="n">
-        <v>409.92</v>
+        <v>350.83</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:20:53</t>
+          <t>08:21:59</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.9</v>
+        <v>4.51</v>
       </c>
       <c r="F73" t="n">
-        <v>14.24</v>
+        <v>13.38</v>
       </c>
       <c r="G73" t="n">
-        <v>253.8</v>
+        <v>266.1</v>
       </c>
       <c r="H73" t="n">
-        <v>78.90000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>542.14</v>
+        <v>-38.43</v>
       </c>
       <c r="K73" t="n">
-        <v>129.7</v>
+        <v>-350.21</v>
       </c>
       <c r="L73" t="n">
-        <v>557.4400000000001</v>
+        <v>352.31</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:32:39</t>
+          <t>08:29:58</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.61</v>
+        <v>5.25</v>
       </c>
       <c r="F74" t="n">
-        <v>13.59</v>
+        <v>13.87</v>
       </c>
       <c r="G74" t="n">
-        <v>252.1</v>
+        <v>254.6</v>
       </c>
       <c r="H74" t="n">
-        <v>80.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>-49.87</v>
+        <v>88.54000000000001</v>
       </c>
       <c r="K74" t="n">
-        <v>-153.85</v>
+        <v>112.2</v>
       </c>
       <c r="L74" t="n">
-        <v>161.73</v>
+        <v>142.93</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:34:16</t>
+          <t>08:31:25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.96</v>
+        <v>5.05</v>
       </c>
       <c r="F75" t="n">
-        <v>14.08</v>
+        <v>14.48</v>
       </c>
       <c r="G75" t="n">
-        <v>260.1</v>
+        <v>251.4</v>
       </c>
       <c r="H75" t="n">
-        <v>79.40000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-127.81</v>
+        <v>137.55</v>
       </c>
       <c r="K75" t="n">
-        <v>-75.11</v>
+        <v>84.39</v>
       </c>
       <c r="L75" t="n">
-        <v>148.24</v>
+        <v>161.37</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:36:19</t>
+          <t>08:34:13</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.94</v>
+        <v>4.88</v>
       </c>
       <c r="F76" t="n">
-        <v>13.14</v>
+        <v>13.89</v>
       </c>
       <c r="G76" t="n">
-        <v>246.4</v>
+        <v>254.9</v>
       </c>
       <c r="H76" t="n">
-        <v>79</v>
+        <v>77.7</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>-109.63</v>
+        <v>175.47</v>
       </c>
       <c r="K76" t="n">
-        <v>37.18</v>
+        <v>-138.86</v>
       </c>
       <c r="L76" t="n">
-        <v>115.76</v>
+        <v>223.77</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:40:56</t>
+          <t>08:37:57</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.55</v>
+        <v>4.63</v>
       </c>
       <c r="F77" t="n">
-        <v>14.59</v>
+        <v>13.76</v>
       </c>
       <c r="G77" t="n">
-        <v>239.6</v>
+        <v>253.2</v>
       </c>
       <c r="H77" t="n">
-        <v>82.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="I77" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-139.62</v>
+        <v>89.09</v>
       </c>
       <c r="K77" t="n">
-        <v>-44.2</v>
+        <v>536.63</v>
       </c>
       <c r="L77" t="n">
-        <v>146.45</v>
+        <v>543.98</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:42:30</t>
+          <t>08:39:51</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.77</v>
+        <v>5.03</v>
       </c>
       <c r="F78" t="n">
-        <v>13.73</v>
+        <v>14.29</v>
       </c>
       <c r="G78" t="n">
-        <v>246.8</v>
+        <v>250.2</v>
       </c>
       <c r="H78" t="n">
-        <v>78.09999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I78" t="n">
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>320.7</v>
+        <v>-914.61</v>
       </c>
       <c r="K78" t="n">
-        <v>-120.56</v>
+        <v>134.3</v>
       </c>
       <c r="L78" t="n">
-        <v>342.61</v>
+        <v>924.42</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:45:00</t>
+          <t>08:41:49</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="F79" t="n">
-        <v>13.19</v>
+        <v>13.8</v>
       </c>
       <c r="G79" t="n">
-        <v>258.7</v>
+        <v>261.6</v>
       </c>
       <c r="H79" t="n">
-        <v>85.7</v>
+        <v>67.5</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>-253.51</v>
+        <v>100.34</v>
       </c>
       <c r="K79" t="n">
-        <v>116.97</v>
+        <v>304.72</v>
       </c>
       <c r="L79" t="n">
-        <v>279.2</v>
+        <v>320.81</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:49:44</t>
+          <t>08:46:53</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.5</v>
+        <v>5.13</v>
       </c>
       <c r="F80" t="n">
-        <v>13.98</v>
+        <v>14.08</v>
       </c>
       <c r="G80" t="n">
-        <v>252.1</v>
+        <v>239.2</v>
       </c>
       <c r="H80" t="n">
-        <v>85.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="I80" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>-227.25</v>
+        <v>323.24</v>
       </c>
       <c r="K80" t="n">
-        <v>-67.64</v>
+        <v>-649.73</v>
       </c>
       <c r="L80" t="n">
-        <v>237.1</v>
+        <v>725.7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:51:56</t>
+          <t>08:48:49</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.78</v>
+        <v>4.3</v>
       </c>
       <c r="F81" t="n">
-        <v>13.27</v>
+        <v>13.23</v>
       </c>
       <c r="G81" t="n">
-        <v>268</v>
+        <v>257.2</v>
       </c>
       <c r="H81" t="n">
-        <v>75.5</v>
+        <v>78.8</v>
       </c>
       <c r="I81" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>-106.85</v>
+        <v>158.06</v>
       </c>
       <c r="K81" t="n">
-        <v>-67.31999999999999</v>
+        <v>-181.46</v>
       </c>
       <c r="L81" t="n">
-        <v>126.29</v>
+        <v>240.65</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:53:03</t>
+          <t>08:49:57</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.34</v>
+        <v>4.9</v>
       </c>
       <c r="F82" t="n">
         <v>13.87</v>
       </c>
       <c r="G82" t="n">
-        <v>250.9</v>
+        <v>254.2</v>
       </c>
       <c r="H82" t="n">
-        <v>83.40000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="I82" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-113.48</v>
+        <v>52.29</v>
       </c>
       <c r="K82" t="n">
-        <v>44.05</v>
+        <v>-121.22</v>
       </c>
       <c r="L82" t="n">
-        <v>121.73</v>
+        <v>132.02</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:57:34</t>
+          <t>08:53:20</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.16</v>
+        <v>5.11</v>
       </c>
       <c r="F83" t="n">
-        <v>13.24</v>
+        <v>13.54</v>
       </c>
       <c r="G83" t="n">
-        <v>249.4</v>
+        <v>252.6</v>
       </c>
       <c r="H83" t="n">
-        <v>83.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>-102.02</v>
+        <v>-348.63</v>
       </c>
       <c r="K83" t="n">
-        <v>577.13</v>
+        <v>156.34</v>
       </c>
       <c r="L83" t="n">
-        <v>586.08</v>
+        <v>382.07</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:59:01</t>
+          <t>08:55:08</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.24</v>
+        <v>5.01</v>
       </c>
       <c r="F84" t="n">
-        <v>13.25</v>
+        <v>13.14</v>
       </c>
       <c r="G84" t="n">
-        <v>251.5</v>
+        <v>250</v>
       </c>
       <c r="H84" t="n">
-        <v>78.2</v>
+        <v>77.3</v>
       </c>
       <c r="I84" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>294.04</v>
+        <v>26.4</v>
       </c>
       <c r="K84" t="n">
-        <v>-143.41</v>
+        <v>359.7</v>
       </c>
       <c r="L84" t="n">
-        <v>327.15</v>
+        <v>360.66</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:56:17</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.57</v>
+        <v>4.76</v>
       </c>
       <c r="F85" t="n">
-        <v>14.01</v>
+        <v>13.11</v>
       </c>
       <c r="G85" t="n">
-        <v>265.9</v>
+        <v>246.2</v>
       </c>
       <c r="H85" t="n">
-        <v>75.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.02</v>
+        <v>523.6</v>
       </c>
       <c r="K85" t="n">
-        <v>-105.43</v>
+        <v>229.22</v>
       </c>
       <c r="L85" t="n">
-        <v>106.01</v>
+        <v>571.58</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:03:39</t>
+          <t>09:00:46</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>5.33</v>
+        <v>4.62</v>
       </c>
       <c r="F86" t="n">
-        <v>13.77</v>
+        <v>14.37</v>
       </c>
       <c r="G86" t="n">
-        <v>258.9</v>
+        <v>251.9</v>
       </c>
       <c r="H86" t="n">
-        <v>75.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="I86" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>660.67</v>
+        <v>1033.49</v>
       </c>
       <c r="K86" t="n">
-        <v>574.8</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="L86" t="n">
-        <v>875.72</v>
+        <v>1037.64</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:05:30</t>
+          <t>09:01:29</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.42</v>
+        <v>4.84</v>
       </c>
       <c r="F87" t="n">
-        <v>13.55</v>
+        <v>14.04</v>
       </c>
       <c r="G87" t="n">
-        <v>251.3</v>
+        <v>263.3</v>
       </c>
       <c r="H87" t="n">
-        <v>84.09999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-546.02</v>
+        <v>-635.38</v>
       </c>
       <c r="K87" t="n">
-        <v>234.87</v>
+        <v>102.7</v>
       </c>
       <c r="L87" t="n">
-        <v>594.39</v>
+        <v>643.63</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:06:53</t>
+          <t>09:03:49</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.94</v>
+        <v>5.47</v>
       </c>
       <c r="F88" t="n">
-        <v>14.23</v>
+        <v>14.15</v>
       </c>
       <c r="G88" t="n">
-        <v>244.8</v>
+        <v>247.7</v>
       </c>
       <c r="H88" t="n">
-        <v>77.5</v>
+        <v>79.3</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>610.26</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K88" t="n">
-        <v>430.3</v>
+        <v>1324.79</v>
       </c>
       <c r="L88" t="n">
-        <v>746.72</v>
+        <v>1327.27</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-30.xlsx
+++ b/output/2024-04-30.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>-45.52</v>
+        <v>-65.67</v>
       </c>
       <c r="K14" t="n">
-        <v>127.52</v>
+        <v>184</v>
       </c>
       <c r="L14" t="n">
-        <v>135.4</v>
+        <v>195.37</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-256.55</v>
+        <v>-313.25</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.18</v>
+        <v>-0.22</v>
       </c>
       <c r="L15" t="n">
-        <v>256.55</v>
+        <v>313.25</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-164.8</v>
+        <v>-190.58</v>
       </c>
       <c r="K16" t="n">
-        <v>291.11</v>
+        <v>336.64</v>
       </c>
       <c r="L16" t="n">
-        <v>334.52</v>
+        <v>386.84</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>148.45</v>
+        <v>267.32</v>
       </c>
       <c r="K17" t="n">
-        <v>-52.89</v>
+        <v>-95.23999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>157.59</v>
+        <v>283.78</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-56.56</v>
+        <v>-89.09999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-160.57</v>
+        <v>-252.97</v>
       </c>
       <c r="L18" t="n">
-        <v>170.24</v>
+        <v>268.2</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>88.23999999999999</v>
+        <v>108.51</v>
       </c>
       <c r="K19" t="n">
-        <v>280.58</v>
+        <v>345.03</v>
       </c>
       <c r="L19" t="n">
-        <v>294.13</v>
+        <v>361.69</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>-209.94</v>
+        <v>-356.23</v>
       </c>
       <c r="K20" t="n">
-        <v>-115.17</v>
+        <v>-195.42</v>
       </c>
       <c r="L20" t="n">
-        <v>239.46</v>
+        <v>406.31</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>290.59</v>
+        <v>368.96</v>
       </c>
       <c r="K21" t="n">
-        <v>-510.85</v>
+        <v>-648.64</v>
       </c>
       <c r="L21" t="n">
-        <v>587.71</v>
+        <v>746.23</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-91.33</v>
+        <v>-259.51</v>
       </c>
       <c r="K22" t="n">
-        <v>8.74</v>
+        <v>24.84</v>
       </c>
       <c r="L22" t="n">
-        <v>91.75</v>
+        <v>260.7</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-96.56999999999999</v>
+        <v>-137.32</v>
       </c>
       <c r="K23" t="n">
-        <v>-640.29</v>
+        <v>-910.48</v>
       </c>
       <c r="L23" t="n">
-        <v>647.54</v>
+        <v>920.78</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>375.63</v>
+        <v>507.87</v>
       </c>
       <c r="K24" t="n">
-        <v>961.88</v>
+        <v>1300.51</v>
       </c>
       <c r="L24" t="n">
-        <v>1032.63</v>
+        <v>1396.16</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>466.82</v>
+        <v>592.3</v>
       </c>
       <c r="K25" t="n">
-        <v>-663.22</v>
+        <v>-841.49</v>
       </c>
       <c r="L25" t="n">
-        <v>811.04</v>
+        <v>1029.04</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>22.69</v>
+        <v>45.35</v>
       </c>
       <c r="K26" t="n">
-        <v>317.69</v>
+        <v>634.9400000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>318.5</v>
+        <v>636.55</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>610.77</v>
+        <v>884.55</v>
       </c>
       <c r="K27" t="n">
-        <v>452.82</v>
+        <v>655.8099999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>760.3200000000001</v>
+        <v>1101.14</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-598.9400000000001</v>
+        <v>-867.84</v>
       </c>
       <c r="K28" t="n">
-        <v>-658.8099999999999</v>
+        <v>-954.59</v>
       </c>
       <c r="L28" t="n">
-        <v>890.37</v>
+        <v>1290.11</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>114.69</v>
+        <v>157.3</v>
       </c>
       <c r="K29" t="n">
-        <v>-89.54000000000001</v>
+        <v>-122.8</v>
       </c>
       <c r="L29" t="n">
-        <v>145.5</v>
+        <v>199.56</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>95.02</v>
+        <v>123.45</v>
       </c>
       <c r="K30" t="n">
-        <v>151.55</v>
+        <v>196.89</v>
       </c>
       <c r="L30" t="n">
-        <v>178.88</v>
+        <v>232.39</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>60.94</v>
+        <v>105.91</v>
       </c>
       <c r="K31" t="n">
-        <v>-56.55</v>
+        <v>-98.28</v>
       </c>
       <c r="L31" t="n">
-        <v>83.14</v>
+        <v>144.49</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-212.76</v>
+        <v>-309.47</v>
       </c>
       <c r="K32" t="n">
-        <v>76.04000000000001</v>
+        <v>110.6</v>
       </c>
       <c r="L32" t="n">
-        <v>225.94</v>
+        <v>328.64</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>16.64</v>
+        <v>17.65</v>
       </c>
       <c r="K33" t="n">
-        <v>589.52</v>
+        <v>625.24</v>
       </c>
       <c r="L33" t="n">
-        <v>589.76</v>
+        <v>625.49</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>295.98</v>
+        <v>359.58</v>
       </c>
       <c r="K34" t="n">
-        <v>159.96</v>
+        <v>194.34</v>
       </c>
       <c r="L34" t="n">
-        <v>336.44</v>
+        <v>408.74</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>110.49</v>
+        <v>181.54</v>
       </c>
       <c r="K35" t="n">
-        <v>138.7</v>
+        <v>227.9</v>
       </c>
       <c r="L35" t="n">
-        <v>177.33</v>
+        <v>291.36</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>214.91</v>
+        <v>298.48</v>
       </c>
       <c r="K36" t="n">
-        <v>287.67</v>
+        <v>399.54</v>
       </c>
       <c r="L36" t="n">
-        <v>359.08</v>
+        <v>498.72</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>488.05</v>
+        <v>577.08</v>
       </c>
       <c r="K37" t="n">
-        <v>-403.66</v>
+        <v>-477.29</v>
       </c>
       <c r="L37" t="n">
-        <v>633.35</v>
+        <v>748.88</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-370.71</v>
+        <v>-565.2</v>
       </c>
       <c r="K38" t="n">
-        <v>353.19</v>
+        <v>538.48</v>
       </c>
       <c r="L38" t="n">
-        <v>512.03</v>
+        <v>780.64</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>-163.83</v>
+        <v>-352.89</v>
       </c>
       <c r="K39" t="n">
-        <v>339.31</v>
+        <v>730.87</v>
       </c>
       <c r="L39" t="n">
-        <v>376.79</v>
+        <v>811.6</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>664.12</v>
+        <v>975.39</v>
       </c>
       <c r="K40" t="n">
-        <v>45.02</v>
+        <v>66.11</v>
       </c>
       <c r="L40" t="n">
-        <v>665.64</v>
+        <v>977.63</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-116.96</v>
+        <v>-200.51</v>
       </c>
       <c r="K41" t="n">
-        <v>520.55</v>
+        <v>892.34</v>
       </c>
       <c r="L41" t="n">
-        <v>533.52</v>
+        <v>914.59</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-487.45</v>
+        <v>-812.1</v>
       </c>
       <c r="K42" t="n">
-        <v>-494.2</v>
+        <v>-823.34</v>
       </c>
       <c r="L42" t="n">
-        <v>694.15</v>
+        <v>1156.46</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>127.08</v>
+        <v>339.13</v>
       </c>
       <c r="K43" t="n">
-        <v>180.67</v>
+        <v>482.15</v>
       </c>
       <c r="L43" t="n">
-        <v>220.89</v>
+        <v>589.47</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>233.19</v>
+        <v>321.85</v>
       </c>
       <c r="K44" t="n">
-        <v>38.75</v>
+        <v>53.49</v>
       </c>
       <c r="L44" t="n">
-        <v>236.39</v>
+        <v>326.27</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>107.74</v>
+        <v>199.28</v>
       </c>
       <c r="K45" t="n">
-        <v>-9.630000000000001</v>
+        <v>-17.82</v>
       </c>
       <c r="L45" t="n">
-        <v>108.17</v>
+        <v>200.07</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-349.81</v>
+        <v>-403.22</v>
       </c>
       <c r="K46" t="n">
-        <v>-12.41</v>
+        <v>-14.31</v>
       </c>
       <c r="L46" t="n">
-        <v>350.03</v>
+        <v>403.48</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>382.5</v>
+        <v>435.09</v>
       </c>
       <c r="K47" t="n">
-        <v>-108.5</v>
+        <v>-123.41</v>
       </c>
       <c r="L47" t="n">
-        <v>397.59</v>
+        <v>452.26</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-201.37</v>
+        <v>-350.98</v>
       </c>
       <c r="K48" t="n">
-        <v>18.81</v>
+        <v>32.78</v>
       </c>
       <c r="L48" t="n">
-        <v>202.25</v>
+        <v>352.51</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>287.78</v>
+        <v>391.82</v>
       </c>
       <c r="K49" t="n">
-        <v>-169.31</v>
+        <v>-230.52</v>
       </c>
       <c r="L49" t="n">
-        <v>333.89</v>
+        <v>454.6</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-292.17</v>
+        <v>-412.01</v>
       </c>
       <c r="K50" t="n">
-        <v>-78.92</v>
+        <v>-111.3</v>
       </c>
       <c r="L50" t="n">
-        <v>302.64</v>
+        <v>426.78</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>112.21</v>
+        <v>174.57</v>
       </c>
       <c r="K51" t="n">
-        <v>399.37</v>
+        <v>621.3</v>
       </c>
       <c r="L51" t="n">
-        <v>414.83</v>
+        <v>645.36</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>40.2</v>
+        <v>57.25</v>
       </c>
       <c r="K52" t="n">
-        <v>320.39</v>
+        <v>456.28</v>
       </c>
       <c r="L52" t="n">
-        <v>322.9</v>
+        <v>459.86</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>507.11</v>
+        <v>690.4299999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>-718.04</v>
+        <v>-977.63</v>
       </c>
       <c r="L53" t="n">
-        <v>879.0599999999999</v>
+        <v>1196.85</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>-199.11</v>
+        <v>-496.7</v>
       </c>
       <c r="K54" t="n">
-        <v>-69.05</v>
+        <v>-172.25</v>
       </c>
       <c r="L54" t="n">
-        <v>210.75</v>
+        <v>525.72</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>62.5</v>
+        <v>103.52</v>
       </c>
       <c r="K55" t="n">
-        <v>-521.63</v>
+        <v>-864.05</v>
       </c>
       <c r="L55" t="n">
-        <v>525.36</v>
+        <v>870.23</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>207.03</v>
+        <v>613.37</v>
       </c>
       <c r="K56" t="n">
-        <v>-77.70999999999999</v>
+        <v>-230.25</v>
       </c>
       <c r="L56" t="n">
-        <v>221.13</v>
+        <v>655.16</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>579.66</v>
+        <v>942.1900000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>45.24</v>
+        <v>73.53</v>
       </c>
       <c r="L57" t="n">
-        <v>581.42</v>
+        <v>945.05</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-1081.11</v>
+        <v>-1480.9</v>
       </c>
       <c r="K58" t="n">
-        <v>619.3200000000001</v>
+        <v>848.35</v>
       </c>
       <c r="L58" t="n">
-        <v>1245.94</v>
+        <v>1706.69</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>97.95</v>
+        <v>150.31</v>
       </c>
       <c r="K59" t="n">
-        <v>171.36</v>
+        <v>262.97</v>
       </c>
       <c r="L59" t="n">
-        <v>197.37</v>
+        <v>302.89</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-106.62</v>
+        <v>-203.91</v>
       </c>
       <c r="K60" t="n">
-        <v>64.48999999999999</v>
+        <v>123.34</v>
       </c>
       <c r="L60" t="n">
-        <v>124.61</v>
+        <v>238.31</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-2.2</v>
+        <v>-2.78</v>
       </c>
       <c r="K61" t="n">
-        <v>248.69</v>
+        <v>315.04</v>
       </c>
       <c r="L61" t="n">
-        <v>248.69</v>
+        <v>315.05</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-70.15000000000001</v>
+        <v>-80.69</v>
       </c>
       <c r="K62" t="n">
-        <v>-532.4400000000001</v>
+        <v>-612.51</v>
       </c>
       <c r="L62" t="n">
-        <v>537.04</v>
+        <v>617.8</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-193.74</v>
+        <v>-292.69</v>
       </c>
       <c r="K63" t="n">
-        <v>-120.93</v>
+        <v>-182.7</v>
       </c>
       <c r="L63" t="n">
-        <v>228.39</v>
+        <v>345.03</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-221.45</v>
+        <v>-271.76</v>
       </c>
       <c r="K64" t="n">
-        <v>27.68</v>
+        <v>33.96</v>
       </c>
       <c r="L64" t="n">
-        <v>223.17</v>
+        <v>273.87</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-12.77</v>
+        <v>-18.66</v>
       </c>
       <c r="K65" t="n">
-        <v>443.77</v>
+        <v>648.3200000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>443.96</v>
+        <v>648.59</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-93.34</v>
+        <v>-135.37</v>
       </c>
       <c r="K66" t="n">
-        <v>-469.32</v>
+        <v>-680.66</v>
       </c>
       <c r="L66" t="n">
-        <v>478.51</v>
+        <v>693.99</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>79.41</v>
+        <v>125.69</v>
       </c>
       <c r="K67" t="n">
-        <v>-431.5</v>
+        <v>-682.96</v>
       </c>
       <c r="L67" t="n">
-        <v>438.75</v>
+        <v>694.4299999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>182.75</v>
+        <v>280.22</v>
       </c>
       <c r="K68" t="n">
-        <v>-512.58</v>
+        <v>-786</v>
       </c>
       <c r="L68" t="n">
-        <v>544.1799999999999</v>
+        <v>834.46</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-151.76</v>
+        <v>-296.56</v>
       </c>
       <c r="K69" t="n">
-        <v>238.46</v>
+        <v>465.97</v>
       </c>
       <c r="L69" t="n">
-        <v>282.65</v>
+        <v>552.33</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-545.26</v>
+        <v>-693.22</v>
       </c>
       <c r="K70" t="n">
-        <v>573.1799999999999</v>
+        <v>728.72</v>
       </c>
       <c r="L70" t="n">
-        <v>791.1</v>
+        <v>1005.78</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-296.67</v>
+        <v>-783.73</v>
       </c>
       <c r="K71" t="n">
-        <v>116.41</v>
+        <v>307.52</v>
       </c>
       <c r="L71" t="n">
-        <v>318.69</v>
+        <v>841.9</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>102.71</v>
+        <v>227.43</v>
       </c>
       <c r="K72" t="n">
-        <v>-335.46</v>
+        <v>-742.8200000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>350.83</v>
+        <v>776.86</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-38.43</v>
+        <v>-81.5</v>
       </c>
       <c r="K73" t="n">
-        <v>-350.21</v>
+        <v>-742.65</v>
       </c>
       <c r="L73" t="n">
-        <v>352.31</v>
+        <v>747.11</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>88.54000000000001</v>
+        <v>163.31</v>
       </c>
       <c r="K74" t="n">
-        <v>112.2</v>
+        <v>206.95</v>
       </c>
       <c r="L74" t="n">
-        <v>142.93</v>
+        <v>263.63</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>137.55</v>
+        <v>232.32</v>
       </c>
       <c r="K75" t="n">
-        <v>84.39</v>
+        <v>142.53</v>
       </c>
       <c r="L75" t="n">
-        <v>161.37</v>
+        <v>272.56</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>175.47</v>
+        <v>240.06</v>
       </c>
       <c r="K76" t="n">
-        <v>-138.86</v>
+        <v>-189.96</v>
       </c>
       <c r="L76" t="n">
-        <v>223.77</v>
+        <v>306.12</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>89.09</v>
+        <v>102.54</v>
       </c>
       <c r="K77" t="n">
-        <v>536.63</v>
+        <v>617.63</v>
       </c>
       <c r="L77" t="n">
-        <v>543.98</v>
+        <v>626.08</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-914.61</v>
+        <v>-905.15</v>
       </c>
       <c r="K78" t="n">
-        <v>134.3</v>
+        <v>132.91</v>
       </c>
       <c r="L78" t="n">
-        <v>924.42</v>
+        <v>914.85</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>100.34</v>
+        <v>142.94</v>
       </c>
       <c r="K79" t="n">
-        <v>304.72</v>
+        <v>434.1</v>
       </c>
       <c r="L79" t="n">
-        <v>320.81</v>
+        <v>457.03</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>323.24</v>
+        <v>416.48</v>
       </c>
       <c r="K80" t="n">
-        <v>-649.73</v>
+        <v>-837.17</v>
       </c>
       <c r="L80" t="n">
-        <v>725.7</v>
+        <v>935.05</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>158.06</v>
+        <v>270.16</v>
       </c>
       <c r="K81" t="n">
-        <v>-181.46</v>
+        <v>-310.16</v>
       </c>
       <c r="L81" t="n">
-        <v>240.65</v>
+        <v>411.33</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>52.29</v>
+        <v>123.7</v>
       </c>
       <c r="K82" t="n">
-        <v>-121.22</v>
+        <v>-286.79</v>
       </c>
       <c r="L82" t="n">
-        <v>132.02</v>
+        <v>312.33</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>-348.63</v>
+        <v>-632.7</v>
       </c>
       <c r="K83" t="n">
-        <v>156.34</v>
+        <v>283.73</v>
       </c>
       <c r="L83" t="n">
-        <v>382.07</v>
+        <v>693.4</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>26.4</v>
+        <v>47.29</v>
       </c>
       <c r="K84" t="n">
-        <v>359.7</v>
+        <v>644.27</v>
       </c>
       <c r="L84" t="n">
-        <v>360.66</v>
+        <v>646.01</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>523.6</v>
+        <v>819.3200000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>229.22</v>
+        <v>358.68</v>
       </c>
       <c r="L85" t="n">
-        <v>571.58</v>
+        <v>894.39</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>1033.49</v>
+        <v>1482.01</v>
       </c>
       <c r="K86" t="n">
-        <v>92.70999999999999</v>
+        <v>132.95</v>
       </c>
       <c r="L86" t="n">
-        <v>1037.64</v>
+        <v>1487.96</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-635.38</v>
+        <v>-991.33</v>
       </c>
       <c r="K87" t="n">
-        <v>102.7</v>
+        <v>160.24</v>
       </c>
       <c r="L87" t="n">
-        <v>643.63</v>
+        <v>1004.19</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>81.09999999999999</v>
+        <v>110.37</v>
       </c>
       <c r="K88" t="n">
-        <v>1324.79</v>
+        <v>1802.96</v>
       </c>
       <c r="L88" t="n">
-        <v>1327.27</v>
+        <v>1806.34</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-30.xlsx
+++ b/output/2024-04-30.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>-65.67</v>
+        <v>-43.92</v>
       </c>
       <c r="K14" t="n">
-        <v>184</v>
+        <v>123.04</v>
       </c>
       <c r="L14" t="n">
-        <v>195.37</v>
+        <v>130.64</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-313.25</v>
+        <v>-204.93</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="L15" t="n">
-        <v>313.25</v>
+        <v>204.93</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-190.58</v>
+        <v>-117.06</v>
       </c>
       <c r="K16" t="n">
-        <v>336.64</v>
+        <v>206.77</v>
       </c>
       <c r="L16" t="n">
-        <v>386.84</v>
+        <v>237.61</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>267.32</v>
+        <v>152.21</v>
       </c>
       <c r="K17" t="n">
-        <v>-95.23999999999999</v>
+        <v>-54.23</v>
       </c>
       <c r="L17" t="n">
-        <v>283.78</v>
+        <v>161.58</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-89.09999999999999</v>
+        <v>-51.56</v>
       </c>
       <c r="K18" t="n">
-        <v>-252.97</v>
+        <v>-146.38</v>
       </c>
       <c r="L18" t="n">
-        <v>268.2</v>
+        <v>155.2</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>108.51</v>
+        <v>68.23</v>
       </c>
       <c r="K19" t="n">
-        <v>345.03</v>
+        <v>216.94</v>
       </c>
       <c r="L19" t="n">
-        <v>361.69</v>
+        <v>227.42</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>-356.23</v>
+        <v>-183.02</v>
       </c>
       <c r="K20" t="n">
-        <v>-195.42</v>
+        <v>-100.4</v>
       </c>
       <c r="L20" t="n">
-        <v>406.31</v>
+        <v>208.75</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>368.96</v>
+        <v>184.76</v>
       </c>
       <c r="K21" t="n">
-        <v>-648.64</v>
+        <v>-324.8</v>
       </c>
       <c r="L21" t="n">
-        <v>746.23</v>
+        <v>373.68</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-259.51</v>
+        <v>-136.82</v>
       </c>
       <c r="K22" t="n">
-        <v>24.84</v>
+        <v>13.1</v>
       </c>
       <c r="L22" t="n">
-        <v>260.7</v>
+        <v>137.45</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-137.32</v>
+        <v>-64.68000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-910.48</v>
+        <v>-428.82</v>
       </c>
       <c r="L23" t="n">
-        <v>920.78</v>
+        <v>433.67</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>507.87</v>
+        <v>221.77</v>
       </c>
       <c r="K24" t="n">
-        <v>1300.51</v>
+        <v>567.89</v>
       </c>
       <c r="L24" t="n">
-        <v>1396.16</v>
+        <v>609.66</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>592.3</v>
+        <v>288.09</v>
       </c>
       <c r="K25" t="n">
-        <v>-841.49</v>
+        <v>-409.29</v>
       </c>
       <c r="L25" t="n">
-        <v>1029.04</v>
+        <v>500.51</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>45.35</v>
+        <v>19.69</v>
       </c>
       <c r="K26" t="n">
-        <v>634.9400000000001</v>
+        <v>275.75</v>
       </c>
       <c r="L26" t="n">
-        <v>636.55</v>
+        <v>276.45</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>884.55</v>
+        <v>380.5</v>
       </c>
       <c r="K27" t="n">
-        <v>655.8099999999999</v>
+        <v>282.1</v>
       </c>
       <c r="L27" t="n">
-        <v>1101.14</v>
+        <v>473.66</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-867.84</v>
+        <v>-355.76</v>
       </c>
       <c r="K28" t="n">
-        <v>-954.59</v>
+        <v>-391.32</v>
       </c>
       <c r="L28" t="n">
-        <v>1290.11</v>
+        <v>528.86</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>157.3</v>
+        <v>98.09</v>
       </c>
       <c r="K29" t="n">
-        <v>-122.8</v>
+        <v>-76.58</v>
       </c>
       <c r="L29" t="n">
-        <v>199.56</v>
+        <v>124.44</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>123.45</v>
+        <v>80.44</v>
       </c>
       <c r="K30" t="n">
-        <v>196.89</v>
+        <v>128.29</v>
       </c>
       <c r="L30" t="n">
-        <v>232.39</v>
+        <v>151.43</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>105.91</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>-98.28</v>
+        <v>-61.84</v>
       </c>
       <c r="L31" t="n">
-        <v>144.49</v>
+        <v>90.92</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-309.47</v>
+        <v>-184.61</v>
       </c>
       <c r="K32" t="n">
-        <v>110.6</v>
+        <v>65.98</v>
       </c>
       <c r="L32" t="n">
-        <v>328.64</v>
+        <v>196.05</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>17.65</v>
+        <v>10.23</v>
       </c>
       <c r="K33" t="n">
-        <v>625.24</v>
+        <v>362.33</v>
       </c>
       <c r="L33" t="n">
-        <v>625.49</v>
+        <v>362.47</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>359.58</v>
+        <v>225.29</v>
       </c>
       <c r="K34" t="n">
-        <v>194.34</v>
+        <v>121.76</v>
       </c>
       <c r="L34" t="n">
-        <v>408.74</v>
+        <v>256.09</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>181.54</v>
+        <v>102.61</v>
       </c>
       <c r="K35" t="n">
-        <v>227.9</v>
+        <v>128.82</v>
       </c>
       <c r="L35" t="n">
-        <v>291.36</v>
+        <v>164.69</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>298.48</v>
+        <v>151.95</v>
       </c>
       <c r="K36" t="n">
-        <v>399.54</v>
+        <v>203.4</v>
       </c>
       <c r="L36" t="n">
-        <v>498.72</v>
+        <v>253.89</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>577.08</v>
+        <v>298.56</v>
       </c>
       <c r="K37" t="n">
-        <v>-477.29</v>
+        <v>-246.93</v>
       </c>
       <c r="L37" t="n">
-        <v>748.88</v>
+        <v>387.44</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-565.2</v>
+        <v>-260.83</v>
       </c>
       <c r="K38" t="n">
-        <v>538.48</v>
+        <v>248.5</v>
       </c>
       <c r="L38" t="n">
-        <v>780.64</v>
+        <v>360.25</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>-352.89</v>
+        <v>-153</v>
       </c>
       <c r="K39" t="n">
-        <v>730.87</v>
+        <v>316.87</v>
       </c>
       <c r="L39" t="n">
-        <v>811.6</v>
+        <v>351.87</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>975.39</v>
+        <v>429.35</v>
       </c>
       <c r="K40" t="n">
-        <v>66.11</v>
+        <v>29.1</v>
       </c>
       <c r="L40" t="n">
-        <v>977.63</v>
+        <v>430.34</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-200.51</v>
+        <v>-82.19</v>
       </c>
       <c r="K41" t="n">
-        <v>892.34</v>
+        <v>365.8</v>
       </c>
       <c r="L41" t="n">
-        <v>914.59</v>
+        <v>374.92</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-812.1</v>
+        <v>-323.58</v>
       </c>
       <c r="K42" t="n">
-        <v>-823.34</v>
+        <v>-328.06</v>
       </c>
       <c r="L42" t="n">
-        <v>1156.46</v>
+        <v>460.78</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>339.13</v>
+        <v>141.27</v>
       </c>
       <c r="K43" t="n">
-        <v>482.15</v>
+        <v>200.85</v>
       </c>
       <c r="L43" t="n">
-        <v>589.47</v>
+        <v>245.56</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>321.85</v>
+        <v>201.64</v>
       </c>
       <c r="K44" t="n">
-        <v>53.49</v>
+        <v>33.51</v>
       </c>
       <c r="L44" t="n">
-        <v>326.27</v>
+        <v>204.41</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>199.28</v>
+        <v>124.16</v>
       </c>
       <c r="K45" t="n">
-        <v>-17.82</v>
+        <v>-11.1</v>
       </c>
       <c r="L45" t="n">
-        <v>200.07</v>
+        <v>124.65</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-403.22</v>
+        <v>-242.85</v>
       </c>
       <c r="K46" t="n">
-        <v>-14.31</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>403.48</v>
+        <v>243</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>435.09</v>
+        <v>267.09</v>
       </c>
       <c r="K47" t="n">
-        <v>-123.41</v>
+        <v>-75.76000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>452.26</v>
+        <v>277.62</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-350.98</v>
+        <v>-196.33</v>
       </c>
       <c r="K48" t="n">
-        <v>32.78</v>
+        <v>18.34</v>
       </c>
       <c r="L48" t="n">
-        <v>352.51</v>
+        <v>197.18</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>391.82</v>
+        <v>221.48</v>
       </c>
       <c r="K49" t="n">
-        <v>-230.52</v>
+        <v>-130.31</v>
       </c>
       <c r="L49" t="n">
-        <v>454.6</v>
+        <v>256.97</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-412.01</v>
+        <v>-228.6</v>
       </c>
       <c r="K50" t="n">
-        <v>-111.3</v>
+        <v>-61.75</v>
       </c>
       <c r="L50" t="n">
-        <v>426.78</v>
+        <v>236.79</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>174.57</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>621.3</v>
+        <v>302.88</v>
       </c>
       <c r="L51" t="n">
-        <v>645.36</v>
+        <v>314.61</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>57.25</v>
+        <v>29.31</v>
       </c>
       <c r="K52" t="n">
-        <v>456.28</v>
+        <v>233.58</v>
       </c>
       <c r="L52" t="n">
-        <v>459.86</v>
+        <v>235.41</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>690.4299999999999</v>
+        <v>314.98</v>
       </c>
       <c r="K53" t="n">
-        <v>-977.63</v>
+        <v>-446.01</v>
       </c>
       <c r="L53" t="n">
-        <v>1196.85</v>
+        <v>546.02</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>-496.7</v>
+        <v>-222.22</v>
       </c>
       <c r="K54" t="n">
-        <v>-172.25</v>
+        <v>-77.06</v>
       </c>
       <c r="L54" t="n">
-        <v>525.72</v>
+        <v>235.2</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>103.52</v>
+        <v>45.2</v>
       </c>
       <c r="K55" t="n">
-        <v>-864.05</v>
+        <v>-377.3</v>
       </c>
       <c r="L55" t="n">
-        <v>870.23</v>
+        <v>380</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>613.37</v>
+        <v>253.87</v>
       </c>
       <c r="K56" t="n">
-        <v>-230.25</v>
+        <v>-95.3</v>
       </c>
       <c r="L56" t="n">
-        <v>655.16</v>
+        <v>271.17</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>942.1900000000001</v>
+        <v>389</v>
       </c>
       <c r="K57" t="n">
-        <v>73.53</v>
+        <v>30.36</v>
       </c>
       <c r="L57" t="n">
-        <v>945.05</v>
+        <v>390.19</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-1480.9</v>
+        <v>-597.66</v>
       </c>
       <c r="K58" t="n">
-        <v>848.35</v>
+        <v>342.37</v>
       </c>
       <c r="L58" t="n">
-        <v>1706.69</v>
+        <v>688.78</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>150.31</v>
+        <v>88.25</v>
       </c>
       <c r="K59" t="n">
-        <v>262.97</v>
+        <v>154.39</v>
       </c>
       <c r="L59" t="n">
-        <v>302.89</v>
+        <v>177.84</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-203.91</v>
+        <v>-124.2</v>
       </c>
       <c r="K60" t="n">
-        <v>123.34</v>
+        <v>75.13</v>
       </c>
       <c r="L60" t="n">
-        <v>238.31</v>
+        <v>145.16</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-2.78</v>
+        <v>-1.68</v>
       </c>
       <c r="K61" t="n">
-        <v>315.04</v>
+        <v>189.97</v>
       </c>
       <c r="L61" t="n">
-        <v>315.05</v>
+        <v>189.98</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-80.69</v>
+        <v>-47.62</v>
       </c>
       <c r="K62" t="n">
-        <v>-612.51</v>
+        <v>-361.47</v>
       </c>
       <c r="L62" t="n">
-        <v>617.8</v>
+        <v>364.6</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-292.69</v>
+        <v>-166.65</v>
       </c>
       <c r="K63" t="n">
-        <v>-182.7</v>
+        <v>-104.02</v>
       </c>
       <c r="L63" t="n">
-        <v>345.03</v>
+        <v>196.45</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-271.76</v>
+        <v>-171.65</v>
       </c>
       <c r="K64" t="n">
-        <v>33.96</v>
+        <v>21.45</v>
       </c>
       <c r="L64" t="n">
-        <v>273.87</v>
+        <v>172.99</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-18.66</v>
+        <v>-9.18</v>
       </c>
       <c r="K65" t="n">
-        <v>648.3200000000001</v>
+        <v>318.82</v>
       </c>
       <c r="L65" t="n">
-        <v>648.59</v>
+        <v>318.95</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-135.37</v>
+        <v>-66.27</v>
       </c>
       <c r="K66" t="n">
-        <v>-680.66</v>
+        <v>-333.22</v>
       </c>
       <c r="L66" t="n">
-        <v>693.99</v>
+        <v>339.75</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>125.69</v>
+        <v>60.66</v>
       </c>
       <c r="K67" t="n">
-        <v>-682.96</v>
+        <v>-329.61</v>
       </c>
       <c r="L67" t="n">
-        <v>694.4299999999999</v>
+        <v>335.15</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>280.22</v>
+        <v>123.77</v>
       </c>
       <c r="K68" t="n">
-        <v>-786</v>
+        <v>-347.15</v>
       </c>
       <c r="L68" t="n">
-        <v>834.46</v>
+        <v>368.55</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-296.56</v>
+        <v>-139.87</v>
       </c>
       <c r="K69" t="n">
-        <v>465.97</v>
+        <v>219.77</v>
       </c>
       <c r="L69" t="n">
-        <v>552.33</v>
+        <v>260.51</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-693.22</v>
+        <v>-337.27</v>
       </c>
       <c r="K70" t="n">
-        <v>728.72</v>
+        <v>354.54</v>
       </c>
       <c r="L70" t="n">
-        <v>1005.78</v>
+        <v>489.34</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-783.73</v>
+        <v>-318.35</v>
       </c>
       <c r="K71" t="n">
-        <v>307.52</v>
+        <v>124.91</v>
       </c>
       <c r="L71" t="n">
-        <v>841.9</v>
+        <v>341.98</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>227.43</v>
+        <v>96.25</v>
       </c>
       <c r="K72" t="n">
-        <v>-742.8200000000001</v>
+        <v>-314.38</v>
       </c>
       <c r="L72" t="n">
-        <v>776.86</v>
+        <v>328.78</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-81.5</v>
+        <v>-33.15</v>
       </c>
       <c r="K73" t="n">
-        <v>-742.65</v>
+        <v>-302.12</v>
       </c>
       <c r="L73" t="n">
-        <v>747.11</v>
+        <v>303.93</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>163.31</v>
+        <v>95.27</v>
       </c>
       <c r="K74" t="n">
-        <v>206.95</v>
+        <v>120.74</v>
       </c>
       <c r="L74" t="n">
-        <v>263.63</v>
+        <v>153.8</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>232.32</v>
+        <v>136.28</v>
       </c>
       <c r="K75" t="n">
-        <v>142.53</v>
+        <v>83.61</v>
       </c>
       <c r="L75" t="n">
-        <v>272.56</v>
+        <v>159.89</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>240.06</v>
+        <v>148.34</v>
       </c>
       <c r="K76" t="n">
-        <v>-189.96</v>
+        <v>-117.39</v>
       </c>
       <c r="L76" t="n">
-        <v>306.12</v>
+        <v>189.17</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>102.54</v>
+        <v>58.39</v>
       </c>
       <c r="K77" t="n">
-        <v>617.63</v>
+        <v>351.67</v>
       </c>
       <c r="L77" t="n">
-        <v>626.08</v>
+        <v>356.49</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-905.15</v>
+        <v>-564.3099999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>132.91</v>
+        <v>82.86</v>
       </c>
       <c r="L78" t="n">
-        <v>914.85</v>
+        <v>570.36</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>142.94</v>
+        <v>83.03</v>
       </c>
       <c r="K79" t="n">
-        <v>434.1</v>
+        <v>252.16</v>
       </c>
       <c r="L79" t="n">
-        <v>457.03</v>
+        <v>265.47</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>416.48</v>
+        <v>204.05</v>
       </c>
       <c r="K80" t="n">
-        <v>-837.17</v>
+        <v>-410.16</v>
       </c>
       <c r="L80" t="n">
-        <v>935.05</v>
+        <v>458.11</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>270.16</v>
+        <v>135.85</v>
       </c>
       <c r="K81" t="n">
-        <v>-310.16</v>
+        <v>-155.97</v>
       </c>
       <c r="L81" t="n">
-        <v>411.33</v>
+        <v>206.84</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>123.7</v>
+        <v>65.56</v>
       </c>
       <c r="K82" t="n">
-        <v>-286.79</v>
+        <v>-151.99</v>
       </c>
       <c r="L82" t="n">
-        <v>312.33</v>
+        <v>165.53</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>-632.7</v>
+        <v>-288.57</v>
       </c>
       <c r="K83" t="n">
-        <v>283.73</v>
+        <v>129.41</v>
       </c>
       <c r="L83" t="n">
-        <v>693.4</v>
+        <v>316.26</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>47.29</v>
+        <v>22.18</v>
       </c>
       <c r="K84" t="n">
-        <v>644.27</v>
+        <v>302.19</v>
       </c>
       <c r="L84" t="n">
-        <v>646.01</v>
+        <v>303</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>819.3200000000001</v>
+        <v>359.99</v>
       </c>
       <c r="K85" t="n">
-        <v>358.68</v>
+        <v>157.6</v>
       </c>
       <c r="L85" t="n">
-        <v>894.39</v>
+        <v>392.98</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>1482.01</v>
+        <v>597.64</v>
       </c>
       <c r="K86" t="n">
-        <v>132.95</v>
+        <v>53.61</v>
       </c>
       <c r="L86" t="n">
-        <v>1487.96</v>
+        <v>600.04</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-991.33</v>
+        <v>-435.88</v>
       </c>
       <c r="K87" t="n">
-        <v>160.24</v>
+        <v>70.45</v>
       </c>
       <c r="L87" t="n">
-        <v>1004.19</v>
+        <v>441.53</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>110.37</v>
+        <v>47.74</v>
       </c>
       <c r="K88" t="n">
-        <v>1802.96</v>
+        <v>779.8</v>
       </c>
       <c r="L88" t="n">
-        <v>1806.34</v>
+        <v>781.26</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-30.xlsx
+++ b/output/2024-04-30.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>-43.92</v>
+        <v>-46.65</v>
       </c>
       <c r="K14" t="n">
-        <v>123.04</v>
+        <v>130.7</v>
       </c>
       <c r="L14" t="n">
-        <v>130.64</v>
+        <v>138.78</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-204.93</v>
+        <v>-218.62</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="L15" t="n">
-        <v>204.93</v>
+        <v>218.62</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-117.06</v>
+        <v>-127.53</v>
       </c>
       <c r="K16" t="n">
-        <v>206.77</v>
+        <v>225.27</v>
       </c>
       <c r="L16" t="n">
-        <v>237.61</v>
+        <v>258.87</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>152.21</v>
+        <v>166.2</v>
       </c>
       <c r="K17" t="n">
-        <v>-54.23</v>
+        <v>-59.22</v>
       </c>
       <c r="L17" t="n">
-        <v>161.58</v>
+        <v>176.44</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-51.56</v>
+        <v>-56.99</v>
       </c>
       <c r="K18" t="n">
-        <v>-146.38</v>
+        <v>-161.81</v>
       </c>
       <c r="L18" t="n">
-        <v>155.2</v>
+        <v>171.56</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>68.23</v>
+        <v>73.55</v>
       </c>
       <c r="K19" t="n">
-        <v>216.94</v>
+        <v>233.88</v>
       </c>
       <c r="L19" t="n">
-        <v>227.42</v>
+        <v>245.17</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>-183.02</v>
+        <v>-207.16</v>
       </c>
       <c r="K20" t="n">
-        <v>-100.4</v>
+        <v>-113.65</v>
       </c>
       <c r="L20" t="n">
-        <v>208.75</v>
+        <v>236.29</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>184.76</v>
+        <v>211.53</v>
       </c>
       <c r="K21" t="n">
-        <v>-324.8</v>
+        <v>-371.87</v>
       </c>
       <c r="L21" t="n">
-        <v>373.68</v>
+        <v>427.83</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-136.82</v>
+        <v>-154.39</v>
       </c>
       <c r="K22" t="n">
-        <v>13.1</v>
+        <v>14.78</v>
       </c>
       <c r="L22" t="n">
-        <v>137.45</v>
+        <v>155.1</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-64.68000000000001</v>
+        <v>-74.94</v>
       </c>
       <c r="K23" t="n">
-        <v>-428.82</v>
+        <v>-496.89</v>
       </c>
       <c r="L23" t="n">
-        <v>433.67</v>
+        <v>502.51</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>221.77</v>
+        <v>259.55</v>
       </c>
       <c r="K24" t="n">
-        <v>567.89</v>
+        <v>664.62</v>
       </c>
       <c r="L24" t="n">
-        <v>609.66</v>
+        <v>713.5</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>288.09</v>
+        <v>331.81</v>
       </c>
       <c r="K25" t="n">
-        <v>-409.29</v>
+        <v>-471.4</v>
       </c>
       <c r="L25" t="n">
-        <v>500.51</v>
+        <v>576.46</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>19.69</v>
+        <v>23.37</v>
       </c>
       <c r="K26" t="n">
-        <v>275.75</v>
+        <v>327.27</v>
       </c>
       <c r="L26" t="n">
-        <v>276.45</v>
+        <v>328.11</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>380.5</v>
+        <v>454.3</v>
       </c>
       <c r="K27" t="n">
-        <v>282.1</v>
+        <v>336.81</v>
       </c>
       <c r="L27" t="n">
-        <v>473.66</v>
+        <v>565.53</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-355.76</v>
+        <v>-426.81</v>
       </c>
       <c r="K28" t="n">
-        <v>-391.32</v>
+        <v>-469.48</v>
       </c>
       <c r="L28" t="n">
-        <v>528.86</v>
+        <v>634.49</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>98.09</v>
+        <v>104.54</v>
       </c>
       <c r="K29" t="n">
-        <v>-76.58</v>
+        <v>-81.61</v>
       </c>
       <c r="L29" t="n">
-        <v>124.44</v>
+        <v>132.62</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>80.44</v>
+        <v>85.77</v>
       </c>
       <c r="K30" t="n">
-        <v>128.29</v>
+        <v>136.79</v>
       </c>
       <c r="L30" t="n">
-        <v>151.43</v>
+        <v>161.45</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>66.65000000000001</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>-61.84</v>
+        <v>-66.39</v>
       </c>
       <c r="L31" t="n">
-        <v>90.92</v>
+        <v>97.59999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-184.61</v>
+        <v>-200.21</v>
       </c>
       <c r="K32" t="n">
-        <v>65.98</v>
+        <v>71.55</v>
       </c>
       <c r="L32" t="n">
-        <v>196.05</v>
+        <v>212.61</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>10.23</v>
+        <v>11.22</v>
       </c>
       <c r="K33" t="n">
-        <v>362.33</v>
+        <v>397.42</v>
       </c>
       <c r="L33" t="n">
-        <v>362.47</v>
+        <v>397.57</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>225.29</v>
+        <v>242.09</v>
       </c>
       <c r="K34" t="n">
-        <v>121.76</v>
+        <v>130.84</v>
       </c>
       <c r="L34" t="n">
-        <v>256.09</v>
+        <v>275.18</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>102.61</v>
+        <v>114.37</v>
       </c>
       <c r="K35" t="n">
-        <v>128.82</v>
+        <v>143.58</v>
       </c>
       <c r="L35" t="n">
-        <v>164.69</v>
+        <v>183.56</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>151.95</v>
+        <v>172.14</v>
       </c>
       <c r="K36" t="n">
-        <v>203.4</v>
+        <v>230.43</v>
       </c>
       <c r="L36" t="n">
-        <v>253.89</v>
+        <v>287.63</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>298.56</v>
+        <v>336.27</v>
       </c>
       <c r="K37" t="n">
-        <v>-246.93</v>
+        <v>-278.12</v>
       </c>
       <c r="L37" t="n">
-        <v>387.44</v>
+        <v>436.38</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-260.83</v>
+        <v>-306.02</v>
       </c>
       <c r="K38" t="n">
-        <v>248.5</v>
+        <v>291.56</v>
       </c>
       <c r="L38" t="n">
-        <v>360.25</v>
+        <v>422.68</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>-153</v>
+        <v>-180.19</v>
       </c>
       <c r="K39" t="n">
-        <v>316.87</v>
+        <v>373.19</v>
       </c>
       <c r="L39" t="n">
-        <v>351.87</v>
+        <v>414.42</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>429.35</v>
+        <v>503.24</v>
       </c>
       <c r="K40" t="n">
-        <v>29.1</v>
+        <v>34.11</v>
       </c>
       <c r="L40" t="n">
-        <v>430.34</v>
+        <v>504.39</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-82.19</v>
+        <v>-98.41</v>
       </c>
       <c r="K41" t="n">
-        <v>365.8</v>
+        <v>437.98</v>
       </c>
       <c r="L41" t="n">
-        <v>374.92</v>
+        <v>448.9</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-323.58</v>
+        <v>-387.41</v>
       </c>
       <c r="K42" t="n">
-        <v>-328.06</v>
+        <v>-392.77</v>
       </c>
       <c r="L42" t="n">
-        <v>460.78</v>
+        <v>551.6799999999999</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>141.27</v>
+        <v>169.04</v>
       </c>
       <c r="K43" t="n">
-        <v>200.85</v>
+        <v>240.32</v>
       </c>
       <c r="L43" t="n">
-        <v>245.56</v>
+        <v>293.82</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>201.64</v>
+        <v>217.91</v>
       </c>
       <c r="K44" t="n">
-        <v>33.51</v>
+        <v>36.21</v>
       </c>
       <c r="L44" t="n">
-        <v>204.41</v>
+        <v>220.9</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>124.16</v>
+        <v>134.39</v>
       </c>
       <c r="K45" t="n">
-        <v>-11.1</v>
+        <v>-12.01</v>
       </c>
       <c r="L45" t="n">
-        <v>124.65</v>
+        <v>134.93</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-242.85</v>
+        <v>-265.17</v>
       </c>
       <c r="K46" t="n">
-        <v>-8.619999999999999</v>
+        <v>-9.41</v>
       </c>
       <c r="L46" t="n">
-        <v>243</v>
+        <v>265.33</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>267.09</v>
+        <v>290.09</v>
       </c>
       <c r="K47" t="n">
-        <v>-75.76000000000001</v>
+        <v>-82.29000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>277.62</v>
+        <v>301.54</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-196.33</v>
+        <v>-218.57</v>
       </c>
       <c r="K48" t="n">
-        <v>18.34</v>
+        <v>20.41</v>
       </c>
       <c r="L48" t="n">
-        <v>197.18</v>
+        <v>219.52</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>221.48</v>
+        <v>245.21</v>
       </c>
       <c r="K49" t="n">
-        <v>-130.31</v>
+        <v>-144.27</v>
       </c>
       <c r="L49" t="n">
-        <v>256.97</v>
+        <v>284.5</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-228.6</v>
+        <v>-258.91</v>
       </c>
       <c r="K50" t="n">
-        <v>-61.75</v>
+        <v>-69.94</v>
       </c>
       <c r="L50" t="n">
-        <v>236.79</v>
+        <v>268.19</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>85.09999999999999</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>302.88</v>
+        <v>344.69</v>
       </c>
       <c r="L51" t="n">
-        <v>314.61</v>
+        <v>358.04</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>29.31</v>
+        <v>33.41</v>
       </c>
       <c r="K52" t="n">
-        <v>233.58</v>
+        <v>266.33</v>
       </c>
       <c r="L52" t="n">
-        <v>235.41</v>
+        <v>268.41</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>314.98</v>
+        <v>368.73</v>
       </c>
       <c r="K53" t="n">
-        <v>-446.01</v>
+        <v>-522.1</v>
       </c>
       <c r="L53" t="n">
-        <v>546.02</v>
+        <v>639.1799999999999</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>-222.22</v>
+        <v>-260.04</v>
       </c>
       <c r="K54" t="n">
-        <v>-77.06</v>
+        <v>-90.18000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>235.2</v>
+        <v>275.24</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>45.2</v>
+        <v>53.19</v>
       </c>
       <c r="K55" t="n">
-        <v>-377.3</v>
+        <v>-443.94</v>
       </c>
       <c r="L55" t="n">
-        <v>380</v>
+        <v>447.12</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>253.87</v>
+        <v>302.32</v>
       </c>
       <c r="K56" t="n">
-        <v>-95.3</v>
+        <v>-113.49</v>
       </c>
       <c r="L56" t="n">
-        <v>271.17</v>
+        <v>322.92</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>389</v>
+        <v>469.31</v>
       </c>
       <c r="K57" t="n">
-        <v>30.36</v>
+        <v>36.63</v>
       </c>
       <c r="L57" t="n">
-        <v>390.19</v>
+        <v>470.74</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-597.66</v>
+        <v>-729.03</v>
       </c>
       <c r="K58" t="n">
-        <v>342.37</v>
+        <v>417.63</v>
       </c>
       <c r="L58" t="n">
-        <v>688.78</v>
+        <v>840.1799999999999</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>88.25</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>154.39</v>
+        <v>169.2</v>
       </c>
       <c r="L59" t="n">
-        <v>177.84</v>
+        <v>194.89</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-124.2</v>
+        <v>-136.37</v>
       </c>
       <c r="K60" t="n">
-        <v>75.13</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>145.16</v>
+        <v>159.38</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.68</v>
+        <v>-1.83</v>
       </c>
       <c r="K61" t="n">
-        <v>189.97</v>
+        <v>207.19</v>
       </c>
       <c r="L61" t="n">
-        <v>189.98</v>
+        <v>207.2</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-47.62</v>
+        <v>-52.51</v>
       </c>
       <c r="K62" t="n">
-        <v>-361.47</v>
+        <v>-398.61</v>
       </c>
       <c r="L62" t="n">
-        <v>364.6</v>
+        <v>402.05</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-166.65</v>
+        <v>-183.09</v>
       </c>
       <c r="K63" t="n">
-        <v>-104.02</v>
+        <v>-114.28</v>
       </c>
       <c r="L63" t="n">
-        <v>196.45</v>
+        <v>215.83</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-171.65</v>
+        <v>-186.35</v>
       </c>
       <c r="K64" t="n">
-        <v>21.45</v>
+        <v>23.29</v>
       </c>
       <c r="L64" t="n">
-        <v>172.99</v>
+        <v>187.8</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-9.18</v>
+        <v>-10.39</v>
       </c>
       <c r="K65" t="n">
-        <v>318.82</v>
+        <v>361.08</v>
       </c>
       <c r="L65" t="n">
-        <v>318.95</v>
+        <v>361.23</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-66.27</v>
+        <v>-75.95999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>-333.22</v>
+        <v>-381.92</v>
       </c>
       <c r="L66" t="n">
-        <v>339.75</v>
+        <v>389.4</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>60.66</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-329.61</v>
+        <v>-374.96</v>
       </c>
       <c r="L67" t="n">
-        <v>335.15</v>
+        <v>381.26</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>123.77</v>
+        <v>145.96</v>
       </c>
       <c r="K68" t="n">
-        <v>-347.15</v>
+        <v>-409.4</v>
       </c>
       <c r="L68" t="n">
-        <v>368.55</v>
+        <v>434.64</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-139.87</v>
+        <v>-163.55</v>
       </c>
       <c r="K69" t="n">
-        <v>219.77</v>
+        <v>256.97</v>
       </c>
       <c r="L69" t="n">
-        <v>260.51</v>
+        <v>304.6</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-337.27</v>
+        <v>-390.76</v>
       </c>
       <c r="K70" t="n">
-        <v>354.54</v>
+        <v>410.76</v>
       </c>
       <c r="L70" t="n">
-        <v>489.34</v>
+        <v>566.9400000000001</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-318.35</v>
+        <v>-375.53</v>
       </c>
       <c r="K71" t="n">
-        <v>124.91</v>
+        <v>147.35</v>
       </c>
       <c r="L71" t="n">
-        <v>341.98</v>
+        <v>403.41</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>96.25</v>
+        <v>113.43</v>
       </c>
       <c r="K72" t="n">
-        <v>-314.38</v>
+        <v>-370.49</v>
       </c>
       <c r="L72" t="n">
-        <v>328.78</v>
+        <v>387.46</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-33.15</v>
+        <v>-40.11</v>
       </c>
       <c r="K73" t="n">
-        <v>-302.12</v>
+        <v>-365.55</v>
       </c>
       <c r="L73" t="n">
-        <v>303.93</v>
+        <v>367.75</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>95.27</v>
+        <v>104.2</v>
       </c>
       <c r="K74" t="n">
-        <v>120.74</v>
+        <v>132.05</v>
       </c>
       <c r="L74" t="n">
-        <v>153.8</v>
+        <v>168.21</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>136.28</v>
+        <v>149.76</v>
       </c>
       <c r="K75" t="n">
-        <v>83.61</v>
+        <v>91.88</v>
       </c>
       <c r="L75" t="n">
-        <v>159.89</v>
+        <v>175.7</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>148.34</v>
+        <v>160.94</v>
       </c>
       <c r="K76" t="n">
-        <v>-117.39</v>
+        <v>-127.36</v>
       </c>
       <c r="L76" t="n">
-        <v>189.17</v>
+        <v>205.24</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>58.39</v>
+        <v>63.91</v>
       </c>
       <c r="K77" t="n">
-        <v>351.67</v>
+        <v>384.93</v>
       </c>
       <c r="L77" t="n">
-        <v>356.49</v>
+        <v>390.2</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-564.3099999999999</v>
+        <v>-604.8</v>
       </c>
       <c r="K78" t="n">
-        <v>82.86</v>
+        <v>88.81</v>
       </c>
       <c r="L78" t="n">
-        <v>570.36</v>
+        <v>611.29</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>83.03</v>
+        <v>89.78</v>
       </c>
       <c r="K79" t="n">
-        <v>252.16</v>
+        <v>272.65</v>
       </c>
       <c r="L79" t="n">
-        <v>265.47</v>
+        <v>287.06</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>204.05</v>
+        <v>232.53</v>
       </c>
       <c r="K80" t="n">
-        <v>-410.16</v>
+        <v>-467.41</v>
       </c>
       <c r="L80" t="n">
-        <v>458.11</v>
+        <v>522.05</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>135.85</v>
+        <v>155.19</v>
       </c>
       <c r="K81" t="n">
-        <v>-155.97</v>
+        <v>-178.17</v>
       </c>
       <c r="L81" t="n">
-        <v>206.84</v>
+        <v>236.27</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>65.56</v>
+        <v>73.84</v>
       </c>
       <c r="K82" t="n">
-        <v>-151.99</v>
+        <v>-171.19</v>
       </c>
       <c r="L82" t="n">
-        <v>165.53</v>
+        <v>186.44</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>-288.57</v>
+        <v>-336.97</v>
       </c>
       <c r="K83" t="n">
-        <v>129.41</v>
+        <v>151.11</v>
       </c>
       <c r="L83" t="n">
-        <v>316.26</v>
+        <v>369.3</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>22.18</v>
+        <v>25.72</v>
       </c>
       <c r="K84" t="n">
-        <v>302.19</v>
+        <v>350.42</v>
       </c>
       <c r="L84" t="n">
-        <v>303</v>
+        <v>351.36</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>359.99</v>
+        <v>422.01</v>
       </c>
       <c r="K85" t="n">
-        <v>157.6</v>
+        <v>184.74</v>
       </c>
       <c r="L85" t="n">
-        <v>392.98</v>
+        <v>460.67</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>597.64</v>
+        <v>721</v>
       </c>
       <c r="K86" t="n">
-        <v>53.61</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="L86" t="n">
-        <v>600.04</v>
+        <v>723.89</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-435.88</v>
+        <v>-517.8099999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>70.45</v>
+        <v>83.7</v>
       </c>
       <c r="L87" t="n">
-        <v>441.53</v>
+        <v>524.53</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>47.74</v>
+        <v>56.41</v>
       </c>
       <c r="K88" t="n">
-        <v>779.8</v>
+        <v>921.47</v>
       </c>
       <c r="L88" t="n">
-        <v>781.26</v>
+        <v>923.1900000000001</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-30.xlsx
+++ b/output/2024-04-30.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>-46.65</v>
+        <v>-20.49</v>
       </c>
       <c r="K14" t="n">
-        <v>130.7</v>
+        <v>57.4</v>
       </c>
       <c r="L14" t="n">
-        <v>138.78</v>
+        <v>60.95</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-218.62</v>
+        <v>-87.09</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.16</v>
+        <v>-0.06</v>
       </c>
       <c r="L15" t="n">
-        <v>218.62</v>
+        <v>87.09</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-127.53</v>
+        <v>-53.85</v>
       </c>
       <c r="K16" t="n">
-        <v>225.27</v>
+        <v>95.12</v>
       </c>
       <c r="L16" t="n">
-        <v>258.87</v>
+        <v>109.3</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>166.2</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-59.22</v>
+        <v>-24.88</v>
       </c>
       <c r="L17" t="n">
-        <v>176.44</v>
+        <v>74.12</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-56.99</v>
+        <v>-26.06</v>
       </c>
       <c r="K18" t="n">
-        <v>-161.81</v>
+        <v>-73.98999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>171.56</v>
+        <v>78.45</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>73.55</v>
+        <v>31.6</v>
       </c>
       <c r="K19" t="n">
-        <v>233.88</v>
+        <v>100.5</v>
       </c>
       <c r="L19" t="n">
-        <v>245.17</v>
+        <v>105.35</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>-207.16</v>
+        <v>-100.58</v>
       </c>
       <c r="K20" t="n">
-        <v>-113.65</v>
+        <v>-55.18</v>
       </c>
       <c r="L20" t="n">
-        <v>236.29</v>
+        <v>114.72</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>211.53</v>
+        <v>102.34</v>
       </c>
       <c r="K21" t="n">
-        <v>-371.87</v>
+        <v>-179.91</v>
       </c>
       <c r="L21" t="n">
-        <v>427.83</v>
+        <v>206.98</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-154.39</v>
+        <v>-51.01</v>
       </c>
       <c r="K22" t="n">
-        <v>14.78</v>
+        <v>4.88</v>
       </c>
       <c r="L22" t="n">
-        <v>155.1</v>
+        <v>51.24</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-74.94</v>
+        <v>-32.83</v>
       </c>
       <c r="K23" t="n">
-        <v>-496.89</v>
+        <v>-217.7</v>
       </c>
       <c r="L23" t="n">
-        <v>502.51</v>
+        <v>220.16</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>259.55</v>
+        <v>114.57</v>
       </c>
       <c r="K24" t="n">
-        <v>664.62</v>
+        <v>293.37</v>
       </c>
       <c r="L24" t="n">
-        <v>713.5</v>
+        <v>314.95</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>331.81</v>
+        <v>148.01</v>
       </c>
       <c r="K25" t="n">
-        <v>-471.4</v>
+        <v>-210.28</v>
       </c>
       <c r="L25" t="n">
-        <v>576.46</v>
+        <v>257.15</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>23.37</v>
+        <v>12.73</v>
       </c>
       <c r="K26" t="n">
-        <v>327.27</v>
+        <v>178.28</v>
       </c>
       <c r="L26" t="n">
-        <v>328.11</v>
+        <v>178.73</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>454.3</v>
+        <v>244.15</v>
       </c>
       <c r="K27" t="n">
-        <v>336.81</v>
+        <v>181.01</v>
       </c>
       <c r="L27" t="n">
-        <v>565.53</v>
+        <v>303.93</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-426.81</v>
+        <v>-228.99</v>
       </c>
       <c r="K28" t="n">
-        <v>-469.48</v>
+        <v>-251.88</v>
       </c>
       <c r="L28" t="n">
-        <v>634.49</v>
+        <v>340.41</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>104.54</v>
+        <v>51.81</v>
       </c>
       <c r="K29" t="n">
-        <v>-81.61</v>
+        <v>-40.45</v>
       </c>
       <c r="L29" t="n">
-        <v>132.62</v>
+        <v>65.73</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>85.77</v>
+        <v>37.82</v>
       </c>
       <c r="K30" t="n">
-        <v>136.79</v>
+        <v>60.31</v>
       </c>
       <c r="L30" t="n">
-        <v>161.45</v>
+        <v>71.19</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>71.54000000000001</v>
+        <v>36.7</v>
       </c>
       <c r="K31" t="n">
-        <v>-66.39</v>
+        <v>-34.06</v>
       </c>
       <c r="L31" t="n">
-        <v>97.59999999999999</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-200.21</v>
+        <v>-83.02</v>
       </c>
       <c r="K32" t="n">
-        <v>71.55</v>
+        <v>29.67</v>
       </c>
       <c r="L32" t="n">
-        <v>212.61</v>
+        <v>88.16</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>11.22</v>
+        <v>5.16</v>
       </c>
       <c r="K33" t="n">
-        <v>397.42</v>
+        <v>182.64</v>
       </c>
       <c r="L33" t="n">
-        <v>397.57</v>
+        <v>182.71</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>242.09</v>
+        <v>100.85</v>
       </c>
       <c r="K34" t="n">
-        <v>130.84</v>
+        <v>54.51</v>
       </c>
       <c r="L34" t="n">
-        <v>275.18</v>
+        <v>114.64</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>114.37</v>
+        <v>56.87</v>
       </c>
       <c r="K35" t="n">
-        <v>143.58</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>183.56</v>
+        <v>91.28</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>172.14</v>
+        <v>85.02</v>
       </c>
       <c r="K36" t="n">
-        <v>230.43</v>
+        <v>113.81</v>
       </c>
       <c r="L36" t="n">
-        <v>287.63</v>
+        <v>142.06</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>336.27</v>
+        <v>164.7</v>
       </c>
       <c r="K37" t="n">
-        <v>-278.12</v>
+        <v>-136.22</v>
       </c>
       <c r="L37" t="n">
-        <v>436.38</v>
+        <v>213.74</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-306.02</v>
+        <v>-135.86</v>
       </c>
       <c r="K38" t="n">
-        <v>291.56</v>
+        <v>129.44</v>
       </c>
       <c r="L38" t="n">
-        <v>422.68</v>
+        <v>187.65</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>-180.19</v>
+        <v>-85.04000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>373.19</v>
+        <v>176.13</v>
       </c>
       <c r="L39" t="n">
-        <v>414.42</v>
+        <v>195.58</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>503.24</v>
+        <v>222.7</v>
       </c>
       <c r="K40" t="n">
-        <v>34.11</v>
+        <v>15.1</v>
       </c>
       <c r="L40" t="n">
-        <v>504.39</v>
+        <v>223.21</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-98.41</v>
+        <v>-52.8</v>
       </c>
       <c r="K41" t="n">
-        <v>437.98</v>
+        <v>234.98</v>
       </c>
       <c r="L41" t="n">
-        <v>448.9</v>
+        <v>240.84</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-387.41</v>
+        <v>-204.98</v>
       </c>
       <c r="K42" t="n">
-        <v>-392.77</v>
+        <v>-207.82</v>
       </c>
       <c r="L42" t="n">
-        <v>551.6799999999999</v>
+        <v>291.9</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>169.04</v>
+        <v>90.09</v>
       </c>
       <c r="K43" t="n">
-        <v>240.32</v>
+        <v>128.08</v>
       </c>
       <c r="L43" t="n">
-        <v>293.82</v>
+        <v>156.59</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>217.91</v>
+        <v>87.62</v>
       </c>
       <c r="K44" t="n">
-        <v>36.21</v>
+        <v>14.56</v>
       </c>
       <c r="L44" t="n">
-        <v>220.9</v>
+        <v>88.81999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>134.39</v>
+        <v>54.33</v>
       </c>
       <c r="K45" t="n">
-        <v>-12.01</v>
+        <v>-4.86</v>
       </c>
       <c r="L45" t="n">
-        <v>134.93</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-265.17</v>
+        <v>-113.62</v>
       </c>
       <c r="K46" t="n">
-        <v>-9.41</v>
+        <v>-4.03</v>
       </c>
       <c r="L46" t="n">
-        <v>265.33</v>
+        <v>113.69</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>290.09</v>
+        <v>126.5</v>
       </c>
       <c r="K47" t="n">
-        <v>-82.29000000000001</v>
+        <v>-35.88</v>
       </c>
       <c r="L47" t="n">
-        <v>301.54</v>
+        <v>131.49</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-218.57</v>
+        <v>-93.03</v>
       </c>
       <c r="K48" t="n">
-        <v>20.41</v>
+        <v>8.69</v>
       </c>
       <c r="L48" t="n">
-        <v>219.52</v>
+        <v>93.43000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>245.21</v>
+        <v>102.74</v>
       </c>
       <c r="K49" t="n">
-        <v>-144.27</v>
+        <v>-60.45</v>
       </c>
       <c r="L49" t="n">
-        <v>284.5</v>
+        <v>119.2</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-258.91</v>
+        <v>-125.82</v>
       </c>
       <c r="K50" t="n">
-        <v>-69.94</v>
+        <v>-33.99</v>
       </c>
       <c r="L50" t="n">
-        <v>268.19</v>
+        <v>130.33</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>96.84999999999999</v>
+        <v>46.3</v>
       </c>
       <c r="K51" t="n">
-        <v>344.69</v>
+        <v>164.78</v>
       </c>
       <c r="L51" t="n">
-        <v>358.04</v>
+        <v>171.16</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>33.41</v>
+        <v>16.62</v>
       </c>
       <c r="K52" t="n">
-        <v>266.33</v>
+        <v>132.44</v>
       </c>
       <c r="L52" t="n">
-        <v>268.41</v>
+        <v>133.48</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>368.73</v>
+        <v>163.93</v>
       </c>
       <c r="K53" t="n">
-        <v>-522.1</v>
+        <v>-232.11</v>
       </c>
       <c r="L53" t="n">
-        <v>639.1799999999999</v>
+        <v>284.16</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>-260.04</v>
+        <v>-114.44</v>
       </c>
       <c r="K54" t="n">
-        <v>-90.18000000000001</v>
+        <v>-39.68</v>
       </c>
       <c r="L54" t="n">
-        <v>275.24</v>
+        <v>121.12</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>53.19</v>
+        <v>23.48</v>
       </c>
       <c r="K55" t="n">
-        <v>-443.94</v>
+        <v>-195.96</v>
       </c>
       <c r="L55" t="n">
-        <v>447.12</v>
+        <v>197.36</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>302.32</v>
+        <v>161.69</v>
       </c>
       <c r="K56" t="n">
-        <v>-113.49</v>
+        <v>-60.7</v>
       </c>
       <c r="L56" t="n">
-        <v>322.92</v>
+        <v>172.71</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>469.31</v>
+        <v>254.35</v>
       </c>
       <c r="K57" t="n">
-        <v>36.63</v>
+        <v>19.85</v>
       </c>
       <c r="L57" t="n">
-        <v>470.74</v>
+        <v>255.12</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-729.03</v>
+        <v>-386.84</v>
       </c>
       <c r="K58" t="n">
-        <v>417.63</v>
+        <v>221.61</v>
       </c>
       <c r="L58" t="n">
-        <v>840.1799999999999</v>
+        <v>445.82</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>96.70999999999999</v>
+        <v>38.66</v>
       </c>
       <c r="K59" t="n">
-        <v>169.2</v>
+        <v>67.63</v>
       </c>
       <c r="L59" t="n">
-        <v>194.89</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-136.37</v>
+        <v>-54.95</v>
       </c>
       <c r="K60" t="n">
-        <v>82.48999999999999</v>
+        <v>33.24</v>
       </c>
       <c r="L60" t="n">
-        <v>159.38</v>
+        <v>64.22</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.83</v>
+        <v>-0.79</v>
       </c>
       <c r="K61" t="n">
-        <v>207.19</v>
+        <v>89.28</v>
       </c>
       <c r="L61" t="n">
-        <v>207.2</v>
+        <v>89.28</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-52.51</v>
+        <v>-22.13</v>
       </c>
       <c r="K62" t="n">
-        <v>-398.61</v>
+        <v>-167.99</v>
       </c>
       <c r="L62" t="n">
-        <v>402.05</v>
+        <v>169.44</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-183.09</v>
+        <v>-76.5</v>
       </c>
       <c r="K63" t="n">
-        <v>-114.28</v>
+        <v>-47.75</v>
       </c>
       <c r="L63" t="n">
-        <v>215.83</v>
+        <v>90.18000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-186.35</v>
+        <v>-89.68000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>23.29</v>
+        <v>11.21</v>
       </c>
       <c r="L64" t="n">
-        <v>187.8</v>
+        <v>90.38</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.39</v>
+        <v>-4.96</v>
       </c>
       <c r="K65" t="n">
-        <v>361.08</v>
+        <v>172.46</v>
       </c>
       <c r="L65" t="n">
-        <v>361.23</v>
+        <v>172.53</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-75.95999999999999</v>
+        <v>-36.29</v>
       </c>
       <c r="K66" t="n">
-        <v>-381.92</v>
+        <v>-182.49</v>
       </c>
       <c r="L66" t="n">
-        <v>389.4</v>
+        <v>186.07</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>69.01000000000001</v>
+        <v>33.02</v>
       </c>
       <c r="K67" t="n">
-        <v>-374.96</v>
+        <v>-179.44</v>
       </c>
       <c r="L67" t="n">
-        <v>381.26</v>
+        <v>182.45</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>145.96</v>
+        <v>66.72</v>
       </c>
       <c r="K68" t="n">
-        <v>-409.4</v>
+        <v>-187.15</v>
       </c>
       <c r="L68" t="n">
-        <v>434.64</v>
+        <v>198.69</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-163.55</v>
+        <v>-71.42</v>
       </c>
       <c r="K69" t="n">
-        <v>256.97</v>
+        <v>112.23</v>
       </c>
       <c r="L69" t="n">
-        <v>304.6</v>
+        <v>133.03</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-390.76</v>
+        <v>-174.87</v>
       </c>
       <c r="K70" t="n">
-        <v>410.76</v>
+        <v>183.82</v>
       </c>
       <c r="L70" t="n">
-        <v>566.9400000000001</v>
+        <v>253.71</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-375.53</v>
+        <v>-205.49</v>
       </c>
       <c r="K71" t="n">
-        <v>147.35</v>
+        <v>80.63</v>
       </c>
       <c r="L71" t="n">
-        <v>403.41</v>
+        <v>220.75</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>113.43</v>
+        <v>60.89</v>
       </c>
       <c r="K72" t="n">
-        <v>-370.49</v>
+        <v>-198.89</v>
       </c>
       <c r="L72" t="n">
-        <v>387.46</v>
+        <v>208</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-40.11</v>
+        <v>-21.37</v>
       </c>
       <c r="K73" t="n">
-        <v>-365.55</v>
+        <v>-194.75</v>
       </c>
       <c r="L73" t="n">
-        <v>367.75</v>
+        <v>195.92</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>104.2</v>
+        <v>41.86</v>
       </c>
       <c r="K74" t="n">
-        <v>132.05</v>
+        <v>53.05</v>
       </c>
       <c r="L74" t="n">
-        <v>168.21</v>
+        <v>67.58</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>149.76</v>
+        <v>59.9</v>
       </c>
       <c r="K75" t="n">
-        <v>91.88</v>
+        <v>36.75</v>
       </c>
       <c r="L75" t="n">
-        <v>175.7</v>
+        <v>70.28</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>160.94</v>
+        <v>64.12</v>
       </c>
       <c r="K76" t="n">
-        <v>-127.36</v>
+        <v>-50.74</v>
       </c>
       <c r="L76" t="n">
-        <v>205.24</v>
+        <v>81.76000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>63.91</v>
+        <v>26.92</v>
       </c>
       <c r="K77" t="n">
-        <v>384.93</v>
+        <v>162.16</v>
       </c>
       <c r="L77" t="n">
-        <v>390.2</v>
+        <v>164.38</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-604.8</v>
+        <v>-253.84</v>
       </c>
       <c r="K78" t="n">
-        <v>88.81</v>
+        <v>37.27</v>
       </c>
       <c r="L78" t="n">
-        <v>611.29</v>
+        <v>256.56</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>89.78</v>
+        <v>38.74</v>
       </c>
       <c r="K79" t="n">
-        <v>272.65</v>
+        <v>117.64</v>
       </c>
       <c r="L79" t="n">
-        <v>287.06</v>
+        <v>123.85</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>232.53</v>
+        <v>111.1</v>
       </c>
       <c r="K80" t="n">
-        <v>-467.41</v>
+        <v>-223.33</v>
       </c>
       <c r="L80" t="n">
-        <v>522.05</v>
+        <v>249.43</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>155.19</v>
+        <v>75.48</v>
       </c>
       <c r="K81" t="n">
-        <v>-178.17</v>
+        <v>-86.66</v>
       </c>
       <c r="L81" t="n">
-        <v>236.27</v>
+        <v>114.92</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>73.84</v>
+        <v>35.26</v>
       </c>
       <c r="K82" t="n">
-        <v>-171.19</v>
+        <v>-81.73999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>186.44</v>
+        <v>89.02</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>-336.97</v>
+        <v>-149.9</v>
       </c>
       <c r="K83" t="n">
-        <v>151.11</v>
+        <v>67.22</v>
       </c>
       <c r="L83" t="n">
-        <v>369.3</v>
+        <v>164.28</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>25.72</v>
+        <v>11.37</v>
       </c>
       <c r="K84" t="n">
-        <v>350.42</v>
+        <v>154.96</v>
       </c>
       <c r="L84" t="n">
-        <v>351.36</v>
+        <v>155.38</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>422.01</v>
+        <v>183.69</v>
       </c>
       <c r="K85" t="n">
-        <v>184.74</v>
+        <v>80.42</v>
       </c>
       <c r="L85" t="n">
-        <v>460.67</v>
+        <v>200.53</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>721</v>
+        <v>382.43</v>
       </c>
       <c r="K86" t="n">
-        <v>64.68000000000001</v>
+        <v>34.31</v>
       </c>
       <c r="L86" t="n">
-        <v>723.89</v>
+        <v>383.97</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-517.8099999999999</v>
+        <v>-274.17</v>
       </c>
       <c r="K87" t="n">
-        <v>83.7</v>
+        <v>44.32</v>
       </c>
       <c r="L87" t="n">
-        <v>524.53</v>
+        <v>277.73</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>56.41</v>
+        <v>30.47</v>
       </c>
       <c r="K88" t="n">
-        <v>921.47</v>
+        <v>497.72</v>
       </c>
       <c r="L88" t="n">
-        <v>923.1900000000001</v>
+        <v>498.65</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-30.xlsx
+++ b/output/2024-04-30.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>-20.49</v>
+        <v>-20.64</v>
       </c>
       <c r="K14" t="n">
-        <v>57.4</v>
+        <v>57.83</v>
       </c>
       <c r="L14" t="n">
-        <v>60.95</v>
+        <v>61.41</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-87.09</v>
+        <v>-82.73</v>
       </c>
       <c r="K15" t="n">
         <v>-0.06</v>
       </c>
       <c r="L15" t="n">
-        <v>87.09</v>
+        <v>82.73</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-53.85</v>
+        <v>-50.62</v>
       </c>
       <c r="K16" t="n">
-        <v>95.12</v>
+        <v>89.42</v>
       </c>
       <c r="L16" t="n">
-        <v>109.3</v>
+        <v>102.75</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>69.81999999999999</v>
+        <v>70.53</v>
       </c>
       <c r="K17" t="n">
-        <v>-24.88</v>
+        <v>-25.13</v>
       </c>
       <c r="L17" t="n">
-        <v>74.12</v>
+        <v>74.87</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-26.06</v>
+        <v>-26.3</v>
       </c>
       <c r="K18" t="n">
-        <v>-73.98999999999999</v>
+        <v>-74.66</v>
       </c>
       <c r="L18" t="n">
-        <v>78.45</v>
+        <v>79.16</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>31.6</v>
+        <v>30.17</v>
       </c>
       <c r="K19" t="n">
-        <v>100.5</v>
+        <v>95.92</v>
       </c>
       <c r="L19" t="n">
-        <v>105.35</v>
+        <v>100.55</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>-100.58</v>
+        <v>-103.19</v>
       </c>
       <c r="K20" t="n">
-        <v>-55.18</v>
+        <v>-56.61</v>
       </c>
       <c r="L20" t="n">
-        <v>114.72</v>
+        <v>117.7</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>102.34</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-179.91</v>
+        <v>-172.31</v>
       </c>
       <c r="L21" t="n">
-        <v>206.98</v>
+        <v>198.23</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-51.01</v>
+        <v>-49.3</v>
       </c>
       <c r="K22" t="n">
-        <v>4.88</v>
+        <v>4.72</v>
       </c>
       <c r="L22" t="n">
-        <v>51.24</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-32.83</v>
+        <v>-34.37</v>
       </c>
       <c r="K23" t="n">
-        <v>-217.7</v>
+        <v>-227.88</v>
       </c>
       <c r="L23" t="n">
-        <v>220.16</v>
+        <v>230.46</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>114.57</v>
+        <v>117.04</v>
       </c>
       <c r="K24" t="n">
-        <v>293.37</v>
+        <v>299.69</v>
       </c>
       <c r="L24" t="n">
-        <v>314.95</v>
+        <v>321.73</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>148.01</v>
+        <v>145.98</v>
       </c>
       <c r="K25" t="n">
-        <v>-210.28</v>
+        <v>-207.4</v>
       </c>
       <c r="L25" t="n">
-        <v>257.15</v>
+        <v>253.62</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>12.73</v>
+        <v>13.99</v>
       </c>
       <c r="K26" t="n">
-        <v>178.28</v>
+        <v>195.95</v>
       </c>
       <c r="L26" t="n">
-        <v>178.73</v>
+        <v>196.45</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>244.15</v>
+        <v>254.28</v>
       </c>
       <c r="K27" t="n">
-        <v>181.01</v>
+        <v>188.53</v>
       </c>
       <c r="L27" t="n">
-        <v>303.93</v>
+        <v>316.55</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-228.99</v>
+        <v>-237.5</v>
       </c>
       <c r="K28" t="n">
-        <v>-251.88</v>
+        <v>-261.24</v>
       </c>
       <c r="L28" t="n">
-        <v>340.41</v>
+        <v>353.06</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>51.81</v>
+        <v>52.36</v>
       </c>
       <c r="K29" t="n">
-        <v>-40.45</v>
+        <v>-40.88</v>
       </c>
       <c r="L29" t="n">
-        <v>65.73</v>
+        <v>66.43000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>37.82</v>
+        <v>37.14</v>
       </c>
       <c r="K30" t="n">
-        <v>60.31</v>
+        <v>59.23</v>
       </c>
       <c r="L30" t="n">
-        <v>71.19</v>
+        <v>69.91</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>36.7</v>
+        <v>38.92</v>
       </c>
       <c r="K31" t="n">
-        <v>-34.06</v>
+        <v>-36.11</v>
       </c>
       <c r="L31" t="n">
-        <v>50.07</v>
+        <v>53.09</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-83.02</v>
+        <v>-80.51000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>29.67</v>
+        <v>28.77</v>
       </c>
       <c r="L32" t="n">
-        <v>88.16</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>5.16</v>
+        <v>4.73</v>
       </c>
       <c r="K33" t="n">
-        <v>182.64</v>
+        <v>167.66</v>
       </c>
       <c r="L33" t="n">
-        <v>182.71</v>
+        <v>167.73</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>100.85</v>
+        <v>92.83</v>
       </c>
       <c r="K34" t="n">
-        <v>54.51</v>
+        <v>50.17</v>
       </c>
       <c r="L34" t="n">
-        <v>114.64</v>
+        <v>105.52</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>56.87</v>
+        <v>59.1</v>
       </c>
       <c r="K35" t="n">
-        <v>71.40000000000001</v>
+        <v>74.19</v>
       </c>
       <c r="L35" t="n">
-        <v>91.28</v>
+        <v>94.86</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>85.02</v>
+        <v>84.02</v>
       </c>
       <c r="K36" t="n">
-        <v>113.81</v>
+        <v>112.47</v>
       </c>
       <c r="L36" t="n">
-        <v>142.06</v>
+        <v>140.39</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>164.7</v>
+        <v>156.07</v>
       </c>
       <c r="K37" t="n">
-        <v>-136.22</v>
+        <v>-129.08</v>
       </c>
       <c r="L37" t="n">
-        <v>213.74</v>
+        <v>202.53</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-135.86</v>
+        <v>-139.53</v>
       </c>
       <c r="K38" t="n">
-        <v>129.44</v>
+        <v>132.94</v>
       </c>
       <c r="L38" t="n">
-        <v>187.65</v>
+        <v>192.72</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>-85.04000000000001</v>
+        <v>-97.16</v>
       </c>
       <c r="K39" t="n">
-        <v>176.13</v>
+        <v>201.23</v>
       </c>
       <c r="L39" t="n">
-        <v>195.58</v>
+        <v>223.46</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>222.7</v>
+        <v>225.96</v>
       </c>
       <c r="K40" t="n">
-        <v>15.1</v>
+        <v>15.32</v>
       </c>
       <c r="L40" t="n">
-        <v>223.21</v>
+        <v>226.48</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-52.8</v>
+        <v>-56.76</v>
       </c>
       <c r="K41" t="n">
-        <v>234.98</v>
+        <v>252.62</v>
       </c>
       <c r="L41" t="n">
-        <v>240.84</v>
+        <v>258.92</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-204.98</v>
+        <v>-231.91</v>
       </c>
       <c r="K42" t="n">
-        <v>-207.82</v>
+        <v>-235.12</v>
       </c>
       <c r="L42" t="n">
-        <v>291.9</v>
+        <v>330.25</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>90.09</v>
+        <v>106.82</v>
       </c>
       <c r="K43" t="n">
-        <v>128.08</v>
+        <v>151.87</v>
       </c>
       <c r="L43" t="n">
-        <v>156.59</v>
+        <v>185.67</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>87.62</v>
+        <v>75.75</v>
       </c>
       <c r="K44" t="n">
-        <v>14.56</v>
+        <v>12.59</v>
       </c>
       <c r="L44" t="n">
-        <v>88.81999999999999</v>
+        <v>76.79000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>54.33</v>
+        <v>55.59</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.86</v>
+        <v>-4.97</v>
       </c>
       <c r="L45" t="n">
-        <v>54.55</v>
+        <v>55.81</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-113.62</v>
+        <v>-106.62</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.03</v>
+        <v>-3.78</v>
       </c>
       <c r="L46" t="n">
-        <v>113.69</v>
+        <v>106.69</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>126.5</v>
+        <v>118.28</v>
       </c>
       <c r="K47" t="n">
-        <v>-35.88</v>
+        <v>-33.55</v>
       </c>
       <c r="L47" t="n">
-        <v>131.49</v>
+        <v>122.95</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-93.03</v>
+        <v>-82.95999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>8.69</v>
+        <v>7.75</v>
       </c>
       <c r="L48" t="n">
-        <v>93.43000000000001</v>
+        <v>83.31999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>102.74</v>
+        <v>93.48999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>-60.45</v>
+        <v>-55.01</v>
       </c>
       <c r="L49" t="n">
-        <v>119.2</v>
+        <v>108.47</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-125.82</v>
+        <v>-125.73</v>
       </c>
       <c r="K50" t="n">
-        <v>-33.99</v>
+        <v>-33.96</v>
       </c>
       <c r="L50" t="n">
-        <v>130.33</v>
+        <v>130.24</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>46.3</v>
+        <v>45.37</v>
       </c>
       <c r="K51" t="n">
-        <v>164.78</v>
+        <v>161.48</v>
       </c>
       <c r="L51" t="n">
-        <v>171.16</v>
+        <v>167.73</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>16.62</v>
+        <v>16.6</v>
       </c>
       <c r="K52" t="n">
-        <v>132.44</v>
+        <v>132.33</v>
       </c>
       <c r="L52" t="n">
-        <v>133.48</v>
+        <v>133.37</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>163.93</v>
+        <v>169.27</v>
       </c>
       <c r="K53" t="n">
-        <v>-232.11</v>
+        <v>-239.69</v>
       </c>
       <c r="L53" t="n">
-        <v>284.16</v>
+        <v>293.43</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>-114.44</v>
+        <v>-131.84</v>
       </c>
       <c r="K54" t="n">
-        <v>-39.68</v>
+        <v>-45.72</v>
       </c>
       <c r="L54" t="n">
-        <v>121.12</v>
+        <v>139.54</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>23.48</v>
+        <v>25.19</v>
       </c>
       <c r="K55" t="n">
-        <v>-195.96</v>
+        <v>-210.23</v>
       </c>
       <c r="L55" t="n">
-        <v>197.36</v>
+        <v>211.73</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>161.69</v>
+        <v>195.76</v>
       </c>
       <c r="K56" t="n">
-        <v>-60.7</v>
+        <v>-73.48</v>
       </c>
       <c r="L56" t="n">
-        <v>172.71</v>
+        <v>209.1</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>254.35</v>
+        <v>268.27</v>
       </c>
       <c r="K57" t="n">
-        <v>19.85</v>
+        <v>20.94</v>
       </c>
       <c r="L57" t="n">
-        <v>255.12</v>
+        <v>269.09</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-386.84</v>
+        <v>-409.72</v>
       </c>
       <c r="K58" t="n">
-        <v>221.61</v>
+        <v>234.71</v>
       </c>
       <c r="L58" t="n">
-        <v>445.82</v>
+        <v>472.19</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>38.66</v>
+        <v>35.7</v>
       </c>
       <c r="K59" t="n">
-        <v>67.63</v>
+        <v>62.46</v>
       </c>
       <c r="L59" t="n">
-        <v>77.90000000000001</v>
+        <v>71.94</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-54.95</v>
+        <v>-49.14</v>
       </c>
       <c r="K60" t="n">
-        <v>33.24</v>
+        <v>29.72</v>
       </c>
       <c r="L60" t="n">
-        <v>64.22</v>
+        <v>57.43</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.79</v>
+        <v>-0.76</v>
       </c>
       <c r="K61" t="n">
-        <v>89.28</v>
+        <v>85.77</v>
       </c>
       <c r="L61" t="n">
-        <v>89.28</v>
+        <v>85.77</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-22.13</v>
+        <v>-18.93</v>
       </c>
       <c r="K62" t="n">
-        <v>-167.99</v>
+        <v>-143.69</v>
       </c>
       <c r="L62" t="n">
-        <v>169.44</v>
+        <v>144.93</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-76.5</v>
+        <v>-74.59999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-47.75</v>
+        <v>-46.57</v>
       </c>
       <c r="L63" t="n">
-        <v>90.18000000000001</v>
+        <v>87.94</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-89.68000000000001</v>
+        <v>-87.97</v>
       </c>
       <c r="K64" t="n">
-        <v>11.21</v>
+        <v>10.99</v>
       </c>
       <c r="L64" t="n">
-        <v>90.38</v>
+        <v>88.65000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.96</v>
+        <v>-4.82</v>
       </c>
       <c r="K65" t="n">
-        <v>172.46</v>
+        <v>167.52</v>
       </c>
       <c r="L65" t="n">
-        <v>172.53</v>
+        <v>167.59</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-36.29</v>
+        <v>-35.07</v>
       </c>
       <c r="K66" t="n">
-        <v>-182.49</v>
+        <v>-176.32</v>
       </c>
       <c r="L66" t="n">
-        <v>186.07</v>
+        <v>179.78</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>33.02</v>
+        <v>32.19</v>
       </c>
       <c r="K67" t="n">
-        <v>-179.44</v>
+        <v>-174.93</v>
       </c>
       <c r="L67" t="n">
-        <v>182.45</v>
+        <v>177.87</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>66.72</v>
+        <v>66.97</v>
       </c>
       <c r="K68" t="n">
-        <v>-187.15</v>
+        <v>-187.85</v>
       </c>
       <c r="L68" t="n">
-        <v>198.69</v>
+        <v>199.43</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-71.42</v>
+        <v>-79.52</v>
       </c>
       <c r="K69" t="n">
-        <v>112.23</v>
+        <v>124.95</v>
       </c>
       <c r="L69" t="n">
-        <v>133.03</v>
+        <v>148.11</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-174.87</v>
+        <v>-171.39</v>
       </c>
       <c r="K70" t="n">
-        <v>183.82</v>
+        <v>180.16</v>
       </c>
       <c r="L70" t="n">
-        <v>253.71</v>
+        <v>248.66</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-205.49</v>
+        <v>-262.38</v>
       </c>
       <c r="K71" t="n">
-        <v>80.63</v>
+        <v>102.95</v>
       </c>
       <c r="L71" t="n">
-        <v>220.75</v>
+        <v>281.85</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>60.89</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>-198.89</v>
+        <v>-243</v>
       </c>
       <c r="L72" t="n">
-        <v>208</v>
+        <v>254.13</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-21.37</v>
+        <v>-24.51</v>
       </c>
       <c r="K73" t="n">
-        <v>-194.75</v>
+        <v>-223.36</v>
       </c>
       <c r="L73" t="n">
-        <v>195.92</v>
+        <v>224.7</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>41.86</v>
+        <v>38.13</v>
       </c>
       <c r="K74" t="n">
-        <v>53.05</v>
+        <v>48.33</v>
       </c>
       <c r="L74" t="n">
-        <v>67.58</v>
+        <v>61.56</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>59.9</v>
+        <v>55.99</v>
       </c>
       <c r="K75" t="n">
-        <v>36.75</v>
+        <v>34.35</v>
       </c>
       <c r="L75" t="n">
-        <v>70.28</v>
+        <v>65.68000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>64.12</v>
+        <v>60.02</v>
       </c>
       <c r="K76" t="n">
-        <v>-50.74</v>
+        <v>-47.5</v>
       </c>
       <c r="L76" t="n">
-        <v>81.76000000000001</v>
+        <v>76.54000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>26.92</v>
+        <v>24.65</v>
       </c>
       <c r="K77" t="n">
-        <v>162.16</v>
+        <v>148.47</v>
       </c>
       <c r="L77" t="n">
-        <v>164.38</v>
+        <v>150.5</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-253.84</v>
+        <v>-213.73</v>
       </c>
       <c r="K78" t="n">
-        <v>37.27</v>
+        <v>31.38</v>
       </c>
       <c r="L78" t="n">
-        <v>256.56</v>
+        <v>216.02</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>38.74</v>
+        <v>32.65</v>
       </c>
       <c r="K79" t="n">
-        <v>117.64</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>123.85</v>
+        <v>104.39</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>111.1</v>
+        <v>104.25</v>
       </c>
       <c r="K80" t="n">
-        <v>-223.33</v>
+        <v>-209.55</v>
       </c>
       <c r="L80" t="n">
-        <v>249.43</v>
+        <v>234.05</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>75.48</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>-86.66</v>
+        <v>-88.73999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>114.92</v>
+        <v>117.68</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>35.26</v>
+        <v>37.61</v>
       </c>
       <c r="K82" t="n">
-        <v>-81.73999999999999</v>
+        <v>-87.20999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>89.02</v>
+        <v>94.97</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>-149.9</v>
+        <v>-164.99</v>
       </c>
       <c r="K83" t="n">
-        <v>67.22</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>164.28</v>
+        <v>180.82</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>11.37</v>
+        <v>12.51</v>
       </c>
       <c r="K84" t="n">
-        <v>154.96</v>
+        <v>170.47</v>
       </c>
       <c r="L84" t="n">
-        <v>155.38</v>
+        <v>170.92</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>183.69</v>
+        <v>193.83</v>
       </c>
       <c r="K85" t="n">
-        <v>80.42</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>200.53</v>
+        <v>211.59</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>382.43</v>
+        <v>410.16</v>
       </c>
       <c r="K86" t="n">
-        <v>34.31</v>
+        <v>36.79</v>
       </c>
       <c r="L86" t="n">
-        <v>383.97</v>
+        <v>411.81</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-274.17</v>
+        <v>-310.72</v>
       </c>
       <c r="K87" t="n">
-        <v>44.32</v>
+        <v>50.23</v>
       </c>
       <c r="L87" t="n">
-        <v>277.73</v>
+        <v>314.76</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>30.47</v>
+        <v>33.91</v>
       </c>
       <c r="K88" t="n">
-        <v>497.72</v>
+        <v>553.88</v>
       </c>
       <c r="L88" t="n">
-        <v>498.65</v>
+        <v>554.91</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-30.xlsx
+++ b/output/2024-04-30.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>-20.64</v>
+        <v>-21.43</v>
       </c>
       <c r="K14" t="n">
-        <v>57.83</v>
+        <v>60.03</v>
       </c>
       <c r="L14" t="n">
-        <v>61.41</v>
+        <v>63.74</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-82.73</v>
+        <v>-81.73999999999999</v>
       </c>
       <c r="K15" t="n">
         <v>-0.06</v>
       </c>
       <c r="L15" t="n">
-        <v>82.73</v>
+        <v>81.73999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-50.62</v>
+        <v>-48.89</v>
       </c>
       <c r="K16" t="n">
-        <v>89.42</v>
+        <v>86.37</v>
       </c>
       <c r="L16" t="n">
-        <v>102.75</v>
+        <v>99.23999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>70.53</v>
+        <v>74.3</v>
       </c>
       <c r="K17" t="n">
-        <v>-25.13</v>
+        <v>-26.47</v>
       </c>
       <c r="L17" t="n">
-        <v>74.87</v>
+        <v>78.88</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-26.3</v>
+        <v>-27.27</v>
       </c>
       <c r="K18" t="n">
-        <v>-74.66</v>
+        <v>-77.44</v>
       </c>
       <c r="L18" t="n">
-        <v>79.16</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>30.17</v>
+        <v>29.75</v>
       </c>
       <c r="K19" t="n">
-        <v>95.92</v>
+        <v>94.59</v>
       </c>
       <c r="L19" t="n">
-        <v>100.55</v>
+        <v>99.15000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>-103.19</v>
+        <v>-107.4</v>
       </c>
       <c r="K20" t="n">
-        <v>-56.61</v>
+        <v>-58.92</v>
       </c>
       <c r="L20" t="n">
-        <v>117.7</v>
+        <v>122.5</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>98.01000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-172.31</v>
+        <v>-165.96</v>
       </c>
       <c r="L21" t="n">
-        <v>198.23</v>
+        <v>190.93</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-49.3</v>
+        <v>-53.71</v>
       </c>
       <c r="K22" t="n">
-        <v>4.72</v>
+        <v>5.14</v>
       </c>
       <c r="L22" t="n">
-        <v>49.53</v>
+        <v>53.95</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-34.37</v>
+        <v>-34.01</v>
       </c>
       <c r="K23" t="n">
-        <v>-227.88</v>
+        <v>-225.5</v>
       </c>
       <c r="L23" t="n">
-        <v>230.46</v>
+        <v>228.05</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>117.04</v>
+        <v>112.11</v>
       </c>
       <c r="K24" t="n">
-        <v>299.69</v>
+        <v>287.07</v>
       </c>
       <c r="L24" t="n">
-        <v>321.73</v>
+        <v>308.18</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>145.98</v>
+        <v>140.67</v>
       </c>
       <c r="K25" t="n">
-        <v>-207.4</v>
+        <v>-199.85</v>
       </c>
       <c r="L25" t="n">
-        <v>253.62</v>
+        <v>244.4</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>13.99</v>
+        <v>14.9</v>
       </c>
       <c r="K26" t="n">
-        <v>195.95</v>
+        <v>208.7</v>
       </c>
       <c r="L26" t="n">
-        <v>196.45</v>
+        <v>209.23</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>254.28</v>
+        <v>252.2</v>
       </c>
       <c r="K27" t="n">
-        <v>188.53</v>
+        <v>186.98</v>
       </c>
       <c r="L27" t="n">
-        <v>316.55</v>
+        <v>313.95</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-237.5</v>
+        <v>-233.96</v>
       </c>
       <c r="K28" t="n">
-        <v>-261.24</v>
+        <v>-257.35</v>
       </c>
       <c r="L28" t="n">
-        <v>353.06</v>
+        <v>347.8</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>52.36</v>
+        <v>53.64</v>
       </c>
       <c r="K29" t="n">
-        <v>-40.88</v>
+        <v>-41.88</v>
       </c>
       <c r="L29" t="n">
-        <v>66.43000000000001</v>
+        <v>68.05</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>37.14</v>
+        <v>37.47</v>
       </c>
       <c r="K30" t="n">
-        <v>59.23</v>
+        <v>59.77</v>
       </c>
       <c r="L30" t="n">
-        <v>69.91</v>
+        <v>70.54000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>38.92</v>
+        <v>41.73</v>
       </c>
       <c r="K31" t="n">
-        <v>-36.11</v>
+        <v>-38.73</v>
       </c>
       <c r="L31" t="n">
-        <v>53.09</v>
+        <v>56.94</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-80.51000000000001</v>
+        <v>-81.59</v>
       </c>
       <c r="K32" t="n">
-        <v>28.77</v>
+        <v>29.16</v>
       </c>
       <c r="L32" t="n">
-        <v>85.5</v>
+        <v>86.64</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>4.73</v>
+        <v>4.39</v>
       </c>
       <c r="K33" t="n">
-        <v>167.66</v>
+        <v>155.42</v>
       </c>
       <c r="L33" t="n">
-        <v>167.73</v>
+        <v>155.48</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>92.83</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>50.17</v>
+        <v>48.92</v>
       </c>
       <c r="L34" t="n">
-        <v>105.52</v>
+        <v>102.89</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>59.1</v>
+        <v>62.05</v>
       </c>
       <c r="K35" t="n">
-        <v>74.19</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>94.86</v>
+        <v>99.59</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>84.02</v>
+        <v>83.61</v>
       </c>
       <c r="K36" t="n">
-        <v>112.47</v>
+        <v>111.92</v>
       </c>
       <c r="L36" t="n">
-        <v>140.39</v>
+        <v>139.7</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>156.07</v>
+        <v>147.92</v>
       </c>
       <c r="K37" t="n">
-        <v>-129.08</v>
+        <v>-122.34</v>
       </c>
       <c r="L37" t="n">
-        <v>202.53</v>
+        <v>191.95</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-139.53</v>
+        <v>-139.97</v>
       </c>
       <c r="K38" t="n">
-        <v>132.94</v>
+        <v>133.35</v>
       </c>
       <c r="L38" t="n">
-        <v>192.72</v>
+        <v>193.33</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>-97.16</v>
+        <v>-103.25</v>
       </c>
       <c r="K39" t="n">
-        <v>201.23</v>
+        <v>213.84</v>
       </c>
       <c r="L39" t="n">
-        <v>223.46</v>
+        <v>237.46</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>225.96</v>
+        <v>222.32</v>
       </c>
       <c r="K40" t="n">
-        <v>15.32</v>
+        <v>15.07</v>
       </c>
       <c r="L40" t="n">
-        <v>226.48</v>
+        <v>222.83</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-56.76</v>
+        <v>-58.27</v>
       </c>
       <c r="K41" t="n">
-        <v>252.62</v>
+        <v>259.35</v>
       </c>
       <c r="L41" t="n">
-        <v>258.92</v>
+        <v>265.81</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-231.91</v>
+        <v>-234.5</v>
       </c>
       <c r="K42" t="n">
-        <v>-235.12</v>
+        <v>-237.75</v>
       </c>
       <c r="L42" t="n">
-        <v>330.25</v>
+        <v>333.94</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>106.82</v>
+        <v>118.2</v>
       </c>
       <c r="K43" t="n">
-        <v>151.87</v>
+        <v>168.05</v>
       </c>
       <c r="L43" t="n">
-        <v>185.67</v>
+        <v>205.46</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>75.75</v>
+        <v>76.03</v>
       </c>
       <c r="K44" t="n">
-        <v>12.59</v>
+        <v>12.63</v>
       </c>
       <c r="L44" t="n">
-        <v>76.79000000000001</v>
+        <v>77.06999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>55.59</v>
+        <v>59.34</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.97</v>
+        <v>-5.31</v>
       </c>
       <c r="L45" t="n">
-        <v>55.81</v>
+        <v>59.58</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-106.62</v>
+        <v>-102.5</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.78</v>
+        <v>-3.64</v>
       </c>
       <c r="L46" t="n">
-        <v>106.69</v>
+        <v>102.56</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>118.28</v>
+        <v>113.46</v>
       </c>
       <c r="K47" t="n">
-        <v>-33.55</v>
+        <v>-32.18</v>
       </c>
       <c r="L47" t="n">
-        <v>122.95</v>
+        <v>117.93</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-82.95999999999999</v>
+        <v>-86.23999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>7.75</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>83.31999999999999</v>
+        <v>86.62</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>93.48999999999999</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-55.01</v>
+        <v>-54.38</v>
       </c>
       <c r="L49" t="n">
-        <v>108.47</v>
+        <v>107.24</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-125.73</v>
+        <v>-127.14</v>
       </c>
       <c r="K50" t="n">
-        <v>-33.96</v>
+        <v>-34.35</v>
       </c>
       <c r="L50" t="n">
-        <v>130.24</v>
+        <v>131.7</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>45.37</v>
+        <v>45.51</v>
       </c>
       <c r="K51" t="n">
-        <v>161.48</v>
+        <v>161.97</v>
       </c>
       <c r="L51" t="n">
-        <v>167.73</v>
+        <v>168.24</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>16.6</v>
+        <v>16.71</v>
       </c>
       <c r="K52" t="n">
-        <v>132.33</v>
+        <v>133.16</v>
       </c>
       <c r="L52" t="n">
-        <v>133.37</v>
+        <v>134.21</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>169.27</v>
+        <v>163.86</v>
       </c>
       <c r="K53" t="n">
-        <v>-239.69</v>
+        <v>-232.02</v>
       </c>
       <c r="L53" t="n">
-        <v>293.43</v>
+        <v>284.05</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>-131.84</v>
+        <v>-144.32</v>
       </c>
       <c r="K54" t="n">
-        <v>-45.72</v>
+        <v>-50.05</v>
       </c>
       <c r="L54" t="n">
-        <v>139.54</v>
+        <v>152.75</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>25.19</v>
+        <v>25.57</v>
       </c>
       <c r="K55" t="n">
-        <v>-210.23</v>
+        <v>-213.41</v>
       </c>
       <c r="L55" t="n">
-        <v>211.73</v>
+        <v>214.93</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>195.76</v>
+        <v>218.4</v>
       </c>
       <c r="K56" t="n">
-        <v>-73.48</v>
+        <v>-81.98</v>
       </c>
       <c r="L56" t="n">
-        <v>209.1</v>
+        <v>233.28</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>268.27</v>
+        <v>272.04</v>
       </c>
       <c r="K57" t="n">
-        <v>20.94</v>
+        <v>21.23</v>
       </c>
       <c r="L57" t="n">
-        <v>269.09</v>
+        <v>272.86</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-409.72</v>
+        <v>-393.58</v>
       </c>
       <c r="K58" t="n">
-        <v>234.71</v>
+        <v>225.47</v>
       </c>
       <c r="L58" t="n">
-        <v>472.19</v>
+        <v>453.58</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>35.7</v>
+        <v>36.4</v>
       </c>
       <c r="K59" t="n">
-        <v>62.46</v>
+        <v>63.69</v>
       </c>
       <c r="L59" t="n">
-        <v>71.94</v>
+        <v>73.34999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-49.14</v>
+        <v>-52.2</v>
       </c>
       <c r="K60" t="n">
-        <v>29.72</v>
+        <v>31.58</v>
       </c>
       <c r="L60" t="n">
-        <v>57.43</v>
+        <v>61.01</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.76</v>
+        <v>-0.75</v>
       </c>
       <c r="K61" t="n">
-        <v>85.77</v>
+        <v>84.70999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>85.77</v>
+        <v>84.72</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-18.93</v>
+        <v>-17.88</v>
       </c>
       <c r="K62" t="n">
-        <v>-143.69</v>
+        <v>-135.72</v>
       </c>
       <c r="L62" t="n">
-        <v>144.93</v>
+        <v>136.9</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-74.59999999999999</v>
+        <v>-75.79000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>-46.57</v>
+        <v>-47.31</v>
       </c>
       <c r="L63" t="n">
-        <v>87.94</v>
+        <v>89.34</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-87.97</v>
+        <v>-87.66</v>
       </c>
       <c r="K64" t="n">
-        <v>10.99</v>
+        <v>10.96</v>
       </c>
       <c r="L64" t="n">
-        <v>88.65000000000001</v>
+        <v>88.34</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.82</v>
+        <v>-4.77</v>
       </c>
       <c r="K65" t="n">
-        <v>167.52</v>
+        <v>165.83</v>
       </c>
       <c r="L65" t="n">
-        <v>167.59</v>
+        <v>165.9</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-35.07</v>
+        <v>-34.55</v>
       </c>
       <c r="K66" t="n">
-        <v>-176.32</v>
+        <v>-173.74</v>
       </c>
       <c r="L66" t="n">
-        <v>179.78</v>
+        <v>177.14</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>32.19</v>
+        <v>32.21</v>
       </c>
       <c r="K67" t="n">
-        <v>-174.93</v>
+        <v>-175.01</v>
       </c>
       <c r="L67" t="n">
-        <v>177.87</v>
+        <v>177.95</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>66.97</v>
+        <v>66.62</v>
       </c>
       <c r="K68" t="n">
-        <v>-187.85</v>
+        <v>-186.87</v>
       </c>
       <c r="L68" t="n">
-        <v>199.43</v>
+        <v>198.39</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-79.52</v>
+        <v>-84.34</v>
       </c>
       <c r="K69" t="n">
-        <v>124.95</v>
+        <v>132.51</v>
       </c>
       <c r="L69" t="n">
-        <v>148.11</v>
+        <v>157.08</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-171.39</v>
+        <v>-164.79</v>
       </c>
       <c r="K70" t="n">
-        <v>180.16</v>
+        <v>173.23</v>
       </c>
       <c r="L70" t="n">
-        <v>248.66</v>
+        <v>239.09</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-262.38</v>
+        <v>-288.6</v>
       </c>
       <c r="K71" t="n">
-        <v>102.95</v>
+        <v>113.24</v>
       </c>
       <c r="L71" t="n">
-        <v>281.85</v>
+        <v>310.02</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>74.40000000000001</v>
+        <v>80.14</v>
       </c>
       <c r="K72" t="n">
-        <v>-243</v>
+        <v>-261.75</v>
       </c>
       <c r="L72" t="n">
-        <v>254.13</v>
+        <v>273.74</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-24.51</v>
+        <v>-26.21</v>
       </c>
       <c r="K73" t="n">
-        <v>-223.36</v>
+        <v>-238.81</v>
       </c>
       <c r="L73" t="n">
-        <v>224.7</v>
+        <v>240.25</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>38.13</v>
+        <v>40.16</v>
       </c>
       <c r="K74" t="n">
-        <v>48.33</v>
+        <v>50.89</v>
       </c>
       <c r="L74" t="n">
-        <v>61.56</v>
+        <v>64.81999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>55.99</v>
+        <v>58.2</v>
       </c>
       <c r="K75" t="n">
-        <v>34.35</v>
+        <v>35.7</v>
       </c>
       <c r="L75" t="n">
-        <v>65.68000000000001</v>
+        <v>68.28</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>60.02</v>
+        <v>60.21</v>
       </c>
       <c r="K76" t="n">
-        <v>-47.5</v>
+        <v>-47.65</v>
       </c>
       <c r="L76" t="n">
-        <v>76.54000000000001</v>
+        <v>76.78</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>24.65</v>
+        <v>23.2</v>
       </c>
       <c r="K77" t="n">
-        <v>148.47</v>
+        <v>139.76</v>
       </c>
       <c r="L77" t="n">
-        <v>150.5</v>
+        <v>141.68</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-213.73</v>
+        <v>-193.41</v>
       </c>
       <c r="K78" t="n">
-        <v>31.38</v>
+        <v>28.4</v>
       </c>
       <c r="L78" t="n">
-        <v>216.02</v>
+        <v>195.49</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>32.65</v>
+        <v>32.14</v>
       </c>
       <c r="K79" t="n">
-        <v>99.15000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>104.39</v>
+        <v>102.76</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>104.25</v>
+        <v>99.13</v>
       </c>
       <c r="K80" t="n">
-        <v>-209.55</v>
+        <v>-199.25</v>
       </c>
       <c r="L80" t="n">
-        <v>234.05</v>
+        <v>222.55</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>77.29000000000001</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>-88.73999999999999</v>
+        <v>-92.13</v>
       </c>
       <c r="L81" t="n">
-        <v>117.68</v>
+        <v>122.17</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>37.61</v>
+        <v>41.07</v>
       </c>
       <c r="K82" t="n">
-        <v>-87.20999999999999</v>
+        <v>-95.23</v>
       </c>
       <c r="L82" t="n">
-        <v>94.97</v>
+        <v>103.71</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>-164.99</v>
+        <v>-171.8</v>
       </c>
       <c r="K83" t="n">
-        <v>73.98999999999999</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="L83" t="n">
-        <v>180.82</v>
+        <v>188.28</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>12.51</v>
+        <v>13.05</v>
       </c>
       <c r="K84" t="n">
-        <v>170.47</v>
+        <v>177.75</v>
       </c>
       <c r="L84" t="n">
-        <v>170.92</v>
+        <v>178.23</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>193.83</v>
+        <v>194.09</v>
       </c>
       <c r="K85" t="n">
-        <v>84.84999999999999</v>
+        <v>84.97</v>
       </c>
       <c r="L85" t="n">
-        <v>211.59</v>
+        <v>211.87</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>410.16</v>
+        <v>399.45</v>
       </c>
       <c r="K86" t="n">
-        <v>36.79</v>
+        <v>35.83</v>
       </c>
       <c r="L86" t="n">
-        <v>411.81</v>
+        <v>401.05</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-310.72</v>
+        <v>-314.48</v>
       </c>
       <c r="K87" t="n">
-        <v>50.23</v>
+        <v>50.83</v>
       </c>
       <c r="L87" t="n">
-        <v>314.76</v>
+        <v>318.57</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>33.91</v>
+        <v>32.58</v>
       </c>
       <c r="K88" t="n">
-        <v>553.88</v>
+        <v>532.15</v>
       </c>
       <c r="L88" t="n">
-        <v>554.91</v>
+        <v>533.15</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-30.xlsx
+++ b/output/2024-04-30.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.18</v>
+        <v>4.22</v>
       </c>
       <c r="F14" t="n">
-        <v>13.54</v>
+        <v>12.85</v>
       </c>
       <c r="G14" t="n">
-        <v>246.2</v>
+        <v>246.3</v>
       </c>
       <c r="H14" t="n">
-        <v>75.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-21.43</v>
+        <v>-67.5</v>
       </c>
       <c r="K14" t="n">
-        <v>60.03</v>
+        <v>91.25</v>
       </c>
       <c r="L14" t="n">
-        <v>63.74</v>
+        <v>113.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:32:56</t>
+          <t>05:33:48</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.73</v>
+        <v>4.29</v>
       </c>
       <c r="F15" t="n">
-        <v>13.92</v>
+        <v>9.41</v>
       </c>
       <c r="G15" t="n">
-        <v>270.3</v>
+        <v>252.1</v>
       </c>
       <c r="H15" t="n">
-        <v>72.90000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-81.73999999999999</v>
+        <v>103.68</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.06</v>
+        <v>-44.24</v>
       </c>
       <c r="L15" t="n">
-        <v>81.73999999999999</v>
+        <v>112.73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:34:43</t>
+          <t>05:36:22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.39</v>
+        <v>3.72</v>
       </c>
       <c r="F16" t="n">
-        <v>13.42</v>
+        <v>13.1</v>
       </c>
       <c r="G16" t="n">
-        <v>272.6</v>
+        <v>253</v>
       </c>
       <c r="H16" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-48.89</v>
+        <v>-69.94</v>
       </c>
       <c r="K16" t="n">
-        <v>86.37</v>
+        <v>71.05</v>
       </c>
       <c r="L16" t="n">
-        <v>99.23999999999999</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:39:38</t>
+          <t>05:41:49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.65</v>
+        <v>4.03</v>
       </c>
       <c r="F17" t="n">
-        <v>13.65</v>
+        <v>12.23</v>
       </c>
       <c r="G17" t="n">
-        <v>261.2</v>
+        <v>254.2</v>
       </c>
       <c r="H17" t="n">
-        <v>75.3</v>
+        <v>77.7</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>74.3</v>
+        <v>108.01</v>
       </c>
       <c r="K17" t="n">
-        <v>-26.47</v>
+        <v>38.9</v>
       </c>
       <c r="L17" t="n">
-        <v>78.88</v>
+        <v>114.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:41:51</t>
+          <t>05:43:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.09</v>
+        <v>4.56</v>
       </c>
       <c r="F18" t="n">
-        <v>14.03</v>
+        <v>11.37</v>
       </c>
       <c r="G18" t="n">
-        <v>267.3</v>
+        <v>255.5</v>
       </c>
       <c r="H18" t="n">
-        <v>81.8</v>
+        <v>81.2</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-27.27</v>
+        <v>-75.56999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-77.44</v>
+        <v>-19.21</v>
       </c>
       <c r="L18" t="n">
-        <v>82.09999999999999</v>
+        <v>77.97</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:43:37</t>
+          <t>05:45:01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.49</v>
+        <v>3.99</v>
       </c>
       <c r="F19" t="n">
-        <v>13.6</v>
+        <v>11.91</v>
       </c>
       <c r="G19" t="n">
-        <v>253.4</v>
+        <v>254.8</v>
       </c>
       <c r="H19" t="n">
-        <v>77.3</v>
+        <v>79.7</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>29.75</v>
+        <v>-13.07</v>
       </c>
       <c r="K19" t="n">
-        <v>94.59</v>
+        <v>-2.03</v>
       </c>
       <c r="L19" t="n">
-        <v>99.15000000000001</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:48:10</t>
+          <t>05:48:03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.34</v>
+        <v>3.62</v>
       </c>
       <c r="F20" t="n">
-        <v>13.81</v>
+        <v>9.48</v>
       </c>
       <c r="G20" t="n">
-        <v>254.2</v>
+        <v>257.8</v>
       </c>
       <c r="H20" t="n">
-        <v>74.90000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>-107.4</v>
+        <v>73.3</v>
       </c>
       <c r="K20" t="n">
-        <v>-58.92</v>
+        <v>-66.89</v>
       </c>
       <c r="L20" t="n">
-        <v>122.5</v>
+        <v>99.23999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:49:51</t>
+          <t>05:48:47</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.42</v>
+        <v>2.96</v>
       </c>
       <c r="F21" t="n">
-        <v>12.65</v>
+        <v>10.14</v>
       </c>
       <c r="G21" t="n">
-        <v>252.6</v>
+        <v>266.8</v>
       </c>
       <c r="H21" t="n">
-        <v>80.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>94.40000000000001</v>
+        <v>-17.32</v>
       </c>
       <c r="K21" t="n">
-        <v>-165.96</v>
+        <v>-126.66</v>
       </c>
       <c r="L21" t="n">
-        <v>190.93</v>
+        <v>127.84</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:51:06</t>
+          <t>05:50:29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.29</v>
+        <v>4.96</v>
       </c>
       <c r="F22" t="n">
-        <v>13.28</v>
+        <v>13.89</v>
       </c>
       <c r="G22" t="n">
-        <v>254.1</v>
+        <v>259.4</v>
       </c>
       <c r="H22" t="n">
-        <v>75.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-53.71</v>
+        <v>-135</v>
       </c>
       <c r="K22" t="n">
-        <v>5.14</v>
+        <v>62.53</v>
       </c>
       <c r="L22" t="n">
-        <v>53.95</v>
+        <v>148.78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:54:57</t>
+          <t>05:55:32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.86</v>
+        <v>3.99</v>
       </c>
       <c r="F23" t="n">
-        <v>13.55</v>
+        <v>11.05</v>
       </c>
       <c r="G23" t="n">
-        <v>258.1</v>
+        <v>255.5</v>
       </c>
       <c r="H23" t="n">
-        <v>76</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-34.01</v>
+        <v>-114.23</v>
       </c>
       <c r="K23" t="n">
-        <v>-225.5</v>
+        <v>-209.29</v>
       </c>
       <c r="L23" t="n">
-        <v>228.05</v>
+        <v>238.43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:56:15</t>
+          <t>05:57:19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.98</v>
+        <v>3.78</v>
       </c>
       <c r="F24" t="n">
-        <v>13.04</v>
+        <v>14.54</v>
       </c>
       <c r="G24" t="n">
-        <v>248.5</v>
+        <v>253.4</v>
       </c>
       <c r="H24" t="n">
-        <v>75</v>
+        <v>81.5</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>112.11</v>
+        <v>-163.35</v>
       </c>
       <c r="K24" t="n">
-        <v>287.07</v>
+        <v>238.41</v>
       </c>
       <c r="L24" t="n">
-        <v>308.18</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:57:24</t>
+          <t>05:58:26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.59</v>
+        <v>4.19</v>
       </c>
       <c r="F25" t="n">
-        <v>13.72</v>
+        <v>14.2</v>
       </c>
       <c r="G25" t="n">
-        <v>270.6</v>
+        <v>248.7</v>
       </c>
       <c r="H25" t="n">
-        <v>74.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>140.67</v>
+        <v>-48.71</v>
       </c>
       <c r="K25" t="n">
-        <v>-199.85</v>
+        <v>320.74</v>
       </c>
       <c r="L25" t="n">
-        <v>244.4</v>
+        <v>324.42</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:01:37</t>
+          <t>06:02:46</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="F26" t="n">
-        <v>15</v>
+        <v>11.82</v>
       </c>
       <c r="G26" t="n">
-        <v>253.6</v>
+        <v>255</v>
       </c>
       <c r="H26" t="n">
-        <v>78.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>14.9</v>
+        <v>-121.25</v>
       </c>
       <c r="K26" t="n">
-        <v>208.7</v>
+        <v>176.69</v>
       </c>
       <c r="L26" t="n">
-        <v>209.23</v>
+        <v>214.29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:03:06</t>
+          <t>06:03:54</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="F27" t="n">
-        <v>13.93</v>
+        <v>15.01</v>
       </c>
       <c r="G27" t="n">
-        <v>258.2</v>
+        <v>244.7</v>
       </c>
       <c r="H27" t="n">
-        <v>79</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>252.2</v>
+        <v>-266.25</v>
       </c>
       <c r="K27" t="n">
-        <v>186.98</v>
+        <v>37.29</v>
       </c>
       <c r="L27" t="n">
-        <v>313.95</v>
+        <v>268.85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:04:38</t>
+          <t>06:05:04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.34</v>
+        <v>4.1</v>
       </c>
       <c r="F28" t="n">
-        <v>13.9</v>
+        <v>9.42</v>
       </c>
       <c r="G28" t="n">
-        <v>252.3</v>
+        <v>252.2</v>
       </c>
       <c r="H28" t="n">
-        <v>76.2</v>
+        <v>72</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-233.96</v>
+        <v>-291.73</v>
       </c>
       <c r="K28" t="n">
-        <v>-257.35</v>
+        <v>-109.01</v>
       </c>
       <c r="L28" t="n">
-        <v>347.8</v>
+        <v>311.43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:13:35</t>
+          <t>06:14:38</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.62</v>
+        <v>3.76</v>
       </c>
       <c r="F29" t="n">
-        <v>13.27</v>
+        <v>11.96</v>
       </c>
       <c r="G29" t="n">
-        <v>250.9</v>
+        <v>258.4</v>
       </c>
       <c r="H29" t="n">
-        <v>74.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>53.64</v>
+        <v>-49.07</v>
       </c>
       <c r="K29" t="n">
-        <v>-41.88</v>
+        <v>70.16</v>
       </c>
       <c r="L29" t="n">
-        <v>68.05</v>
+        <v>85.62</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:14:31</t>
+          <t>06:16:55</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.16</v>
+        <v>4.75</v>
       </c>
       <c r="F30" t="n">
-        <v>14.28</v>
+        <v>15.11</v>
       </c>
       <c r="G30" t="n">
-        <v>247.8</v>
+        <v>264.9</v>
       </c>
       <c r="H30" t="n">
-        <v>75.7</v>
+        <v>70.7</v>
       </c>
       <c r="I30" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>37.47</v>
+        <v>74.09</v>
       </c>
       <c r="K30" t="n">
-        <v>59.77</v>
+        <v>29.77</v>
       </c>
       <c r="L30" t="n">
-        <v>70.54000000000001</v>
+        <v>79.84999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:16:08</t>
+          <t>06:18:48</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.48</v>
+        <v>4.39</v>
       </c>
       <c r="F31" t="n">
-        <v>13.82</v>
+        <v>13.11</v>
       </c>
       <c r="G31" t="n">
-        <v>257.2</v>
+        <v>241.4</v>
       </c>
       <c r="H31" t="n">
-        <v>82.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>41.73</v>
+        <v>97.95</v>
       </c>
       <c r="K31" t="n">
-        <v>-38.73</v>
+        <v>-32.06</v>
       </c>
       <c r="L31" t="n">
-        <v>56.94</v>
+        <v>103.07</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:21:05</t>
+          <t>06:22:33</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.76</v>
+        <v>4.28</v>
       </c>
       <c r="F32" t="n">
-        <v>13.55</v>
+        <v>12.78</v>
       </c>
       <c r="G32" t="n">
-        <v>270.5</v>
+        <v>252.6</v>
       </c>
       <c r="H32" t="n">
-        <v>76.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="I32" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-81.59</v>
+        <v>-66.06</v>
       </c>
       <c r="K32" t="n">
-        <v>29.16</v>
+        <v>62.42</v>
       </c>
       <c r="L32" t="n">
-        <v>86.64</v>
+        <v>90.88</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:22:52</t>
+          <t>06:23:43</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.06</v>
+        <v>4.75</v>
       </c>
       <c r="F33" t="n">
-        <v>14.13</v>
+        <v>13.78</v>
       </c>
       <c r="G33" t="n">
-        <v>260.4</v>
+        <v>262.5</v>
       </c>
       <c r="H33" t="n">
-        <v>75.8</v>
+        <v>77.7</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>4.39</v>
+        <v>-95.59</v>
       </c>
       <c r="K33" t="n">
-        <v>155.42</v>
+        <v>-10.83</v>
       </c>
       <c r="L33" t="n">
-        <v>155.48</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:23:34</t>
+          <t>06:25:06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.86</v>
+        <v>5.03</v>
       </c>
       <c r="F34" t="n">
-        <v>14.37</v>
+        <v>15.87</v>
       </c>
       <c r="G34" t="n">
-        <v>253.3</v>
+        <v>244.1</v>
       </c>
       <c r="H34" t="n">
-        <v>75.09999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>90.51000000000001</v>
+        <v>-83.45</v>
       </c>
       <c r="K34" t="n">
-        <v>48.92</v>
+        <v>-95.03</v>
       </c>
       <c r="L34" t="n">
-        <v>102.89</v>
+        <v>126.47</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:27:16</t>
+          <t>06:29:46</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.85</v>
+        <v>4.52</v>
       </c>
       <c r="F35" t="n">
-        <v>14.01</v>
+        <v>14.53</v>
       </c>
       <c r="G35" t="n">
-        <v>256</v>
+        <v>246.2</v>
       </c>
       <c r="H35" t="n">
-        <v>72.7</v>
+        <v>80.7</v>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>62.05</v>
+        <v>-153.03</v>
       </c>
       <c r="K35" t="n">
-        <v>77.90000000000001</v>
+        <v>-183.78</v>
       </c>
       <c r="L35" t="n">
-        <v>99.59</v>
+        <v>239.16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:29:49</t>
+          <t>06:31:08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.98</v>
+        <v>4.75</v>
       </c>
       <c r="F36" t="n">
-        <v>14.1</v>
+        <v>15.14</v>
       </c>
       <c r="G36" t="n">
-        <v>238.1</v>
+        <v>249.1</v>
       </c>
       <c r="H36" t="n">
-        <v>72.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>83.61</v>
+        <v>-91.95999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>111.92</v>
+        <v>-191.95</v>
       </c>
       <c r="L36" t="n">
-        <v>139.7</v>
+        <v>212.84</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:31:37</t>
+          <t>06:32:22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.15</v>
+        <v>4.49</v>
       </c>
       <c r="F37" t="n">
-        <v>13.61</v>
+        <v>12.08</v>
       </c>
       <c r="G37" t="n">
-        <v>255.1</v>
+        <v>257.2</v>
       </c>
       <c r="H37" t="n">
-        <v>71.2</v>
+        <v>72.5</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>147.92</v>
+        <v>121.52</v>
       </c>
       <c r="K37" t="n">
-        <v>-122.34</v>
+        <v>45.13</v>
       </c>
       <c r="L37" t="n">
-        <v>191.95</v>
+        <v>129.63</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:35:53</t>
+          <t>06:37:17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1636,31 +1636,31 @@
         <v>4.62</v>
       </c>
       <c r="F38" t="n">
-        <v>13.95</v>
+        <v>11.92</v>
       </c>
       <c r="G38" t="n">
-        <v>256.5</v>
+        <v>268.3</v>
       </c>
       <c r="H38" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="I38" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-139.97</v>
+        <v>-194.49</v>
       </c>
       <c r="K38" t="n">
-        <v>133.35</v>
+        <v>49.04</v>
       </c>
       <c r="L38" t="n">
-        <v>193.33</v>
+        <v>200.58</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:37:22</t>
+          <t>06:38:15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>6.38</v>
+        <v>5.53</v>
       </c>
       <c r="F39" t="n">
-        <v>14.38</v>
+        <v>15.87</v>
       </c>
       <c r="G39" t="n">
-        <v>254.9</v>
+        <v>259.1</v>
       </c>
       <c r="H39" t="n">
-        <v>88.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J39" t="n">
-        <v>-103.25</v>
+        <v>-214.34</v>
       </c>
       <c r="K39" t="n">
-        <v>213.84</v>
+        <v>-163.67</v>
       </c>
       <c r="L39" t="n">
-        <v>237.46</v>
+        <v>269.68</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:39:19</t>
+          <t>06:39:16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.64</v>
+        <v>4.9</v>
       </c>
       <c r="F40" t="n">
-        <v>14.28</v>
+        <v>15.87</v>
       </c>
       <c r="G40" t="n">
-        <v>262</v>
+        <v>255.2</v>
       </c>
       <c r="H40" t="n">
-        <v>75.40000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>222.32</v>
+        <v>184.26</v>
       </c>
       <c r="K40" t="n">
-        <v>15.07</v>
+        <v>116.73</v>
       </c>
       <c r="L40" t="n">
-        <v>222.83</v>
+        <v>218.13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:43:04</t>
+          <t>06:43:45</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.34</v>
+        <v>4.05</v>
       </c>
       <c r="F41" t="n">
-        <v>14</v>
+        <v>12.56</v>
       </c>
       <c r="G41" t="n">
-        <v>245.8</v>
+        <v>262.7</v>
       </c>
       <c r="H41" t="n">
-        <v>74.7</v>
+        <v>78.5</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-58.27</v>
+        <v>153.44</v>
       </c>
       <c r="K41" t="n">
-        <v>259.35</v>
+        <v>-325.98</v>
       </c>
       <c r="L41" t="n">
-        <v>265.81</v>
+        <v>360.29</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:44:47</t>
+          <t>06:45:01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.82</v>
+        <v>4.6</v>
       </c>
       <c r="F42" t="n">
-        <v>14.08</v>
+        <v>10.57</v>
       </c>
       <c r="G42" t="n">
-        <v>256.1</v>
+        <v>247.4</v>
       </c>
       <c r="H42" t="n">
-        <v>70.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>-234.5</v>
+        <v>265.81</v>
       </c>
       <c r="K42" t="n">
-        <v>-237.75</v>
+        <v>394.71</v>
       </c>
       <c r="L42" t="n">
-        <v>333.94</v>
+        <v>475.87</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:45:50</t>
+          <t>06:47:35</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.5</v>
+        <v>4.14</v>
       </c>
       <c r="F43" t="n">
-        <v>14.02</v>
+        <v>12.97</v>
       </c>
       <c r="G43" t="n">
-        <v>258.3</v>
+        <v>256.5</v>
       </c>
       <c r="H43" t="n">
-        <v>75.3</v>
+        <v>80.2</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>118.2</v>
+        <v>169.63</v>
       </c>
       <c r="K43" t="n">
-        <v>168.05</v>
+        <v>-274.23</v>
       </c>
       <c r="L43" t="n">
-        <v>205.46</v>
+        <v>322.45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:57:04</t>
+          <t>07:00:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.29</v>
+        <v>4.91</v>
       </c>
       <c r="F44" t="n">
-        <v>14.16</v>
+        <v>14.88</v>
       </c>
       <c r="G44" t="n">
-        <v>260.5</v>
+        <v>255.6</v>
       </c>
       <c r="H44" t="n">
-        <v>74.40000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>76.03</v>
+        <v>3.39</v>
       </c>
       <c r="K44" t="n">
-        <v>12.63</v>
+        <v>-114.69</v>
       </c>
       <c r="L44" t="n">
-        <v>77.06999999999999</v>
+        <v>114.74</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:59:12</t>
+          <t>07:01:58</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.64</v>
+        <v>4.53</v>
       </c>
       <c r="F45" t="n">
-        <v>13.33</v>
+        <v>11.12</v>
       </c>
       <c r="G45" t="n">
-        <v>248.8</v>
+        <v>253.9</v>
       </c>
       <c r="H45" t="n">
-        <v>78.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>59.34</v>
+        <v>17.76</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.31</v>
+        <v>72.11</v>
       </c>
       <c r="L45" t="n">
-        <v>59.58</v>
+        <v>74.26000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:01:32</t>
+          <t>07:03:10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.31</v>
+        <v>4.81</v>
       </c>
       <c r="F46" t="n">
-        <v>13.8</v>
+        <v>10.61</v>
       </c>
       <c r="G46" t="n">
-        <v>247.5</v>
+        <v>250.7</v>
       </c>
       <c r="H46" t="n">
-        <v>82.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-102.5</v>
+        <v>-66.98</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.64</v>
+        <v>14.01</v>
       </c>
       <c r="L46" t="n">
-        <v>102.56</v>
+        <v>68.43000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:06:36</t>
+          <t>07:08:56</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.39</v>
+        <v>5.44</v>
       </c>
       <c r="F47" t="n">
-        <v>13.67</v>
+        <v>15.87</v>
       </c>
       <c r="G47" t="n">
-        <v>269.5</v>
+        <v>268.6</v>
       </c>
       <c r="H47" t="n">
-        <v>79.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>113.46</v>
+        <v>109.88</v>
       </c>
       <c r="K47" t="n">
-        <v>-32.18</v>
+        <v>49.86</v>
       </c>
       <c r="L47" t="n">
-        <v>117.93</v>
+        <v>120.66</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:08:22</t>
+          <t>07:10:55</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>5.39</v>
+        <v>4.74</v>
       </c>
       <c r="F48" t="n">
-        <v>13.92</v>
+        <v>12.81</v>
       </c>
       <c r="G48" t="n">
-        <v>260.1</v>
+        <v>261.3</v>
       </c>
       <c r="H48" t="n">
-        <v>85.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-86.23999999999999</v>
+        <v>-71.62</v>
       </c>
       <c r="K48" t="n">
-        <v>8.050000000000001</v>
+        <v>-44.37</v>
       </c>
       <c r="L48" t="n">
-        <v>86.62</v>
+        <v>84.25</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:09:59</t>
+          <t>07:13:03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.99</v>
+        <v>5.05</v>
       </c>
       <c r="F49" t="n">
-        <v>13.7</v>
+        <v>13.66</v>
       </c>
       <c r="G49" t="n">
-        <v>251.6</v>
+        <v>266.3</v>
       </c>
       <c r="H49" t="n">
-        <v>84.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>92.43000000000001</v>
+        <v>-106.57</v>
       </c>
       <c r="K49" t="n">
-        <v>-54.38</v>
+        <v>-21.06</v>
       </c>
       <c r="L49" t="n">
-        <v>107.24</v>
+        <v>108.63</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:15:38</t>
+          <t>07:16:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.32</v>
+        <v>4.21</v>
       </c>
       <c r="F50" t="n">
-        <v>13.3</v>
+        <v>15.25</v>
       </c>
       <c r="G50" t="n">
-        <v>263.3</v>
+        <v>241.1</v>
       </c>
       <c r="H50" t="n">
-        <v>84.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-127.14</v>
+        <v>15.23</v>
       </c>
       <c r="K50" t="n">
-        <v>-34.35</v>
+        <v>124.73</v>
       </c>
       <c r="L50" t="n">
-        <v>131.7</v>
+        <v>125.66</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:17:07</t>
+          <t>07:18:34</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>5.33</v>
+        <v>4.83</v>
       </c>
       <c r="F51" t="n">
-        <v>13.91</v>
+        <v>15.29</v>
       </c>
       <c r="G51" t="n">
-        <v>247.5</v>
+        <v>263.6</v>
       </c>
       <c r="H51" t="n">
-        <v>76</v>
+        <v>71.5</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>45.51</v>
+        <v>51.13</v>
       </c>
       <c r="K51" t="n">
-        <v>161.97</v>
+        <v>-159.05</v>
       </c>
       <c r="L51" t="n">
-        <v>168.24</v>
+        <v>167.07</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:18:09</t>
+          <t>07:19:36</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.85</v>
+        <v>4.64</v>
       </c>
       <c r="F52" t="n">
-        <v>13.27</v>
+        <v>15.75</v>
       </c>
       <c r="G52" t="n">
-        <v>260</v>
+        <v>254.3</v>
       </c>
       <c r="H52" t="n">
-        <v>77.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>16.71</v>
+        <v>42.86</v>
       </c>
       <c r="K52" t="n">
-        <v>133.16</v>
+        <v>130.07</v>
       </c>
       <c r="L52" t="n">
-        <v>134.21</v>
+        <v>136.95</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:23:02</t>
+          <t>07:24:54</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.1</v>
+        <v>5.23</v>
       </c>
       <c r="F53" t="n">
-        <v>13.59</v>
+        <v>15.87</v>
       </c>
       <c r="G53" t="n">
-        <v>264.4</v>
+        <v>259</v>
       </c>
       <c r="H53" t="n">
-        <v>81.7</v>
+        <v>72</v>
       </c>
       <c r="I53" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>163.86</v>
+        <v>-126.86</v>
       </c>
       <c r="K53" t="n">
-        <v>-232.02</v>
+        <v>-250.67</v>
       </c>
       <c r="L53" t="n">
-        <v>284.05</v>
+        <v>280.94</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:24:31</t>
+          <t>07:27:02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.93</v>
+        <v>5.08</v>
       </c>
       <c r="F54" t="n">
-        <v>14.18</v>
+        <v>14.74</v>
       </c>
       <c r="G54" t="n">
-        <v>244.4</v>
+        <v>259.8</v>
       </c>
       <c r="H54" t="n">
-        <v>77.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>-144.32</v>
+        <v>-214.53</v>
       </c>
       <c r="K54" t="n">
-        <v>-50.05</v>
+        <v>5.59</v>
       </c>
       <c r="L54" t="n">
-        <v>152.75</v>
+        <v>214.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:26:35</t>
+          <t>07:29:07</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.98</v>
+        <v>5.12</v>
       </c>
       <c r="F55" t="n">
-        <v>14.71</v>
+        <v>12.52</v>
       </c>
       <c r="G55" t="n">
-        <v>262.2</v>
+        <v>262.3</v>
       </c>
       <c r="H55" t="n">
-        <v>79</v>
+        <v>74.3</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>25.57</v>
+        <v>-206.84</v>
       </c>
       <c r="K55" t="n">
-        <v>-213.41</v>
+        <v>-124.15</v>
       </c>
       <c r="L55" t="n">
-        <v>214.93</v>
+        <v>241.23</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:32:19</t>
+          <t>07:35:01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.14</v>
+        <v>4.67</v>
       </c>
       <c r="F56" t="n">
-        <v>13.77</v>
+        <v>14.77</v>
       </c>
       <c r="G56" t="n">
-        <v>249.4</v>
+        <v>243.5</v>
       </c>
       <c r="H56" t="n">
-        <v>75.90000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>218.4</v>
+        <v>-134.21</v>
       </c>
       <c r="K56" t="n">
-        <v>-81.98</v>
+        <v>321.13</v>
       </c>
       <c r="L56" t="n">
-        <v>233.28</v>
+        <v>348.05</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:33:20</t>
+          <t>07:35:49</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.11</v>
+        <v>4.39</v>
       </c>
       <c r="F57" t="n">
-        <v>13.16</v>
+        <v>13.02</v>
       </c>
       <c r="G57" t="n">
-        <v>248.4</v>
+        <v>252.5</v>
       </c>
       <c r="H57" t="n">
-        <v>83.2</v>
+        <v>79.2</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>272.04</v>
+        <v>284.6</v>
       </c>
       <c r="K57" t="n">
-        <v>21.23</v>
+        <v>-237.78</v>
       </c>
       <c r="L57" t="n">
-        <v>272.86</v>
+        <v>370.86</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:35:06</t>
+          <t>07:37:35</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.61</v>
+        <v>4.39</v>
       </c>
       <c r="F58" t="n">
-        <v>13.51</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G58" t="n">
-        <v>245.9</v>
+        <v>259.1</v>
       </c>
       <c r="H58" t="n">
-        <v>85.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>-393.58</v>
+        <v>120.88</v>
       </c>
       <c r="K58" t="n">
-        <v>225.47</v>
+        <v>-173.1</v>
       </c>
       <c r="L58" t="n">
-        <v>453.58</v>
+        <v>211.13</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:45:02</t>
+          <t>07:48:01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.02</v>
+        <v>4.28</v>
       </c>
       <c r="F59" t="n">
-        <v>13.74</v>
+        <v>11.11</v>
       </c>
       <c r="G59" t="n">
-        <v>245.6</v>
+        <v>265.9</v>
       </c>
       <c r="H59" t="n">
-        <v>78</v>
+        <v>81.8</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>36.4</v>
+        <v>73.48</v>
       </c>
       <c r="K59" t="n">
-        <v>63.69</v>
+        <v>-25.44</v>
       </c>
       <c r="L59" t="n">
-        <v>73.34999999999999</v>
+        <v>77.76000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:46:43</t>
+          <t>07:49:41</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.4</v>
+        <v>4.55</v>
       </c>
       <c r="F60" t="n">
-        <v>13.61</v>
+        <v>12.98</v>
       </c>
       <c r="G60" t="n">
-        <v>251.7</v>
+        <v>245.6</v>
       </c>
       <c r="H60" t="n">
-        <v>82.3</v>
+        <v>79.7</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>-52.2</v>
+        <v>44.92</v>
       </c>
       <c r="K60" t="n">
-        <v>31.58</v>
+        <v>66.56</v>
       </c>
       <c r="L60" t="n">
-        <v>61.01</v>
+        <v>80.31</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:48:13</t>
+          <t>07:52:25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.28</v>
+        <v>4.33</v>
       </c>
       <c r="F61" t="n">
-        <v>14.07</v>
+        <v>12.08</v>
       </c>
       <c r="G61" t="n">
-        <v>246.2</v>
+        <v>260.6</v>
       </c>
       <c r="H61" t="n">
-        <v>82.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.75</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>84.70999999999999</v>
+        <v>-36.35</v>
       </c>
       <c r="L61" t="n">
-        <v>84.72</v>
+        <v>101.25</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:52:39</t>
+          <t>07:55:43</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>5.13</v>
+        <v>4.35</v>
       </c>
       <c r="F62" t="n">
-        <v>13.41</v>
+        <v>12.65</v>
       </c>
       <c r="G62" t="n">
-        <v>248.5</v>
+        <v>252.4</v>
       </c>
       <c r="H62" t="n">
-        <v>86.2</v>
+        <v>69.2</v>
       </c>
       <c r="I62" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-17.88</v>
+        <v>74.56</v>
       </c>
       <c r="K62" t="n">
-        <v>-135.72</v>
+        <v>35.03</v>
       </c>
       <c r="L62" t="n">
-        <v>136.9</v>
+        <v>82.38</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:54:48</t>
+          <t>07:57:41</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.69</v>
+        <v>4.52</v>
       </c>
       <c r="F63" t="n">
-        <v>14.04</v>
+        <v>14.92</v>
       </c>
       <c r="G63" t="n">
-        <v>249.3</v>
+        <v>236.3</v>
       </c>
       <c r="H63" t="n">
-        <v>80</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>-75.79000000000001</v>
+        <v>-87.81</v>
       </c>
       <c r="K63" t="n">
-        <v>-47.31</v>
+        <v>1.21</v>
       </c>
       <c r="L63" t="n">
-        <v>89.34</v>
+        <v>87.81</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:55:53</t>
+          <t>07:58:56</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.8</v>
+        <v>4.38</v>
       </c>
       <c r="F64" t="n">
-        <v>13.42</v>
+        <v>11.04</v>
       </c>
       <c r="G64" t="n">
-        <v>254.7</v>
+        <v>257.5</v>
       </c>
       <c r="H64" t="n">
-        <v>75.59999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="I64" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-87.66</v>
+        <v>-6.64</v>
       </c>
       <c r="K64" t="n">
-        <v>10.96</v>
+        <v>-109.86</v>
       </c>
       <c r="L64" t="n">
-        <v>88.34</v>
+        <v>110.06</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:01:24</t>
+          <t>08:02:41</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.99</v>
+        <v>4.53</v>
       </c>
       <c r="F65" t="n">
-        <v>13.64</v>
+        <v>12.98</v>
       </c>
       <c r="G65" t="n">
-        <v>249.1</v>
+        <v>260.6</v>
       </c>
       <c r="H65" t="n">
-        <v>72.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.77</v>
+        <v>69.48</v>
       </c>
       <c r="K65" t="n">
-        <v>165.83</v>
+        <v>102.45</v>
       </c>
       <c r="L65" t="n">
-        <v>165.9</v>
+        <v>123.78</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:02:06</t>
+          <t>08:04:25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.16</v>
+        <v>4.46</v>
       </c>
       <c r="F66" t="n">
-        <v>13.48</v>
+        <v>13.22</v>
       </c>
       <c r="G66" t="n">
-        <v>259.2</v>
+        <v>257.7</v>
       </c>
       <c r="H66" t="n">
-        <v>81.3</v>
+        <v>73</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>-34.55</v>
+        <v>-110.62</v>
       </c>
       <c r="K66" t="n">
-        <v>-173.74</v>
+        <v>-21.4</v>
       </c>
       <c r="L66" t="n">
-        <v>177.14</v>
+        <v>112.67</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:03:43</t>
+          <t>08:05:58</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5.78</v>
+        <v>4.5</v>
       </c>
       <c r="F67" t="n">
-        <v>13.78</v>
+        <v>13.56</v>
       </c>
       <c r="G67" t="n">
-        <v>259</v>
+        <v>244.9</v>
       </c>
       <c r="H67" t="n">
-        <v>75.7</v>
+        <v>80</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>32.21</v>
+        <v>-206.93</v>
       </c>
       <c r="K67" t="n">
-        <v>-175.01</v>
+        <v>37.61</v>
       </c>
       <c r="L67" t="n">
-        <v>177.95</v>
+        <v>210.32</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:08:27</t>
+          <t>08:11:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="F68" t="n">
-        <v>13.85</v>
+        <v>13.72</v>
       </c>
       <c r="G68" t="n">
-        <v>244.4</v>
+        <v>244.5</v>
       </c>
       <c r="H68" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>66.62</v>
+        <v>150.81</v>
       </c>
       <c r="K68" t="n">
-        <v>-186.87</v>
+        <v>177.63</v>
       </c>
       <c r="L68" t="n">
-        <v>198.39</v>
+        <v>233.01</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:10:50</t>
+          <t>08:12:38</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.81</v>
+        <v>5.28</v>
       </c>
       <c r="F69" t="n">
-        <v>13.4</v>
+        <v>14.27</v>
       </c>
       <c r="G69" t="n">
-        <v>256.8</v>
+        <v>258.6</v>
       </c>
       <c r="H69" t="n">
-        <v>82.5</v>
+        <v>78</v>
       </c>
       <c r="I69" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-84.34</v>
+        <v>-183.3</v>
       </c>
       <c r="K69" t="n">
-        <v>132.51</v>
+        <v>27.6</v>
       </c>
       <c r="L69" t="n">
-        <v>157.08</v>
+        <v>185.36</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:13:20</t>
+          <t>08:13:49</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.57</v>
+        <v>4.96</v>
       </c>
       <c r="F70" t="n">
-        <v>14</v>
+        <v>14.06</v>
       </c>
       <c r="G70" t="n">
-        <v>256.1</v>
+        <v>267.1</v>
       </c>
       <c r="H70" t="n">
-        <v>79.3</v>
+        <v>73.2</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-164.79</v>
+        <v>8.34</v>
       </c>
       <c r="K70" t="n">
-        <v>173.23</v>
+        <v>-234.01</v>
       </c>
       <c r="L70" t="n">
-        <v>239.09</v>
+        <v>234.16</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:18:28</t>
+          <t>08:17:31</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.97</v>
+        <v>4.52</v>
       </c>
       <c r="F71" t="n">
-        <v>14.34</v>
+        <v>15.87</v>
       </c>
       <c r="G71" t="n">
-        <v>258.2</v>
+        <v>255.7</v>
       </c>
       <c r="H71" t="n">
-        <v>75.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-288.6</v>
+        <v>-152.55</v>
       </c>
       <c r="K71" t="n">
-        <v>113.24</v>
+        <v>-346.87</v>
       </c>
       <c r="L71" t="n">
-        <v>310.02</v>
+        <v>378.93</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:20:18</t>
+          <t>08:18:21</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>5.26</v>
+        <v>5.14</v>
       </c>
       <c r="F72" t="n">
-        <v>14.25</v>
+        <v>15.52</v>
       </c>
       <c r="G72" t="n">
-        <v>259.1</v>
+        <v>250.3</v>
       </c>
       <c r="H72" t="n">
-        <v>72.3</v>
+        <v>80.2</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>80.14</v>
+        <v>320.74</v>
       </c>
       <c r="K72" t="n">
-        <v>-261.75</v>
+        <v>124.7</v>
       </c>
       <c r="L72" t="n">
-        <v>273.74</v>
+        <v>344.13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:21:59</t>
+          <t>08:20:01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.51</v>
+        <v>5.09</v>
       </c>
       <c r="F73" t="n">
-        <v>13.38</v>
+        <v>13.66</v>
       </c>
       <c r="G73" t="n">
-        <v>266.1</v>
+        <v>249.6</v>
       </c>
       <c r="H73" t="n">
-        <v>80.59999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-26.21</v>
+        <v>-155.9</v>
       </c>
       <c r="K73" t="n">
-        <v>-238.81</v>
+        <v>-313.83</v>
       </c>
       <c r="L73" t="n">
-        <v>240.25</v>
+        <v>350.42</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:29:58</t>
+          <t>08:32:21</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
       <c r="F74" t="n">
-        <v>13.87</v>
+        <v>15.87</v>
       </c>
       <c r="G74" t="n">
-        <v>254.6</v>
+        <v>257.8</v>
       </c>
       <c r="H74" t="n">
-        <v>74.59999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>40.16</v>
+        <v>-25.89</v>
       </c>
       <c r="K74" t="n">
-        <v>50.89</v>
+        <v>-75.42</v>
       </c>
       <c r="L74" t="n">
-        <v>64.81999999999999</v>
+        <v>79.73999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:31:25</t>
+          <t>08:33:08</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3190,31 +3190,31 @@
         <v>5.05</v>
       </c>
       <c r="F75" t="n">
-        <v>14.48</v>
+        <v>15.87</v>
       </c>
       <c r="G75" t="n">
-        <v>251.4</v>
+        <v>257.1</v>
       </c>
       <c r="H75" t="n">
-        <v>79.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>58.2</v>
+        <v>-83.40000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>35.7</v>
+        <v>-14.53</v>
       </c>
       <c r="L75" t="n">
-        <v>68.28</v>
+        <v>84.66</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:34:13</t>
+          <t>08:35:12</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.88</v>
+        <v>4.97</v>
       </c>
       <c r="F76" t="n">
-        <v>13.89</v>
+        <v>15.87</v>
       </c>
       <c r="G76" t="n">
-        <v>254.9</v>
+        <v>248.6</v>
       </c>
       <c r="H76" t="n">
-        <v>77.7</v>
+        <v>82.3</v>
       </c>
       <c r="I76" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>60.21</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>-47.65</v>
+        <v>44.71</v>
       </c>
       <c r="L76" t="n">
-        <v>76.78</v>
+        <v>94.45999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:37:57</t>
+          <t>08:39:50</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.63</v>
+        <v>4.77</v>
       </c>
       <c r="F77" t="n">
-        <v>13.76</v>
+        <v>14.51</v>
       </c>
       <c r="G77" t="n">
-        <v>253.2</v>
+        <v>274.4</v>
       </c>
       <c r="H77" t="n">
-        <v>77</v>
+        <v>80.5</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>23.2</v>
+        <v>37.52</v>
       </c>
       <c r="K77" t="n">
-        <v>139.76</v>
+        <v>-115.74</v>
       </c>
       <c r="L77" t="n">
-        <v>141.68</v>
+        <v>121.67</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:39:51</t>
+          <t>08:41:31</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.03</v>
+        <v>4.73</v>
       </c>
       <c r="F78" t="n">
-        <v>14.29</v>
+        <v>15.3</v>
       </c>
       <c r="G78" t="n">
-        <v>250.2</v>
+        <v>259.5</v>
       </c>
       <c r="H78" t="n">
-        <v>71.90000000000001</v>
+        <v>61</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-193.41</v>
+        <v>-111.8</v>
       </c>
       <c r="K78" t="n">
-        <v>28.4</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>195.49</v>
+        <v>137.06</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:41:49</t>
+          <t>08:43:27</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.8</v>
+        <v>3.73</v>
       </c>
       <c r="F79" t="n">
-        <v>13.8</v>
+        <v>11.5</v>
       </c>
       <c r="G79" t="n">
-        <v>261.6</v>
+        <v>263.3</v>
       </c>
       <c r="H79" t="n">
-        <v>67.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>32.14</v>
+        <v>57.96</v>
       </c>
       <c r="K79" t="n">
-        <v>97.59999999999999</v>
+        <v>-49.76</v>
       </c>
       <c r="L79" t="n">
-        <v>102.76</v>
+        <v>76.39</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:46:53</t>
+          <t>08:46:19</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.13</v>
+        <v>4.14</v>
       </c>
       <c r="F80" t="n">
-        <v>14.08</v>
+        <v>15.87</v>
       </c>
       <c r="G80" t="n">
-        <v>239.2</v>
+        <v>238.2</v>
       </c>
       <c r="H80" t="n">
-        <v>77</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>99.13</v>
+        <v>-106.7</v>
       </c>
       <c r="K80" t="n">
-        <v>-199.25</v>
+        <v>-173.45</v>
       </c>
       <c r="L80" t="n">
-        <v>222.55</v>
+        <v>203.64</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:48:49</t>
+          <t>08:47:27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.3</v>
+        <v>4.99</v>
       </c>
       <c r="F81" t="n">
-        <v>13.23</v>
+        <v>12.89</v>
       </c>
       <c r="G81" t="n">
-        <v>257.2</v>
+        <v>249.7</v>
       </c>
       <c r="H81" t="n">
-        <v>78.8</v>
+        <v>81</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>80.23999999999999</v>
+        <v>-193.86</v>
       </c>
       <c r="K81" t="n">
-        <v>-92.13</v>
+        <v>-38.01</v>
       </c>
       <c r="L81" t="n">
-        <v>122.17</v>
+        <v>197.55</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:49:57</t>
+          <t>08:49:23</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.9</v>
+        <v>4.98</v>
       </c>
       <c r="F82" t="n">
-        <v>13.87</v>
+        <v>15.87</v>
       </c>
       <c r="G82" t="n">
-        <v>254.2</v>
+        <v>252</v>
       </c>
       <c r="H82" t="n">
-        <v>77.3</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>41.07</v>
+        <v>138.66</v>
       </c>
       <c r="K82" t="n">
-        <v>-95.23</v>
+        <v>-37.11</v>
       </c>
       <c r="L82" t="n">
-        <v>103.71</v>
+        <v>143.54</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:53:20</t>
+          <t>08:53:50</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.11</v>
+        <v>5.13</v>
       </c>
       <c r="F83" t="n">
-        <v>13.54</v>
+        <v>14.76</v>
       </c>
       <c r="G83" t="n">
-        <v>252.6</v>
+        <v>257.2</v>
       </c>
       <c r="H83" t="n">
-        <v>79.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-171.8</v>
+        <v>-164.13</v>
       </c>
       <c r="K83" t="n">
-        <v>77.04000000000001</v>
+        <v>-98.56999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>188.28</v>
+        <v>191.45</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:55:08</t>
+          <t>08:55:49</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>5.01</v>
+        <v>4.77</v>
       </c>
       <c r="F84" t="n">
-        <v>13.14</v>
+        <v>15.48</v>
       </c>
       <c r="G84" t="n">
-        <v>250</v>
+        <v>260.9</v>
       </c>
       <c r="H84" t="n">
-        <v>77.3</v>
+        <v>79.5</v>
       </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>13.05</v>
+        <v>226.09</v>
       </c>
       <c r="K84" t="n">
-        <v>177.75</v>
+        <v>-66.75</v>
       </c>
       <c r="L84" t="n">
-        <v>178.23</v>
+        <v>235.73</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:56:17</t>
+          <t>08:58:04</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.76</v>
+        <v>4.62</v>
       </c>
       <c r="F85" t="n">
-        <v>13.11</v>
+        <v>11.27</v>
       </c>
       <c r="G85" t="n">
-        <v>246.2</v>
+        <v>258.9</v>
       </c>
       <c r="H85" t="n">
-        <v>75.09999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>194.09</v>
+        <v>214.15</v>
       </c>
       <c r="K85" t="n">
-        <v>84.97</v>
+        <v>-64.70999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>211.87</v>
+        <v>223.71</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:00:46</t>
+          <t>09:03:51</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.62</v>
+        <v>4.9</v>
       </c>
       <c r="F86" t="n">
-        <v>14.37</v>
+        <v>15.87</v>
       </c>
       <c r="G86" t="n">
-        <v>251.9</v>
+        <v>256.1</v>
       </c>
       <c r="H86" t="n">
-        <v>77.2</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>399.45</v>
+        <v>-225.91</v>
       </c>
       <c r="K86" t="n">
-        <v>35.83</v>
+        <v>-438.92</v>
       </c>
       <c r="L86" t="n">
-        <v>401.05</v>
+        <v>493.65</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:01:29</t>
+          <t>09:05:45</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.84</v>
+        <v>4.9</v>
       </c>
       <c r="F87" t="n">
-        <v>14.04</v>
+        <v>15.87</v>
       </c>
       <c r="G87" t="n">
-        <v>263.3</v>
+        <v>255.9</v>
       </c>
       <c r="H87" t="n">
-        <v>77.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-314.48</v>
+        <v>23.26</v>
       </c>
       <c r="K87" t="n">
-        <v>50.83</v>
+        <v>37.67</v>
       </c>
       <c r="L87" t="n">
-        <v>318.57</v>
+        <v>44.27</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:03:49</t>
+          <t>09:06:47</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.47</v>
+        <v>4.68</v>
       </c>
       <c r="F88" t="n">
-        <v>14.15</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G88" t="n">
-        <v>247.7</v>
+        <v>274.7</v>
       </c>
       <c r="H88" t="n">
-        <v>79.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>32.58</v>
+        <v>-256.68</v>
       </c>
       <c r="K88" t="n">
-        <v>532.15</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L88" t="n">
-        <v>533.15</v>
+        <v>256.88</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-30.xlsx
+++ b/output/2024-04-30.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>-67.5</v>
+        <v>-64.39</v>
       </c>
       <c r="K14" t="n">
-        <v>91.25</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>113.5</v>
+        <v>108.27</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>103.68</v>
+        <v>107.14</v>
       </c>
       <c r="K15" t="n">
-        <v>-44.24</v>
+        <v>-45.71</v>
       </c>
       <c r="L15" t="n">
-        <v>112.73</v>
+        <v>116.48</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-69.94</v>
+        <v>-71.14</v>
       </c>
       <c r="K16" t="n">
-        <v>71.05</v>
+        <v>72.28</v>
       </c>
       <c r="L16" t="n">
-        <v>99.7</v>
+        <v>101.42</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>108.01</v>
+        <v>109.71</v>
       </c>
       <c r="K17" t="n">
-        <v>38.9</v>
+        <v>39.51</v>
       </c>
       <c r="L17" t="n">
-        <v>114.8</v>
+        <v>116.61</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-75.56999999999999</v>
+        <v>-76.58</v>
       </c>
       <c r="K18" t="n">
-        <v>-19.21</v>
+        <v>-19.47</v>
       </c>
       <c r="L18" t="n">
-        <v>77.97</v>
+        <v>79.02</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>-13.07</v>
+        <v>-13.76</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.03</v>
+        <v>-2.14</v>
       </c>
       <c r="L19" t="n">
-        <v>13.22</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>73.3</v>
+        <v>73.25</v>
       </c>
       <c r="K20" t="n">
-        <v>-66.89</v>
+        <v>-66.84</v>
       </c>
       <c r="L20" t="n">
-        <v>99.23999999999999</v>
+        <v>99.17</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>-17.32</v>
+        <v>-16.22</v>
       </c>
       <c r="K21" t="n">
-        <v>-126.66</v>
+        <v>-118.58</v>
       </c>
       <c r="L21" t="n">
-        <v>127.84</v>
+        <v>119.68</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-135</v>
+        <v>-125.96</v>
       </c>
       <c r="K22" t="n">
-        <v>62.53</v>
+        <v>58.35</v>
       </c>
       <c r="L22" t="n">
-        <v>148.78</v>
+        <v>138.82</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-114.23</v>
+        <v>-107.03</v>
       </c>
       <c r="K23" t="n">
-        <v>-209.29</v>
+        <v>-196.1</v>
       </c>
       <c r="L23" t="n">
-        <v>238.43</v>
+        <v>223.4</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-163.35</v>
+        <v>-169.74</v>
       </c>
       <c r="K24" t="n">
-        <v>238.41</v>
+        <v>247.73</v>
       </c>
       <c r="L24" t="n">
-        <v>289</v>
+        <v>300.3</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-48.71</v>
+        <v>-51.53</v>
       </c>
       <c r="K25" t="n">
-        <v>320.74</v>
+        <v>339.26</v>
       </c>
       <c r="L25" t="n">
-        <v>324.42</v>
+        <v>343.15</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-121.25</v>
+        <v>-119.32</v>
       </c>
       <c r="K26" t="n">
-        <v>176.69</v>
+        <v>173.88</v>
       </c>
       <c r="L26" t="n">
-        <v>214.29</v>
+        <v>210.88</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-266.25</v>
+        <v>-270.15</v>
       </c>
       <c r="K27" t="n">
-        <v>37.29</v>
+        <v>37.83</v>
       </c>
       <c r="L27" t="n">
-        <v>268.85</v>
+        <v>272.78</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-291.73</v>
+        <v>-310.24</v>
       </c>
       <c r="K28" t="n">
-        <v>-109.01</v>
+        <v>-115.93</v>
       </c>
       <c r="L28" t="n">
-        <v>311.43</v>
+        <v>331.19</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-49.07</v>
+        <v>-46.91</v>
       </c>
       <c r="K29" t="n">
-        <v>70.16</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>85.62</v>
+        <v>81.84999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>74.09</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>29.77</v>
+        <v>28.96</v>
       </c>
       <c r="L30" t="n">
-        <v>79.84999999999999</v>
+        <v>77.67</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>97.95</v>
+        <v>93.36</v>
       </c>
       <c r="K31" t="n">
-        <v>-32.06</v>
+        <v>-30.56</v>
       </c>
       <c r="L31" t="n">
-        <v>103.07</v>
+        <v>98.23999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-66.06</v>
+        <v>-61.54</v>
       </c>
       <c r="K32" t="n">
-        <v>62.42</v>
+        <v>58.15</v>
       </c>
       <c r="L32" t="n">
-        <v>90.88</v>
+        <v>84.67</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-95.59</v>
+        <v>-94.93000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-10.83</v>
+        <v>-10.75</v>
       </c>
       <c r="L33" t="n">
-        <v>96.2</v>
+        <v>95.54000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>-83.45</v>
+        <v>-77.5</v>
       </c>
       <c r="K34" t="n">
-        <v>-95.03</v>
+        <v>-88.25</v>
       </c>
       <c r="L34" t="n">
-        <v>126.47</v>
+        <v>117.45</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-153.03</v>
+        <v>-155.72</v>
       </c>
       <c r="K35" t="n">
-        <v>-183.78</v>
+        <v>-187.01</v>
       </c>
       <c r="L35" t="n">
-        <v>239.16</v>
+        <v>243.35</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>-91.95999999999999</v>
+        <v>-91.73999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-191.95</v>
+        <v>-191.51</v>
       </c>
       <c r="L36" t="n">
-        <v>212.84</v>
+        <v>212.35</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>121.52</v>
+        <v>123.66</v>
       </c>
       <c r="K37" t="n">
-        <v>45.13</v>
+        <v>45.92</v>
       </c>
       <c r="L37" t="n">
-        <v>129.63</v>
+        <v>131.91</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-194.49</v>
+        <v>-187.85</v>
       </c>
       <c r="K38" t="n">
-        <v>49.04</v>
+        <v>47.36</v>
       </c>
       <c r="L38" t="n">
-        <v>200.58</v>
+        <v>193.72</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>26</v>
       </c>
       <c r="J39" t="n">
-        <v>-214.34</v>
+        <v>-207.55</v>
       </c>
       <c r="K39" t="n">
-        <v>-163.67</v>
+        <v>-158.49</v>
       </c>
       <c r="L39" t="n">
-        <v>269.68</v>
+        <v>261.14</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>184.26</v>
+        <v>178.13</v>
       </c>
       <c r="K40" t="n">
-        <v>116.73</v>
+        <v>112.85</v>
       </c>
       <c r="L40" t="n">
-        <v>218.13</v>
+        <v>210.87</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>153.44</v>
+        <v>147.95</v>
       </c>
       <c r="K41" t="n">
-        <v>-325.98</v>
+        <v>-314.32</v>
       </c>
       <c r="L41" t="n">
-        <v>360.29</v>
+        <v>347.4</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>22</v>
       </c>
       <c r="J42" t="n">
-        <v>265.81</v>
+        <v>280.39</v>
       </c>
       <c r="K42" t="n">
-        <v>394.71</v>
+        <v>416.36</v>
       </c>
       <c r="L42" t="n">
-        <v>475.87</v>
+        <v>501.97</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>169.63</v>
+        <v>177.34</v>
       </c>
       <c r="K43" t="n">
-        <v>-274.23</v>
+        <v>-286.7</v>
       </c>
       <c r="L43" t="n">
-        <v>322.45</v>
+        <v>337.11</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>3.39</v>
+        <v>3.49</v>
       </c>
       <c r="K44" t="n">
-        <v>-114.69</v>
+        <v>-118.19</v>
       </c>
       <c r="L44" t="n">
-        <v>114.74</v>
+        <v>118.24</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>17.76</v>
+        <v>16.91</v>
       </c>
       <c r="K45" t="n">
-        <v>72.11</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>74.26000000000001</v>
+        <v>70.73999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-66.98</v>
+        <v>-69.05</v>
       </c>
       <c r="K46" t="n">
-        <v>14.01</v>
+        <v>14.45</v>
       </c>
       <c r="L46" t="n">
-        <v>68.43000000000001</v>
+        <v>70.54000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>109.88</v>
+        <v>101.88</v>
       </c>
       <c r="K47" t="n">
-        <v>49.86</v>
+        <v>46.23</v>
       </c>
       <c r="L47" t="n">
-        <v>120.66</v>
+        <v>111.88</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-71.62</v>
+        <v>-73.87</v>
       </c>
       <c r="K48" t="n">
-        <v>-44.37</v>
+        <v>-45.76</v>
       </c>
       <c r="L48" t="n">
-        <v>84.25</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-106.57</v>
+        <v>-103.55</v>
       </c>
       <c r="K49" t="n">
-        <v>-21.06</v>
+        <v>-20.46</v>
       </c>
       <c r="L49" t="n">
-        <v>108.63</v>
+        <v>105.55</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>15.23</v>
+        <v>15.2</v>
       </c>
       <c r="K50" t="n">
-        <v>124.73</v>
+        <v>124.53</v>
       </c>
       <c r="L50" t="n">
-        <v>125.66</v>
+        <v>125.46</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>51.13</v>
+        <v>47.75</v>
       </c>
       <c r="K51" t="n">
-        <v>-159.05</v>
+        <v>-148.54</v>
       </c>
       <c r="L51" t="n">
-        <v>167.07</v>
+        <v>156.03</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>42.86</v>
+        <v>40.98</v>
       </c>
       <c r="K52" t="n">
-        <v>130.07</v>
+        <v>124.38</v>
       </c>
       <c r="L52" t="n">
-        <v>136.95</v>
+        <v>130.96</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-126.86</v>
+        <v>-135.34</v>
       </c>
       <c r="K53" t="n">
-        <v>-250.67</v>
+        <v>-267.42</v>
       </c>
       <c r="L53" t="n">
-        <v>280.94</v>
+        <v>299.72</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>-214.53</v>
+        <v>-202.71</v>
       </c>
       <c r="K54" t="n">
-        <v>5.59</v>
+        <v>5.28</v>
       </c>
       <c r="L54" t="n">
-        <v>214.6</v>
+        <v>202.77</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>-206.84</v>
+        <v>-216.81</v>
       </c>
       <c r="K55" t="n">
-        <v>-124.15</v>
+        <v>-130.14</v>
       </c>
       <c r="L55" t="n">
-        <v>241.23</v>
+        <v>252.87</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-134.21</v>
+        <v>-141.64</v>
       </c>
       <c r="K56" t="n">
-        <v>321.13</v>
+        <v>338.91</v>
       </c>
       <c r="L56" t="n">
-        <v>348.05</v>
+        <v>367.31</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>284.6</v>
+        <v>288.62</v>
       </c>
       <c r="K57" t="n">
-        <v>-237.78</v>
+        <v>-241.15</v>
       </c>
       <c r="L57" t="n">
-        <v>370.86</v>
+        <v>376.11</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>120.88</v>
+        <v>120.09</v>
       </c>
       <c r="K58" t="n">
-        <v>-173.1</v>
+        <v>-171.97</v>
       </c>
       <c r="L58" t="n">
-        <v>211.13</v>
+        <v>209.74</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>73.48</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>-25.44</v>
+        <v>-26.75</v>
       </c>
       <c r="L59" t="n">
-        <v>77.76000000000001</v>
+        <v>81.76000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>44.92</v>
+        <v>45.52</v>
       </c>
       <c r="K60" t="n">
-        <v>66.56</v>
+        <v>67.45</v>
       </c>
       <c r="L60" t="n">
-        <v>80.31</v>
+        <v>81.38</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>94.51000000000001</v>
+        <v>94.02</v>
       </c>
       <c r="K61" t="n">
-        <v>-36.35</v>
+        <v>-36.16</v>
       </c>
       <c r="L61" t="n">
-        <v>101.25</v>
+        <v>100.73</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>74.56</v>
+        <v>72.66</v>
       </c>
       <c r="K62" t="n">
-        <v>35.03</v>
+        <v>34.14</v>
       </c>
       <c r="L62" t="n">
-        <v>82.38</v>
+        <v>80.28</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>-87.81</v>
+        <v>-83.65000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="L63" t="n">
-        <v>87.81</v>
+        <v>83.66</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-6.64</v>
+        <v>-6.85</v>
       </c>
       <c r="K64" t="n">
-        <v>-109.86</v>
+        <v>-113.48</v>
       </c>
       <c r="L64" t="n">
-        <v>110.06</v>
+        <v>113.68</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>69.48</v>
+        <v>64.91</v>
       </c>
       <c r="K65" t="n">
-        <v>102.45</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>123.78</v>
+        <v>115.65</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>27</v>
       </c>
       <c r="J66" t="n">
-        <v>-110.62</v>
+        <v>-103.36</v>
       </c>
       <c r="K66" t="n">
-        <v>-21.4</v>
+        <v>-20</v>
       </c>
       <c r="L66" t="n">
-        <v>112.67</v>
+        <v>105.28</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-206.93</v>
+        <v>-202.31</v>
       </c>
       <c r="K67" t="n">
-        <v>37.61</v>
+        <v>36.77</v>
       </c>
       <c r="L67" t="n">
-        <v>210.32</v>
+        <v>205.62</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>150.81</v>
+        <v>141.35</v>
       </c>
       <c r="K68" t="n">
-        <v>177.63</v>
+        <v>166.49</v>
       </c>
       <c r="L68" t="n">
-        <v>233.01</v>
+        <v>218.4</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-183.3</v>
+        <v>-177.39</v>
       </c>
       <c r="K69" t="n">
-        <v>27.6</v>
+        <v>26.71</v>
       </c>
       <c r="L69" t="n">
-        <v>185.36</v>
+        <v>179.39</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>8.34</v>
+        <v>8.58</v>
       </c>
       <c r="K70" t="n">
-        <v>-234.01</v>
+        <v>-240.73</v>
       </c>
       <c r="L70" t="n">
-        <v>234.16</v>
+        <v>240.88</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-152.55</v>
+        <v>-148.41</v>
       </c>
       <c r="K71" t="n">
-        <v>-346.87</v>
+        <v>-337.46</v>
       </c>
       <c r="L71" t="n">
-        <v>378.93</v>
+        <v>368.65</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>320.74</v>
+        <v>345.39</v>
       </c>
       <c r="K72" t="n">
-        <v>124.7</v>
+        <v>134.29</v>
       </c>
       <c r="L72" t="n">
-        <v>344.13</v>
+        <v>370.58</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-155.9</v>
+        <v>-148.7</v>
       </c>
       <c r="K73" t="n">
-        <v>-313.83</v>
+        <v>-299.35</v>
       </c>
       <c r="L73" t="n">
-        <v>350.42</v>
+        <v>334.25</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-25.89</v>
+        <v>-27.14</v>
       </c>
       <c r="K74" t="n">
-        <v>-75.42</v>
+        <v>-79.06</v>
       </c>
       <c r="L74" t="n">
-        <v>79.73999999999999</v>
+        <v>83.59</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-83.40000000000001</v>
+        <v>-77.43000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>-14.53</v>
+        <v>-13.49</v>
       </c>
       <c r="L75" t="n">
-        <v>84.66</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>83.20999999999999</v>
+        <v>80.86</v>
       </c>
       <c r="K76" t="n">
-        <v>44.71</v>
+        <v>43.45</v>
       </c>
       <c r="L76" t="n">
-        <v>94.45999999999999</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>37.52</v>
+        <v>37.99</v>
       </c>
       <c r="K77" t="n">
-        <v>-115.74</v>
+        <v>-117.19</v>
       </c>
       <c r="L77" t="n">
-        <v>121.67</v>
+        <v>123.2</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-111.8</v>
+        <v>-106.41</v>
       </c>
       <c r="K78" t="n">
-        <v>79.29000000000001</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>137.06</v>
+        <v>130.46</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>26</v>
       </c>
       <c r="J79" t="n">
-        <v>57.96</v>
+        <v>55.42</v>
       </c>
       <c r="K79" t="n">
-        <v>-49.76</v>
+        <v>-47.57</v>
       </c>
       <c r="L79" t="n">
-        <v>76.39</v>
+        <v>73.04000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-106.7</v>
+        <v>-110.64</v>
       </c>
       <c r="K80" t="n">
-        <v>-173.45</v>
+        <v>-179.85</v>
       </c>
       <c r="L80" t="n">
-        <v>203.64</v>
+        <v>211.16</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-193.86</v>
+        <v>-180.87</v>
       </c>
       <c r="K81" t="n">
-        <v>-38.01</v>
+        <v>-35.47</v>
       </c>
       <c r="L81" t="n">
-        <v>197.55</v>
+        <v>184.31</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>138.66</v>
+        <v>138.19</v>
       </c>
       <c r="K82" t="n">
-        <v>-37.11</v>
+        <v>-36.99</v>
       </c>
       <c r="L82" t="n">
-        <v>143.54</v>
+        <v>143.06</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-164.13</v>
+        <v>-155.11</v>
       </c>
       <c r="K83" t="n">
-        <v>-98.56999999999999</v>
+        <v>-93.15000000000001</v>
       </c>
       <c r="L83" t="n">
-        <v>191.45</v>
+        <v>180.93</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>226.09</v>
+        <v>223.32</v>
       </c>
       <c r="K84" t="n">
-        <v>-66.75</v>
+        <v>-65.94</v>
       </c>
       <c r="L84" t="n">
-        <v>235.73</v>
+        <v>232.85</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>21</v>
       </c>
       <c r="J85" t="n">
-        <v>214.15</v>
+        <v>228.04</v>
       </c>
       <c r="K85" t="n">
-        <v>-64.70999999999999</v>
+        <v>-68.91</v>
       </c>
       <c r="L85" t="n">
-        <v>223.71</v>
+        <v>238.23</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-225.91</v>
+        <v>-238.77</v>
       </c>
       <c r="K86" t="n">
-        <v>-438.92</v>
+        <v>-463.9</v>
       </c>
       <c r="L86" t="n">
-        <v>493.65</v>
+        <v>521.74</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>23.26</v>
+        <v>24.58</v>
       </c>
       <c r="K87" t="n">
-        <v>37.67</v>
+        <v>39.82</v>
       </c>
       <c r="L87" t="n">
-        <v>44.27</v>
+        <v>46.79</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>-256.68</v>
+        <v>-265.99</v>
       </c>
       <c r="K88" t="n">
-        <v>9.970000000000001</v>
+        <v>10.33</v>
       </c>
       <c r="L88" t="n">
-        <v>256.88</v>
+        <v>266.19</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-30.xlsx
+++ b/output/2024-04-30.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.22</v>
+        <v>2.97</v>
       </c>
       <c r="F14" t="n">
-        <v>12.85</v>
+        <v>8.07</v>
       </c>
       <c r="G14" t="n">
-        <v>246.3</v>
+        <v>261.8</v>
       </c>
       <c r="H14" t="n">
-        <v>83.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>-64.39</v>
+        <v>-26.78</v>
       </c>
       <c r="K14" t="n">
-        <v>87.04000000000001</v>
+        <v>-21.09</v>
       </c>
       <c r="L14" t="n">
-        <v>108.27</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:33:48</t>
+          <t>05:32:59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.29</v>
+        <v>4.64</v>
       </c>
       <c r="F15" t="n">
-        <v>9.41</v>
+        <v>13.36</v>
       </c>
       <c r="G15" t="n">
-        <v>252.1</v>
+        <v>262.8</v>
       </c>
       <c r="H15" t="n">
-        <v>80.59999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>107.14</v>
+        <v>-94.12</v>
       </c>
       <c r="K15" t="n">
-        <v>-45.71</v>
+        <v>-13.6</v>
       </c>
       <c r="L15" t="n">
-        <v>116.48</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:36:22</t>
+          <t>05:34:15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.72</v>
+        <v>4.18</v>
       </c>
       <c r="F16" t="n">
-        <v>13.1</v>
+        <v>14.38</v>
       </c>
       <c r="G16" t="n">
-        <v>253</v>
+        <v>250.5</v>
       </c>
       <c r="H16" t="n">
-        <v>82.8</v>
+        <v>57</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>-71.14</v>
+        <v>59.88</v>
       </c>
       <c r="K16" t="n">
-        <v>72.28</v>
+        <v>-44.02</v>
       </c>
       <c r="L16" t="n">
-        <v>101.42</v>
+        <v>74.31999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:41:49</t>
+          <t>05:39:04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.03</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>12.23</v>
+        <v>13.13</v>
       </c>
       <c r="G17" t="n">
-        <v>254.2</v>
+        <v>261.9</v>
       </c>
       <c r="H17" t="n">
-        <v>77.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>109.71</v>
+        <v>-73.02</v>
       </c>
       <c r="K17" t="n">
-        <v>39.51</v>
+        <v>-143.58</v>
       </c>
       <c r="L17" t="n">
-        <v>116.61</v>
+        <v>161.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:43:34</t>
+          <t>05:39:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.56</v>
+        <v>4.49</v>
       </c>
       <c r="F18" t="n">
-        <v>11.37</v>
+        <v>15.87</v>
       </c>
       <c r="G18" t="n">
-        <v>255.5</v>
+        <v>259.8</v>
       </c>
       <c r="H18" t="n">
-        <v>81.2</v>
+        <v>86.3</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-76.58</v>
+        <v>-148.21</v>
       </c>
       <c r="K18" t="n">
-        <v>-19.47</v>
+        <v>-163.86</v>
       </c>
       <c r="L18" t="n">
-        <v>79.02</v>
+        <v>220.94</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:45:01</t>
+          <t>05:42:14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.99</v>
+        <v>3.81</v>
       </c>
       <c r="F19" t="n">
-        <v>11.91</v>
+        <v>6.8</v>
       </c>
       <c r="G19" t="n">
-        <v>254.8</v>
+        <v>252.4</v>
       </c>
       <c r="H19" t="n">
-        <v>79.7</v>
+        <v>52.2</v>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J19" t="n">
-        <v>-13.76</v>
+        <v>-25.9</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.14</v>
+        <v>102.77</v>
       </c>
       <c r="L19" t="n">
-        <v>13.92</v>
+        <v>105.98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:48:03</t>
+          <t>05:47:35</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.62</v>
+        <v>4.21</v>
       </c>
       <c r="F20" t="n">
-        <v>9.48</v>
+        <v>10.32</v>
       </c>
       <c r="G20" t="n">
-        <v>257.8</v>
+        <v>250.7</v>
       </c>
       <c r="H20" t="n">
-        <v>80.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>73.25</v>
+        <v>61.96</v>
       </c>
       <c r="K20" t="n">
-        <v>-66.84</v>
+        <v>127.65</v>
       </c>
       <c r="L20" t="n">
-        <v>99.17</v>
+        <v>141.89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:48:47</t>
+          <t>05:49:11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.96</v>
+        <v>4.43</v>
       </c>
       <c r="F21" t="n">
-        <v>10.14</v>
+        <v>14.54</v>
       </c>
       <c r="G21" t="n">
-        <v>266.8</v>
+        <v>260.2</v>
       </c>
       <c r="H21" t="n">
-        <v>79.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>-16.22</v>
+        <v>-137.05</v>
       </c>
       <c r="K21" t="n">
-        <v>-118.58</v>
+        <v>10.74</v>
       </c>
       <c r="L21" t="n">
-        <v>119.68</v>
+        <v>137.47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:50:29</t>
+          <t>05:51:44</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.96</v>
+        <v>3.96</v>
       </c>
       <c r="F22" t="n">
-        <v>13.89</v>
+        <v>11.76</v>
       </c>
       <c r="G22" t="n">
-        <v>259.4</v>
+        <v>238.7</v>
       </c>
       <c r="H22" t="n">
-        <v>84</v>
+        <v>54.4</v>
       </c>
       <c r="I22" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J22" t="n">
-        <v>-125.96</v>
+        <v>24.34</v>
       </c>
       <c r="K22" t="n">
-        <v>58.35</v>
+        <v>-108.16</v>
       </c>
       <c r="L22" t="n">
-        <v>138.82</v>
+        <v>110.86</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:55:32</t>
+          <t>05:56:10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.99</v>
+        <v>4.53</v>
       </c>
       <c r="F23" t="n">
-        <v>11.05</v>
+        <v>14.61</v>
       </c>
       <c r="G23" t="n">
-        <v>255.5</v>
+        <v>264.3</v>
       </c>
       <c r="H23" t="n">
-        <v>85.09999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="I23" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J23" t="n">
-        <v>-107.03</v>
+        <v>-210.65</v>
       </c>
       <c r="K23" t="n">
-        <v>-196.1</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>223.4</v>
+        <v>222.71</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:57:19</t>
+          <t>05:58:01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.78</v>
+        <v>4.9</v>
       </c>
       <c r="F24" t="n">
-        <v>14.54</v>
+        <v>11.68</v>
       </c>
       <c r="G24" t="n">
-        <v>253.4</v>
+        <v>251.6</v>
       </c>
       <c r="H24" t="n">
-        <v>81.5</v>
+        <v>52.5</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-169.74</v>
+        <v>123.95</v>
       </c>
       <c r="K24" t="n">
-        <v>247.73</v>
+        <v>251.64</v>
       </c>
       <c r="L24" t="n">
-        <v>300.3</v>
+        <v>280.51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:58:26</t>
+          <t>05:58:54</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.19</v>
+        <v>4.26</v>
       </c>
       <c r="F25" t="n">
-        <v>14.2</v>
+        <v>6.89</v>
       </c>
       <c r="G25" t="n">
-        <v>248.7</v>
+        <v>245.4</v>
       </c>
       <c r="H25" t="n">
-        <v>75.90000000000001</v>
+        <v>57.3</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-51.53</v>
+        <v>-154.29</v>
       </c>
       <c r="K25" t="n">
-        <v>339.26</v>
+        <v>-121.65</v>
       </c>
       <c r="L25" t="n">
-        <v>343.15</v>
+        <v>196.48</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:02:46</t>
+          <t>06:03:20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="F26" t="n">
-        <v>11.82</v>
+        <v>11.5</v>
       </c>
       <c r="G26" t="n">
-        <v>255</v>
+        <v>257.8</v>
       </c>
       <c r="H26" t="n">
-        <v>78.59999999999999</v>
+        <v>22.3</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J26" t="n">
-        <v>-119.32</v>
+        <v>-284.61</v>
       </c>
       <c r="K26" t="n">
-        <v>173.88</v>
+        <v>-53.43</v>
       </c>
       <c r="L26" t="n">
-        <v>210.88</v>
+        <v>289.58</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:03:54</t>
+          <t>06:05:01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.45</v>
+        <v>4.86</v>
       </c>
       <c r="F27" t="n">
-        <v>15.01</v>
+        <v>11.62</v>
       </c>
       <c r="G27" t="n">
-        <v>244.7</v>
+        <v>258.8</v>
       </c>
       <c r="H27" t="n">
-        <v>78.90000000000001</v>
+        <v>55.6</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-270.15</v>
+        <v>-160.7</v>
       </c>
       <c r="K27" t="n">
-        <v>37.83</v>
+        <v>-307</v>
       </c>
       <c r="L27" t="n">
-        <v>272.78</v>
+        <v>346.51</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:05:04</t>
+          <t>06:06:16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="F28" t="n">
-        <v>9.42</v>
+        <v>12.01</v>
       </c>
       <c r="G28" t="n">
-        <v>252.2</v>
+        <v>256.4</v>
       </c>
       <c r="H28" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-310.24</v>
+        <v>-305.89</v>
       </c>
       <c r="K28" t="n">
-        <v>-115.93</v>
+        <v>65.88</v>
       </c>
       <c r="L28" t="n">
-        <v>331.19</v>
+        <v>312.91</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:14:38</t>
+          <t>06:16:16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.76</v>
+        <v>4.09</v>
       </c>
       <c r="F29" t="n">
-        <v>11.96</v>
+        <v>11.17</v>
       </c>
       <c r="G29" t="n">
-        <v>258.4</v>
+        <v>264.2</v>
       </c>
       <c r="H29" t="n">
-        <v>76.90000000000001</v>
+        <v>37</v>
       </c>
       <c r="I29" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>-46.91</v>
+        <v>-28.56</v>
       </c>
       <c r="K29" t="n">
-        <v>67.06999999999999</v>
+        <v>75.66</v>
       </c>
       <c r="L29" t="n">
-        <v>81.84999999999999</v>
+        <v>80.87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:16:55</t>
+          <t>06:18:40</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.75</v>
+        <v>4.3</v>
       </c>
       <c r="F30" t="n">
-        <v>15.11</v>
+        <v>13.31</v>
       </c>
       <c r="G30" t="n">
-        <v>264.9</v>
+        <v>234.1</v>
       </c>
       <c r="H30" t="n">
-        <v>70.7</v>
+        <v>44.6</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>72.06999999999999</v>
+        <v>-59.01</v>
       </c>
       <c r="K30" t="n">
-        <v>28.96</v>
+        <v>57.78</v>
       </c>
       <c r="L30" t="n">
-        <v>77.67</v>
+        <v>82.59</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:18:48</t>
+          <t>06:20:29</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.39</v>
+        <v>4.36</v>
       </c>
       <c r="F31" t="n">
-        <v>13.11</v>
+        <v>11.34</v>
       </c>
       <c r="G31" t="n">
-        <v>241.4</v>
+        <v>265.5</v>
       </c>
       <c r="H31" t="n">
-        <v>82.09999999999999</v>
+        <v>35.4</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>93.36</v>
+        <v>-23.58</v>
       </c>
       <c r="K31" t="n">
-        <v>-30.56</v>
+        <v>-79.22</v>
       </c>
       <c r="L31" t="n">
-        <v>98.23999999999999</v>
+        <v>82.66</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:22:33</t>
+          <t>06:26:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.28</v>
+        <v>4.11</v>
       </c>
       <c r="F32" t="n">
-        <v>12.78</v>
+        <v>11.09</v>
       </c>
       <c r="G32" t="n">
-        <v>252.6</v>
+        <v>243.4</v>
       </c>
       <c r="H32" t="n">
-        <v>75.7</v>
+        <v>48.1</v>
       </c>
       <c r="I32" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>-61.54</v>
+        <v>3.14</v>
       </c>
       <c r="K32" t="n">
-        <v>58.15</v>
+        <v>-96.04000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>84.67</v>
+        <v>96.09</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:23:43</t>
+          <t>06:27:19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="F33" t="n">
-        <v>13.78</v>
+        <v>12.27</v>
       </c>
       <c r="G33" t="n">
-        <v>262.5</v>
+        <v>254.3</v>
       </c>
       <c r="H33" t="n">
-        <v>77.7</v>
+        <v>45.3</v>
       </c>
       <c r="I33" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-94.93000000000001</v>
+        <v>23.39</v>
       </c>
       <c r="K33" t="n">
-        <v>-10.75</v>
+        <v>-107.02</v>
       </c>
       <c r="L33" t="n">
-        <v>95.54000000000001</v>
+        <v>109.54</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:25:06</t>
+          <t>06:28:56</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>5.03</v>
+        <v>4.6</v>
       </c>
       <c r="F34" t="n">
-        <v>15.87</v>
+        <v>12.43</v>
       </c>
       <c r="G34" t="n">
-        <v>244.1</v>
+        <v>262.7</v>
       </c>
       <c r="H34" t="n">
-        <v>81.7</v>
+        <v>52.8</v>
       </c>
       <c r="I34" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-77.5</v>
+        <v>-53.79</v>
       </c>
       <c r="K34" t="n">
-        <v>-88.25</v>
+        <v>162.97</v>
       </c>
       <c r="L34" t="n">
-        <v>117.45</v>
+        <v>171.62</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:29:46</t>
+          <t>06:33:25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.52</v>
+        <v>4.32</v>
       </c>
       <c r="F35" t="n">
-        <v>14.53</v>
+        <v>13.82</v>
       </c>
       <c r="G35" t="n">
-        <v>246.2</v>
+        <v>252.7</v>
       </c>
       <c r="H35" t="n">
-        <v>80.7</v>
+        <v>38.9</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>-155.72</v>
+        <v>-68.09999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>-187.01</v>
+        <v>-97.09999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>243.35</v>
+        <v>118.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:31:08</t>
+          <t>06:35:04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.75</v>
+        <v>5.52</v>
       </c>
       <c r="F36" t="n">
-        <v>15.14</v>
+        <v>15.87</v>
       </c>
       <c r="G36" t="n">
-        <v>249.1</v>
+        <v>258.7</v>
       </c>
       <c r="H36" t="n">
-        <v>83</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>-91.73999999999999</v>
+        <v>-188.66</v>
       </c>
       <c r="K36" t="n">
-        <v>-191.51</v>
+        <v>-86.23</v>
       </c>
       <c r="L36" t="n">
-        <v>212.35</v>
+        <v>207.43</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:32:22</t>
+          <t>06:37:15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.49</v>
+        <v>3.97</v>
       </c>
       <c r="F37" t="n">
-        <v>12.08</v>
+        <v>14.64</v>
       </c>
       <c r="G37" t="n">
-        <v>257.2</v>
+        <v>244.2</v>
       </c>
       <c r="H37" t="n">
-        <v>72.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I37" t="n">
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>123.66</v>
+        <v>-91.01000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>45.92</v>
+        <v>73.05</v>
       </c>
       <c r="L37" t="n">
-        <v>131.91</v>
+        <v>116.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:37:17</t>
+          <t>06:42:12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.62</v>
+        <v>4.89</v>
       </c>
       <c r="F38" t="n">
-        <v>11.92</v>
+        <v>15.87</v>
       </c>
       <c r="G38" t="n">
-        <v>268.3</v>
+        <v>267</v>
       </c>
       <c r="H38" t="n">
-        <v>82.3</v>
+        <v>30.6</v>
       </c>
       <c r="I38" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-187.85</v>
+        <v>-202.87</v>
       </c>
       <c r="K38" t="n">
-        <v>47.36</v>
+        <v>-156.22</v>
       </c>
       <c r="L38" t="n">
-        <v>193.72</v>
+        <v>256.05</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:38:15</t>
+          <t>06:44:05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>5.53</v>
+        <v>5.01</v>
       </c>
       <c r="F39" t="n">
-        <v>15.87</v>
+        <v>14.79</v>
       </c>
       <c r="G39" t="n">
-        <v>259.1</v>
+        <v>244.9</v>
       </c>
       <c r="H39" t="n">
-        <v>78.40000000000001</v>
+        <v>37.3</v>
       </c>
       <c r="I39" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-207.55</v>
+        <v>49.02</v>
       </c>
       <c r="K39" t="n">
-        <v>-158.49</v>
+        <v>-196.41</v>
       </c>
       <c r="L39" t="n">
-        <v>261.14</v>
+        <v>202.44</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:39:16</t>
+          <t>06:46:23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.9</v>
+        <v>4.23</v>
       </c>
       <c r="F40" t="n">
-        <v>15.87</v>
+        <v>13.04</v>
       </c>
       <c r="G40" t="n">
-        <v>255.2</v>
+        <v>263</v>
       </c>
       <c r="H40" t="n">
-        <v>85.8</v>
+        <v>10.8</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>178.13</v>
+        <v>-145.22</v>
       </c>
       <c r="K40" t="n">
-        <v>112.85</v>
+        <v>96.52</v>
       </c>
       <c r="L40" t="n">
-        <v>210.87</v>
+        <v>174.36</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:43:45</t>
+          <t>06:50:51</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.05</v>
+        <v>3.91</v>
       </c>
       <c r="F41" t="n">
-        <v>12.56</v>
+        <v>12.54</v>
       </c>
       <c r="G41" t="n">
-        <v>262.7</v>
+        <v>249.3</v>
       </c>
       <c r="H41" t="n">
-        <v>78.5</v>
+        <v>77.3</v>
       </c>
       <c r="I41" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>147.95</v>
+        <v>-105.17</v>
       </c>
       <c r="K41" t="n">
-        <v>-314.32</v>
+        <v>316.12</v>
       </c>
       <c r="L41" t="n">
-        <v>347.4</v>
+        <v>333.16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:45:01</t>
+          <t>06:52:02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.6</v>
+        <v>4.46</v>
       </c>
       <c r="F42" t="n">
-        <v>10.57</v>
+        <v>13.53</v>
       </c>
       <c r="G42" t="n">
-        <v>247.4</v>
+        <v>259.4</v>
       </c>
       <c r="H42" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="I42" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>280.39</v>
+        <v>-112.34</v>
       </c>
       <c r="K42" t="n">
-        <v>416.36</v>
+        <v>-333.57</v>
       </c>
       <c r="L42" t="n">
-        <v>501.97</v>
+        <v>351.98</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:47:35</t>
+          <t>06:54:32</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.14</v>
+        <v>4.5</v>
       </c>
       <c r="F43" t="n">
-        <v>12.97</v>
+        <v>12.27</v>
       </c>
       <c r="G43" t="n">
-        <v>256.5</v>
+        <v>266.5</v>
       </c>
       <c r="H43" t="n">
-        <v>80.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>177.34</v>
+        <v>22.94</v>
       </c>
       <c r="K43" t="n">
-        <v>-286.7</v>
+        <v>306.6</v>
       </c>
       <c r="L43" t="n">
-        <v>337.11</v>
+        <v>307.46</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:00:12</t>
+          <t>07:07:03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.91</v>
+        <v>5.41</v>
       </c>
       <c r="F44" t="n">
-        <v>14.88</v>
+        <v>15.87</v>
       </c>
       <c r="G44" t="n">
-        <v>255.6</v>
+        <v>258.2</v>
       </c>
       <c r="H44" t="n">
-        <v>83.09999999999999</v>
+        <v>29.2</v>
       </c>
       <c r="I44" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J44" t="n">
-        <v>3.49</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>-118.19</v>
+        <v>109.58</v>
       </c>
       <c r="L44" t="n">
-        <v>118.24</v>
+        <v>109.93</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:01:58</t>
+          <t>07:07:49</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.53</v>
+        <v>4.54</v>
       </c>
       <c r="F45" t="n">
-        <v>11.12</v>
+        <v>15.87</v>
       </c>
       <c r="G45" t="n">
-        <v>253.9</v>
+        <v>244.9</v>
       </c>
       <c r="H45" t="n">
-        <v>80.59999999999999</v>
+        <v>56.5</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>16.91</v>
+        <v>-29.26</v>
       </c>
       <c r="K45" t="n">
-        <v>68.68000000000001</v>
+        <v>-63.49</v>
       </c>
       <c r="L45" t="n">
-        <v>70.73999999999999</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:03:10</t>
+          <t>07:10:10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.81</v>
+        <v>4.32</v>
       </c>
       <c r="F46" t="n">
-        <v>10.61</v>
+        <v>12.01</v>
       </c>
       <c r="G46" t="n">
-        <v>250.7</v>
+        <v>248.3</v>
       </c>
       <c r="H46" t="n">
-        <v>78.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-69.05</v>
+        <v>4.89</v>
       </c>
       <c r="K46" t="n">
-        <v>14.45</v>
+        <v>-97.83</v>
       </c>
       <c r="L46" t="n">
-        <v>70.54000000000001</v>
+        <v>97.95</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:08:56</t>
+          <t>07:14:16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5.44</v>
+        <v>5.29</v>
       </c>
       <c r="F47" t="n">
         <v>15.87</v>
       </c>
       <c r="G47" t="n">
-        <v>268.6</v>
+        <v>259.5</v>
       </c>
       <c r="H47" t="n">
-        <v>76.40000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>101.88</v>
+        <v>121.14</v>
       </c>
       <c r="K47" t="n">
-        <v>46.23</v>
+        <v>49.25</v>
       </c>
       <c r="L47" t="n">
-        <v>111.88</v>
+        <v>130.77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:10:55</t>
+          <t>07:15:56</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.74</v>
+        <v>4.42</v>
       </c>
       <c r="F48" t="n">
-        <v>12.81</v>
+        <v>11.11</v>
       </c>
       <c r="G48" t="n">
-        <v>261.3</v>
+        <v>254.5</v>
       </c>
       <c r="H48" t="n">
-        <v>78.90000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-73.87</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-45.76</v>
+        <v>76.5</v>
       </c>
       <c r="L48" t="n">
-        <v>86.90000000000001</v>
+        <v>109.48</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:13:03</t>
+          <t>07:18:02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>5.05</v>
+        <v>5.67</v>
       </c>
       <c r="F49" t="n">
-        <v>13.66</v>
+        <v>15.87</v>
       </c>
       <c r="G49" t="n">
-        <v>266.3</v>
+        <v>233.6</v>
       </c>
       <c r="H49" t="n">
-        <v>80.09999999999999</v>
+        <v>17.6</v>
       </c>
       <c r="I49" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>-103.55</v>
+        <v>44.65</v>
       </c>
       <c r="K49" t="n">
-        <v>-20.46</v>
+        <v>152.9</v>
       </c>
       <c r="L49" t="n">
-        <v>105.55</v>
+        <v>159.29</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:16:27</t>
+          <t>07:22:42</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.21</v>
+        <v>5.59</v>
       </c>
       <c r="F50" t="n">
-        <v>15.25</v>
+        <v>15.6</v>
       </c>
       <c r="G50" t="n">
-        <v>241.1</v>
+        <v>253.3</v>
       </c>
       <c r="H50" t="n">
-        <v>72.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J50" t="n">
-        <v>15.2</v>
+        <v>-129.19</v>
       </c>
       <c r="K50" t="n">
-        <v>124.53</v>
+        <v>-189.8</v>
       </c>
       <c r="L50" t="n">
-        <v>125.46</v>
+        <v>229.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:18:34</t>
+          <t>07:23:44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.83</v>
+        <v>4.52</v>
       </c>
       <c r="F51" t="n">
-        <v>15.29</v>
+        <v>7.93</v>
       </c>
       <c r="G51" t="n">
-        <v>263.6</v>
+        <v>269.2</v>
       </c>
       <c r="H51" t="n">
-        <v>71.5</v>
+        <v>81.8</v>
       </c>
       <c r="I51" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J51" t="n">
-        <v>47.75</v>
+        <v>-144.97</v>
       </c>
       <c r="K51" t="n">
-        <v>-148.54</v>
+        <v>-2.27</v>
       </c>
       <c r="L51" t="n">
-        <v>156.03</v>
+        <v>144.99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:19:36</t>
+          <t>07:24:51</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.64</v>
+        <v>5.65</v>
       </c>
       <c r="F52" t="n">
-        <v>15.75</v>
+        <v>15.87</v>
       </c>
       <c r="G52" t="n">
-        <v>254.3</v>
+        <v>266.5</v>
       </c>
       <c r="H52" t="n">
-        <v>72.3</v>
+        <v>31.3</v>
       </c>
       <c r="I52" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>40.98</v>
+        <v>-207.81</v>
       </c>
       <c r="K52" t="n">
-        <v>124.38</v>
+        <v>-85.25</v>
       </c>
       <c r="L52" t="n">
-        <v>130.96</v>
+        <v>224.61</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:24:54</t>
+          <t>07:29:30</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.23</v>
+        <v>4.04</v>
       </c>
       <c r="F53" t="n">
-        <v>15.87</v>
+        <v>11.81</v>
       </c>
       <c r="G53" t="n">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="H53" t="n">
-        <v>72</v>
+        <v>53.1</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-135.34</v>
+        <v>-67.63</v>
       </c>
       <c r="K53" t="n">
-        <v>-267.42</v>
+        <v>-165.51</v>
       </c>
       <c r="L53" t="n">
-        <v>299.72</v>
+        <v>178.79</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:27:02</t>
+          <t>07:30:09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>5.08</v>
+        <v>3.93</v>
       </c>
       <c r="F54" t="n">
-        <v>14.74</v>
+        <v>13.08</v>
       </c>
       <c r="G54" t="n">
-        <v>259.8</v>
+        <v>252.3</v>
       </c>
       <c r="H54" t="n">
-        <v>78.40000000000001</v>
+        <v>49.6</v>
       </c>
       <c r="I54" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-202.71</v>
+        <v>-150.76</v>
       </c>
       <c r="K54" t="n">
-        <v>5.28</v>
+        <v>74.27</v>
       </c>
       <c r="L54" t="n">
-        <v>202.77</v>
+        <v>168.06</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:29:07</t>
+          <t>07:31:45</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>5.12</v>
+        <v>4.52</v>
       </c>
       <c r="F55" t="n">
-        <v>12.52</v>
+        <v>15.11</v>
       </c>
       <c r="G55" t="n">
-        <v>262.3</v>
+        <v>254.8</v>
       </c>
       <c r="H55" t="n">
-        <v>74.3</v>
+        <v>40.1</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-216.81</v>
+        <v>174.01</v>
       </c>
       <c r="K55" t="n">
-        <v>-130.14</v>
+        <v>54.1</v>
       </c>
       <c r="L55" t="n">
-        <v>252.87</v>
+        <v>182.22</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:35:01</t>
+          <t>07:37:22</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.67</v>
+        <v>4.92</v>
       </c>
       <c r="F56" t="n">
-        <v>14.77</v>
+        <v>15.87</v>
       </c>
       <c r="G56" t="n">
-        <v>243.5</v>
+        <v>254.4</v>
       </c>
       <c r="H56" t="n">
-        <v>78.59999999999999</v>
+        <v>36.6</v>
       </c>
       <c r="I56" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>-141.64</v>
+        <v>-298.25</v>
       </c>
       <c r="K56" t="n">
-        <v>338.91</v>
+        <v>-199.77</v>
       </c>
       <c r="L56" t="n">
-        <v>367.31</v>
+        <v>358.97</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:35:49</t>
+          <t>07:39:26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.39</v>
+        <v>4</v>
       </c>
       <c r="F57" t="n">
-        <v>13.02</v>
+        <v>11.52</v>
       </c>
       <c r="G57" t="n">
-        <v>252.5</v>
+        <v>243.7</v>
       </c>
       <c r="H57" t="n">
-        <v>79.2</v>
+        <v>50.5</v>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J57" t="n">
-        <v>288.62</v>
+        <v>-245.36</v>
       </c>
       <c r="K57" t="n">
-        <v>-241.15</v>
+        <v>54.19</v>
       </c>
       <c r="L57" t="n">
-        <v>376.11</v>
+        <v>251.27</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:37:35</t>
+          <t>07:41:08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.39</v>
+        <v>4.13</v>
       </c>
       <c r="F58" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="G58" t="n">
-        <v>259.1</v>
+        <v>242.9</v>
       </c>
       <c r="H58" t="n">
-        <v>83.7</v>
+        <v>61.3</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>120.09</v>
+        <v>-184.76</v>
       </c>
       <c r="K58" t="n">
-        <v>-171.97</v>
+        <v>205.63</v>
       </c>
       <c r="L58" t="n">
-        <v>209.74</v>
+        <v>276.45</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:48:01</t>
+          <t>07:51:59</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.28</v>
+        <v>4.53</v>
       </c>
       <c r="F59" t="n">
-        <v>11.11</v>
+        <v>13.46</v>
       </c>
       <c r="G59" t="n">
-        <v>265.9</v>
+        <v>249.6</v>
       </c>
       <c r="H59" t="n">
-        <v>81.8</v>
+        <v>16.7</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>77.26000000000001</v>
+        <v>36.47</v>
       </c>
       <c r="K59" t="n">
-        <v>-26.75</v>
+        <v>114.31</v>
       </c>
       <c r="L59" t="n">
-        <v>81.76000000000001</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:49:41</t>
+          <t>07:53:55</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.55</v>
+        <v>5.11</v>
       </c>
       <c r="F60" t="n">
-        <v>12.98</v>
+        <v>15.87</v>
       </c>
       <c r="G60" t="n">
-        <v>245.6</v>
+        <v>268.9</v>
       </c>
       <c r="H60" t="n">
-        <v>79.7</v>
+        <v>91.3</v>
       </c>
       <c r="I60" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>45.52</v>
+        <v>-97.98999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>67.45</v>
+        <v>-24.24</v>
       </c>
       <c r="L60" t="n">
-        <v>81.38</v>
+        <v>100.95</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:52:25</t>
+          <t>07:55:21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.33</v>
+        <v>4.46</v>
       </c>
       <c r="F61" t="n">
-        <v>12.08</v>
+        <v>9.25</v>
       </c>
       <c r="G61" t="n">
-        <v>260.6</v>
+        <v>257.7</v>
       </c>
       <c r="H61" t="n">
-        <v>84.3</v>
+        <v>52.7</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>94.02</v>
+        <v>83.06</v>
       </c>
       <c r="K61" t="n">
-        <v>-36.16</v>
+        <v>-53.45</v>
       </c>
       <c r="L61" t="n">
-        <v>100.73</v>
+        <v>98.77</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:55:43</t>
+          <t>07:59:22</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.35</v>
+        <v>4.89</v>
       </c>
       <c r="F62" t="n">
-        <v>12.65</v>
+        <v>12.69</v>
       </c>
       <c r="G62" t="n">
-        <v>252.4</v>
+        <v>265.7</v>
       </c>
       <c r="H62" t="n">
-        <v>69.2</v>
+        <v>51.4</v>
       </c>
       <c r="I62" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>72.66</v>
+        <v>24.97</v>
       </c>
       <c r="K62" t="n">
-        <v>34.14</v>
+        <v>137.48</v>
       </c>
       <c r="L62" t="n">
-        <v>80.28</v>
+        <v>139.73</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:57:41</t>
+          <t>08:01:01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.52</v>
+        <v>4.55</v>
       </c>
       <c r="F63" t="n">
-        <v>14.92</v>
+        <v>11.58</v>
       </c>
       <c r="G63" t="n">
-        <v>236.3</v>
+        <v>245.2</v>
       </c>
       <c r="H63" t="n">
-        <v>76.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="I63" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-83.65000000000001</v>
+        <v>-65.39</v>
       </c>
       <c r="K63" t="n">
-        <v>1.15</v>
+        <v>-66.06999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>83.66</v>
+        <v>92.95</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:58:56</t>
+          <t>08:02:44</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.38</v>
+        <v>4.82</v>
       </c>
       <c r="F64" t="n">
-        <v>11.04</v>
+        <v>15.87</v>
       </c>
       <c r="G64" t="n">
-        <v>257.5</v>
+        <v>245.7</v>
       </c>
       <c r="H64" t="n">
-        <v>79.3</v>
+        <v>50.9</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-6.85</v>
+        <v>98.5</v>
       </c>
       <c r="K64" t="n">
-        <v>-113.48</v>
+        <v>-1.22</v>
       </c>
       <c r="L64" t="n">
-        <v>113.68</v>
+        <v>98.51000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:02:41</t>
+          <t>08:06:02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.53</v>
+        <v>4.48</v>
       </c>
       <c r="F65" t="n">
-        <v>12.98</v>
+        <v>10.72</v>
       </c>
       <c r="G65" t="n">
-        <v>260.6</v>
+        <v>252.7</v>
       </c>
       <c r="H65" t="n">
-        <v>84.3</v>
+        <v>50.5</v>
       </c>
       <c r="I65" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>64.91</v>
+        <v>-99.55</v>
       </c>
       <c r="K65" t="n">
-        <v>95.70999999999999</v>
+        <v>104</v>
       </c>
       <c r="L65" t="n">
-        <v>115.65</v>
+        <v>143.97</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:04:25</t>
+          <t>08:07:50</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.46</v>
+        <v>5.48</v>
       </c>
       <c r="F66" t="n">
-        <v>13.22</v>
+        <v>15.18</v>
       </c>
       <c r="G66" t="n">
-        <v>257.7</v>
+        <v>255.1</v>
       </c>
       <c r="H66" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="I66" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-103.36</v>
+        <v>-119.75</v>
       </c>
       <c r="K66" t="n">
-        <v>-20</v>
+        <v>190.47</v>
       </c>
       <c r="L66" t="n">
-        <v>105.28</v>
+        <v>224.99</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:05:58</t>
+          <t>08:08:41</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="F67" t="n">
-        <v>13.56</v>
+        <v>15.87</v>
       </c>
       <c r="G67" t="n">
-        <v>244.9</v>
+        <v>250.4</v>
       </c>
       <c r="H67" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="I67" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J67" t="n">
-        <v>-202.31</v>
+        <v>57.24</v>
       </c>
       <c r="K67" t="n">
-        <v>36.77</v>
+        <v>-147.94</v>
       </c>
       <c r="L67" t="n">
-        <v>205.62</v>
+        <v>158.63</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:11:00</t>
+          <t>08:12:39</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.3</v>
+        <v>5.35</v>
       </c>
       <c r="F68" t="n">
-        <v>13.72</v>
+        <v>15.87</v>
       </c>
       <c r="G68" t="n">
-        <v>244.5</v>
+        <v>255.2</v>
       </c>
       <c r="H68" t="n">
-        <v>81</v>
+        <v>48.6</v>
       </c>
       <c r="I68" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>141.35</v>
+        <v>-279.5</v>
       </c>
       <c r="K68" t="n">
-        <v>166.49</v>
+        <v>88.42</v>
       </c>
       <c r="L68" t="n">
-        <v>218.4</v>
+        <v>293.15</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:12:38</t>
+          <t>08:15:22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.28</v>
+        <v>5.09</v>
       </c>
       <c r="F69" t="n">
-        <v>14.27</v>
+        <v>15.87</v>
       </c>
       <c r="G69" t="n">
-        <v>258.6</v>
+        <v>249.5</v>
       </c>
       <c r="H69" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="I69" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-177.39</v>
+        <v>271.8</v>
       </c>
       <c r="K69" t="n">
-        <v>26.71</v>
+        <v>-147.18</v>
       </c>
       <c r="L69" t="n">
-        <v>179.39</v>
+        <v>309.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:13:49</t>
+          <t>08:16:09</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.96</v>
+        <v>5.56</v>
       </c>
       <c r="F70" t="n">
-        <v>14.06</v>
+        <v>15.87</v>
       </c>
       <c r="G70" t="n">
-        <v>267.1</v>
+        <v>253.4</v>
       </c>
       <c r="H70" t="n">
-        <v>73.2</v>
+        <v>13.9</v>
       </c>
       <c r="I70" t="n">
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>8.58</v>
+        <v>-242.96</v>
       </c>
       <c r="K70" t="n">
-        <v>-240.73</v>
+        <v>232.06</v>
       </c>
       <c r="L70" t="n">
-        <v>240.88</v>
+        <v>335.98</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:17:31</t>
+          <t>08:19:35</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.52</v>
+        <v>3.86</v>
       </c>
       <c r="F71" t="n">
-        <v>15.87</v>
+        <v>11.18</v>
       </c>
       <c r="G71" t="n">
-        <v>255.7</v>
+        <v>263.9</v>
       </c>
       <c r="H71" t="n">
-        <v>78.09999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-148.41</v>
+        <v>-123.35</v>
       </c>
       <c r="K71" t="n">
-        <v>-337.46</v>
+        <v>251.51</v>
       </c>
       <c r="L71" t="n">
-        <v>368.65</v>
+        <v>280.12</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:18:21</t>
+          <t>08:21:20</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>5.14</v>
+        <v>4.6</v>
       </c>
       <c r="F72" t="n">
-        <v>15.52</v>
+        <v>13.97</v>
       </c>
       <c r="G72" t="n">
-        <v>250.3</v>
+        <v>240.6</v>
       </c>
       <c r="H72" t="n">
-        <v>80.2</v>
+        <v>36.2</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>345.39</v>
+        <v>-318.97</v>
       </c>
       <c r="K72" t="n">
-        <v>134.29</v>
+        <v>-24.02</v>
       </c>
       <c r="L72" t="n">
-        <v>370.58</v>
+        <v>319.88</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:20:01</t>
+          <t>08:23:25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>5.09</v>
+        <v>4.81</v>
       </c>
       <c r="F73" t="n">
-        <v>13.66</v>
+        <v>15.87</v>
       </c>
       <c r="G73" t="n">
-        <v>249.6</v>
+        <v>262.4</v>
       </c>
       <c r="H73" t="n">
-        <v>79.2</v>
+        <v>68.5</v>
       </c>
       <c r="I73" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-148.7</v>
+        <v>-321.48</v>
       </c>
       <c r="K73" t="n">
-        <v>-299.35</v>
+        <v>-112.68</v>
       </c>
       <c r="L73" t="n">
-        <v>334.25</v>
+        <v>340.66</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:32:21</t>
+          <t>08:33:40</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.95</v>
+        <v>5.44</v>
       </c>
       <c r="F74" t="n">
-        <v>15.87</v>
+        <v>14.06</v>
       </c>
       <c r="G74" t="n">
-        <v>257.8</v>
+        <v>255.7</v>
       </c>
       <c r="H74" t="n">
-        <v>80.2</v>
+        <v>54.9</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>-27.14</v>
+        <v>90.02</v>
       </c>
       <c r="K74" t="n">
-        <v>-79.06</v>
+        <v>-27.04</v>
       </c>
       <c r="L74" t="n">
-        <v>83.59</v>
+        <v>94</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:33:08</t>
+          <t>08:34:24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.05</v>
+        <v>5.08</v>
       </c>
       <c r="F75" t="n">
         <v>15.87</v>
       </c>
       <c r="G75" t="n">
-        <v>257.1</v>
+        <v>247.9</v>
       </c>
       <c r="H75" t="n">
-        <v>81.09999999999999</v>
+        <v>41.1</v>
       </c>
       <c r="I75" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-77.43000000000001</v>
+        <v>-48.69</v>
       </c>
       <c r="K75" t="n">
-        <v>-13.49</v>
+        <v>-96.91</v>
       </c>
       <c r="L75" t="n">
-        <v>78.59999999999999</v>
+        <v>108.46</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:35:12</t>
+          <t>08:36:18</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.97</v>
+        <v>6.04</v>
       </c>
       <c r="F76" t="n">
         <v>15.87</v>
       </c>
       <c r="G76" t="n">
-        <v>248.6</v>
+        <v>257.5</v>
       </c>
       <c r="H76" t="n">
-        <v>82.3</v>
+        <v>100</v>
       </c>
       <c r="I76" t="n">
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>80.86</v>
+        <v>-120.21</v>
       </c>
       <c r="K76" t="n">
-        <v>43.45</v>
+        <v>-19.4</v>
       </c>
       <c r="L76" t="n">
-        <v>91.8</v>
+        <v>121.77</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:39:50</t>
+          <t>08:41:20</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.77</v>
+        <v>5.66</v>
       </c>
       <c r="F77" t="n">
-        <v>14.51</v>
+        <v>15.87</v>
       </c>
       <c r="G77" t="n">
-        <v>274.4</v>
+        <v>259</v>
       </c>
       <c r="H77" t="n">
-        <v>80.5</v>
+        <v>48.3</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J77" t="n">
-        <v>37.99</v>
+        <v>-70.83</v>
       </c>
       <c r="K77" t="n">
-        <v>-117.19</v>
+        <v>203.9</v>
       </c>
       <c r="L77" t="n">
-        <v>123.2</v>
+        <v>215.85</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:41:31</t>
+          <t>08:41:58</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.73</v>
+        <v>5.01</v>
       </c>
       <c r="F78" t="n">
-        <v>15.3</v>
+        <v>15.29</v>
       </c>
       <c r="G78" t="n">
-        <v>259.5</v>
+        <v>250.8</v>
       </c>
       <c r="H78" t="n">
-        <v>61</v>
+        <v>61.6</v>
       </c>
       <c r="I78" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-106.41</v>
+        <v>-95.84999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>75.45999999999999</v>
+        <v>-121.84</v>
       </c>
       <c r="L78" t="n">
-        <v>130.46</v>
+        <v>155.02</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:43:27</t>
+          <t>08:43:47</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.73</v>
+        <v>5.75</v>
       </c>
       <c r="F79" t="n">
-        <v>11.5</v>
+        <v>15.87</v>
       </c>
       <c r="G79" t="n">
-        <v>263.3</v>
+        <v>266.5</v>
       </c>
       <c r="H79" t="n">
-        <v>80.40000000000001</v>
+        <v>47.4</v>
       </c>
       <c r="I79" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>55.42</v>
+        <v>17.23</v>
       </c>
       <c r="K79" t="n">
-        <v>-47.57</v>
+        <v>-170.55</v>
       </c>
       <c r="L79" t="n">
-        <v>73.04000000000001</v>
+        <v>171.41</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:46:19</t>
+          <t>08:48:17</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.14</v>
+        <v>5.12</v>
       </c>
       <c r="F80" t="n">
         <v>15.87</v>
       </c>
       <c r="G80" t="n">
-        <v>238.2</v>
+        <v>258.9</v>
       </c>
       <c r="H80" t="n">
-        <v>83.09999999999999</v>
+        <v>61.2</v>
       </c>
       <c r="I80" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>-110.64</v>
+        <v>133.04</v>
       </c>
       <c r="K80" t="n">
-        <v>-179.85</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>211.16</v>
+        <v>163.87</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:47:27</t>
+          <t>08:49:56</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.99</v>
+        <v>4.67</v>
       </c>
       <c r="F81" t="n">
-        <v>12.89</v>
+        <v>13.44</v>
       </c>
       <c r="G81" t="n">
-        <v>249.7</v>
+        <v>260.8</v>
       </c>
       <c r="H81" t="n">
-        <v>81</v>
+        <v>36.9</v>
       </c>
       <c r="I81" t="n">
         <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-180.87</v>
+        <v>-114.31</v>
       </c>
       <c r="K81" t="n">
-        <v>-35.47</v>
+        <v>-139.86</v>
       </c>
       <c r="L81" t="n">
-        <v>184.31</v>
+        <v>180.63</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:49:23</t>
+          <t>08:51:16</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.98</v>
+        <v>5.55</v>
       </c>
       <c r="F82" t="n">
         <v>15.87</v>
       </c>
       <c r="G82" t="n">
-        <v>252</v>
+        <v>251.7</v>
       </c>
       <c r="H82" t="n">
-        <v>79.59999999999999</v>
+        <v>57.9</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>138.19</v>
+        <v>-197.8</v>
       </c>
       <c r="K82" t="n">
-        <v>-36.99</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>143.06</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:53:50</t>
+          <t>08:56:01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.13</v>
+        <v>4.83</v>
       </c>
       <c r="F83" t="n">
-        <v>14.76</v>
+        <v>13.44</v>
       </c>
       <c r="G83" t="n">
-        <v>257.2</v>
+        <v>259.3</v>
       </c>
       <c r="H83" t="n">
-        <v>76.40000000000001</v>
+        <v>59.6</v>
       </c>
       <c r="I83" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>-155.11</v>
+        <v>-148.89</v>
       </c>
       <c r="K83" t="n">
-        <v>-93.15000000000001</v>
+        <v>203.27</v>
       </c>
       <c r="L83" t="n">
-        <v>180.93</v>
+        <v>251.96</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:55:49</t>
+          <t>08:57:43</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.77</v>
+        <v>5.24</v>
       </c>
       <c r="F84" t="n">
-        <v>15.48</v>
+        <v>15.87</v>
       </c>
       <c r="G84" t="n">
-        <v>260.9</v>
+        <v>262.6</v>
       </c>
       <c r="H84" t="n">
-        <v>79.5</v>
+        <v>50.4</v>
       </c>
       <c r="I84" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J84" t="n">
-        <v>223.32</v>
+        <v>149.45</v>
       </c>
       <c r="K84" t="n">
-        <v>-65.94</v>
+        <v>259.53</v>
       </c>
       <c r="L84" t="n">
-        <v>232.85</v>
+        <v>299.49</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:58:04</t>
+          <t>09:00:05</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.62</v>
+        <v>5.82</v>
       </c>
       <c r="F85" t="n">
-        <v>11.27</v>
+        <v>15.87</v>
       </c>
       <c r="G85" t="n">
-        <v>258.9</v>
+        <v>235.4</v>
       </c>
       <c r="H85" t="n">
-        <v>84.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>228.04</v>
+        <v>-240.39</v>
       </c>
       <c r="K85" t="n">
-        <v>-68.91</v>
+        <v>-85.26000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>238.23</v>
+        <v>255.06</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:03:51</t>
+          <t>09:05:03</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="F86" t="n">
-        <v>15.87</v>
+        <v>12.62</v>
       </c>
       <c r="G86" t="n">
-        <v>256.1</v>
+        <v>254.9</v>
       </c>
       <c r="H86" t="n">
-        <v>87.40000000000001</v>
+        <v>55.1</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-238.77</v>
+        <v>-276.92</v>
       </c>
       <c r="K86" t="n">
-        <v>-463.9</v>
+        <v>40.16</v>
       </c>
       <c r="L86" t="n">
-        <v>521.74</v>
+        <v>279.82</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:05:45</t>
+          <t>09:06:37</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.9</v>
+        <v>5.55</v>
       </c>
       <c r="F87" t="n">
         <v>15.87</v>
       </c>
       <c r="G87" t="n">
-        <v>255.9</v>
+        <v>249.8</v>
       </c>
       <c r="H87" t="n">
-        <v>74.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J87" t="n">
-        <v>24.58</v>
+        <v>-306.75</v>
       </c>
       <c r="K87" t="n">
-        <v>39.82</v>
+        <v>-291.05</v>
       </c>
       <c r="L87" t="n">
-        <v>46.79</v>
+        <v>422.85</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:06:47</t>
+          <t>09:08:15</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.68</v>
+        <v>5.33</v>
       </c>
       <c r="F88" t="n">
-        <v>9.029999999999999</v>
+        <v>15.87</v>
       </c>
       <c r="G88" t="n">
-        <v>274.7</v>
+        <v>249.4</v>
       </c>
       <c r="H88" t="n">
-        <v>80.09999999999999</v>
+        <v>36.8</v>
       </c>
       <c r="I88" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>-265.99</v>
+        <v>-225.29</v>
       </c>
       <c r="K88" t="n">
-        <v>10.33</v>
+        <v>239.75</v>
       </c>
       <c r="L88" t="n">
-        <v>266.19</v>
+        <v>328.99</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-30.xlsx
+++ b/output/2024-04-30.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.97</v>
+        <v>4.16</v>
       </c>
       <c r="F14" t="n">
-        <v>8.07</v>
+        <v>9.92</v>
       </c>
       <c r="G14" t="n">
-        <v>261.8</v>
+        <v>247.7</v>
       </c>
       <c r="H14" t="n">
-        <v>86.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>-26.78</v>
+        <v>-74.98</v>
       </c>
       <c r="K14" t="n">
-        <v>-21.09</v>
+        <v>-1.65</v>
       </c>
       <c r="L14" t="n">
-        <v>34.09</v>
+        <v>74.98999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:32:59</t>
+          <t>05:33:59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.64</v>
+        <v>4.33</v>
       </c>
       <c r="F15" t="n">
-        <v>13.36</v>
+        <v>15.59</v>
       </c>
       <c r="G15" t="n">
-        <v>262.8</v>
+        <v>252.6</v>
       </c>
       <c r="H15" t="n">
-        <v>75.2</v>
+        <v>88.3</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-94.12</v>
+        <v>-87.44</v>
       </c>
       <c r="K15" t="n">
-        <v>-13.6</v>
+        <v>21.33</v>
       </c>
       <c r="L15" t="n">
-        <v>95.09999999999999</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:34:15</t>
+          <t>05:35:41</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.18</v>
+        <v>5.08</v>
       </c>
       <c r="F16" t="n">
-        <v>14.38</v>
+        <v>13.06</v>
       </c>
       <c r="G16" t="n">
-        <v>250.5</v>
+        <v>267.8</v>
       </c>
       <c r="H16" t="n">
-        <v>57</v>
+        <v>50.2</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>59.88</v>
+        <v>106.8</v>
       </c>
       <c r="K16" t="n">
-        <v>-44.02</v>
+        <v>50.38</v>
       </c>
       <c r="L16" t="n">
-        <v>74.31999999999999</v>
+        <v>118.09</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:39:04</t>
+          <t>05:40:49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>5.13</v>
       </c>
       <c r="F17" t="n">
-        <v>13.13</v>
+        <v>14.4</v>
       </c>
       <c r="G17" t="n">
-        <v>261.9</v>
+        <v>239.9</v>
       </c>
       <c r="H17" t="n">
-        <v>82.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-73.02</v>
+        <v>54.54</v>
       </c>
       <c r="K17" t="n">
-        <v>-143.58</v>
+        <v>127.95</v>
       </c>
       <c r="L17" t="n">
-        <v>161.08</v>
+        <v>139.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:39:56</t>
+          <t>05:42:41</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.49</v>
+        <v>3.68</v>
       </c>
       <c r="F18" t="n">
-        <v>15.87</v>
+        <v>13.87</v>
       </c>
       <c r="G18" t="n">
-        <v>259.8</v>
+        <v>242.1</v>
       </c>
       <c r="H18" t="n">
-        <v>86.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>-148.21</v>
+        <v>40.38</v>
       </c>
       <c r="K18" t="n">
-        <v>-163.86</v>
+        <v>70.81</v>
       </c>
       <c r="L18" t="n">
-        <v>220.94</v>
+        <v>81.51000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:42:14</t>
+          <t>05:45:08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.81</v>
+        <v>5.06</v>
       </c>
       <c r="F19" t="n">
-        <v>6.8</v>
+        <v>15.87</v>
       </c>
       <c r="G19" t="n">
-        <v>252.4</v>
+        <v>259.9</v>
       </c>
       <c r="H19" t="n">
-        <v>52.2</v>
+        <v>36.6</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-25.9</v>
+        <v>-13.42</v>
       </c>
       <c r="K19" t="n">
-        <v>102.77</v>
+        <v>139.72</v>
       </c>
       <c r="L19" t="n">
-        <v>105.98</v>
+        <v>140.37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:47:35</t>
+          <t>05:49:04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.21</v>
+        <v>4.04</v>
       </c>
       <c r="F20" t="n">
-        <v>10.32</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>250.7</v>
+        <v>268.2</v>
       </c>
       <c r="H20" t="n">
-        <v>77.40000000000001</v>
+        <v>44.2</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>61.96</v>
+        <v>94.95</v>
       </c>
       <c r="K20" t="n">
-        <v>127.65</v>
+        <v>85.97</v>
       </c>
       <c r="L20" t="n">
-        <v>141.89</v>
+        <v>128.09</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:49:11</t>
+          <t>05:51:32</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.43</v>
+        <v>4.18</v>
       </c>
       <c r="F21" t="n">
-        <v>14.54</v>
+        <v>11.47</v>
       </c>
       <c r="G21" t="n">
-        <v>260.2</v>
+        <v>232.7</v>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="I21" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-137.05</v>
+        <v>-151.13</v>
       </c>
       <c r="K21" t="n">
-        <v>10.74</v>
+        <v>78.92</v>
       </c>
       <c r="L21" t="n">
-        <v>137.47</v>
+        <v>170.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:51:44</t>
+          <t>05:53:16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.96</v>
+        <v>3.53</v>
       </c>
       <c r="F22" t="n">
-        <v>11.76</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>238.7</v>
+        <v>255.7</v>
       </c>
       <c r="H22" t="n">
-        <v>54.4</v>
+        <v>39.1</v>
       </c>
       <c r="I22" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>24.34</v>
+        <v>-95.2</v>
       </c>
       <c r="K22" t="n">
-        <v>-108.16</v>
+        <v>-73.77</v>
       </c>
       <c r="L22" t="n">
-        <v>110.86</v>
+        <v>120.43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:56:10</t>
+          <t>05:57:23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.53</v>
+        <v>4.62</v>
       </c>
       <c r="F23" t="n">
-        <v>14.61</v>
+        <v>14</v>
       </c>
       <c r="G23" t="n">
-        <v>264.3</v>
+        <v>253.4</v>
       </c>
       <c r="H23" t="n">
-        <v>64.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-210.65</v>
+        <v>-320.39</v>
       </c>
       <c r="K23" t="n">
-        <v>72.31999999999999</v>
+        <v>3.96</v>
       </c>
       <c r="L23" t="n">
-        <v>222.71</v>
+        <v>320.41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:58:01</t>
+          <t>05:58:39</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.9</v>
+        <v>4.63</v>
       </c>
       <c r="F24" t="n">
-        <v>11.68</v>
+        <v>12.39</v>
       </c>
       <c r="G24" t="n">
-        <v>251.6</v>
+        <v>253.9</v>
       </c>
       <c r="H24" t="n">
-        <v>52.5</v>
+        <v>63.8</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>123.95</v>
+        <v>-1.9</v>
       </c>
       <c r="K24" t="n">
-        <v>251.64</v>
+        <v>-103.6</v>
       </c>
       <c r="L24" t="n">
-        <v>280.51</v>
+        <v>103.61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:58:54</t>
+          <t>06:01:02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.26</v>
+        <v>4.69</v>
       </c>
       <c r="F25" t="n">
-        <v>6.89</v>
+        <v>14.87</v>
       </c>
       <c r="G25" t="n">
-        <v>245.4</v>
+        <v>254.7</v>
       </c>
       <c r="H25" t="n">
-        <v>57.3</v>
+        <v>72.3</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-154.29</v>
+        <v>-262.51</v>
       </c>
       <c r="K25" t="n">
-        <v>-121.65</v>
+        <v>6.78</v>
       </c>
       <c r="L25" t="n">
-        <v>196.48</v>
+        <v>262.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:03:20</t>
+          <t>06:05:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.1</v>
+        <v>5.44</v>
       </c>
       <c r="F26" t="n">
-        <v>11.5</v>
+        <v>12.21</v>
       </c>
       <c r="G26" t="n">
-        <v>257.8</v>
+        <v>253.7</v>
       </c>
       <c r="H26" t="n">
-        <v>22.3</v>
+        <v>39.7</v>
       </c>
       <c r="I26" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-284.61</v>
+        <v>-168.03</v>
       </c>
       <c r="K26" t="n">
-        <v>-53.43</v>
+        <v>-91.37</v>
       </c>
       <c r="L26" t="n">
-        <v>289.58</v>
+        <v>191.27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:05:01</t>
+          <t>06:08:10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.86</v>
+        <v>4.03</v>
       </c>
       <c r="F27" t="n">
-        <v>11.62</v>
+        <v>14.42</v>
       </c>
       <c r="G27" t="n">
-        <v>258.8</v>
+        <v>253.6</v>
       </c>
       <c r="H27" t="n">
-        <v>55.6</v>
+        <v>45.9</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-160.7</v>
+        <v>205.41</v>
       </c>
       <c r="K27" t="n">
-        <v>-307</v>
+        <v>-123.48</v>
       </c>
       <c r="L27" t="n">
-        <v>346.51</v>
+        <v>239.67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:06:16</t>
+          <t>06:09:59</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.5</v>
+        <v>4.31</v>
       </c>
       <c r="F28" t="n">
-        <v>12.01</v>
+        <v>8.65</v>
       </c>
       <c r="G28" t="n">
-        <v>256.4</v>
+        <v>261</v>
       </c>
       <c r="H28" t="n">
-        <v>74</v>
+        <v>56.3</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-305.89</v>
+        <v>309.27</v>
       </c>
       <c r="K28" t="n">
-        <v>65.88</v>
+        <v>-154.67</v>
       </c>
       <c r="L28" t="n">
-        <v>312.91</v>
+        <v>345.79</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:16:16</t>
+          <t>06:23:16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.09</v>
+        <v>4.46</v>
       </c>
       <c r="F29" t="n">
-        <v>11.17</v>
+        <v>11.7</v>
       </c>
       <c r="G29" t="n">
-        <v>264.2</v>
+        <v>257.3</v>
       </c>
       <c r="H29" t="n">
-        <v>37</v>
+        <v>44.2</v>
       </c>
       <c r="I29" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-28.56</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>75.66</v>
+        <v>54.57</v>
       </c>
       <c r="L29" t="n">
-        <v>80.87</v>
+        <v>87.11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:18:40</t>
+          <t>06:24:34</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.3</v>
+        <v>3.89</v>
       </c>
       <c r="F30" t="n">
-        <v>13.31</v>
+        <v>11.82</v>
       </c>
       <c r="G30" t="n">
-        <v>234.1</v>
+        <v>262.6</v>
       </c>
       <c r="H30" t="n">
-        <v>44.6</v>
+        <v>61.5</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-59.01</v>
+        <v>66.53</v>
       </c>
       <c r="K30" t="n">
-        <v>57.78</v>
+        <v>-20.18</v>
       </c>
       <c r="L30" t="n">
-        <v>82.59</v>
+        <v>69.52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:20:29</t>
+          <t>06:26:16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.36</v>
+        <v>4.57</v>
       </c>
       <c r="F31" t="n">
-        <v>11.34</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>265.5</v>
+        <v>263.3</v>
       </c>
       <c r="H31" t="n">
-        <v>35.4</v>
+        <v>51</v>
       </c>
       <c r="I31" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-23.58</v>
+        <v>-27.58</v>
       </c>
       <c r="K31" t="n">
-        <v>-79.22</v>
+        <v>-98.95</v>
       </c>
       <c r="L31" t="n">
-        <v>82.66</v>
+        <v>102.72</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:26:00</t>
+          <t>06:31:45</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.11</v>
+        <v>4.29</v>
       </c>
       <c r="F32" t="n">
-        <v>11.09</v>
+        <v>13.44</v>
       </c>
       <c r="G32" t="n">
-        <v>243.4</v>
+        <v>262.5</v>
       </c>
       <c r="H32" t="n">
-        <v>48.1</v>
+        <v>70.7</v>
       </c>
       <c r="I32" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>3.14</v>
+        <v>71.7</v>
       </c>
       <c r="K32" t="n">
-        <v>-96.04000000000001</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>96.09</v>
+        <v>100.15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:27:19</t>
+          <t>06:33:15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.65</v>
+        <v>4.44</v>
       </c>
       <c r="F33" t="n">
         <v>12.27</v>
       </c>
       <c r="G33" t="n">
-        <v>254.3</v>
+        <v>254.6</v>
       </c>
       <c r="H33" t="n">
-        <v>45.3</v>
+        <v>44</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>23.39</v>
+        <v>-93.56</v>
       </c>
       <c r="K33" t="n">
-        <v>-107.02</v>
+        <v>41.1</v>
       </c>
       <c r="L33" t="n">
-        <v>109.54</v>
+        <v>102.19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:28:56</t>
+          <t>06:34:42</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="F34" t="n">
-        <v>12.43</v>
+        <v>15.58</v>
       </c>
       <c r="G34" t="n">
-        <v>262.7</v>
+        <v>263.5</v>
       </c>
       <c r="H34" t="n">
-        <v>52.8</v>
+        <v>69</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-53.79</v>
+        <v>-144.82</v>
       </c>
       <c r="K34" t="n">
-        <v>162.97</v>
+        <v>-69.95999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>171.62</v>
+        <v>160.83</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:33:25</t>
+          <t>06:39:51</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.32</v>
+        <v>5.02</v>
       </c>
       <c r="F35" t="n">
-        <v>13.82</v>
+        <v>12.41</v>
       </c>
       <c r="G35" t="n">
-        <v>252.7</v>
+        <v>258.8</v>
       </c>
       <c r="H35" t="n">
-        <v>38.9</v>
+        <v>55.6</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>-68.09999999999999</v>
+        <v>-43.05</v>
       </c>
       <c r="K35" t="n">
-        <v>-97.09999999999999</v>
+        <v>-188.94</v>
       </c>
       <c r="L35" t="n">
-        <v>118.6</v>
+        <v>193.78</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:35:04</t>
+          <t>06:41:05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>5.52</v>
+        <v>4.65</v>
       </c>
       <c r="F36" t="n">
-        <v>15.87</v>
+        <v>12.75</v>
       </c>
       <c r="G36" t="n">
-        <v>258.7</v>
+        <v>256.4</v>
       </c>
       <c r="H36" t="n">
-        <v>92.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="I36" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-188.66</v>
+        <v>-162.34</v>
       </c>
       <c r="K36" t="n">
-        <v>-86.23</v>
+        <v>60.52</v>
       </c>
       <c r="L36" t="n">
-        <v>207.43</v>
+        <v>173.25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:37:15</t>
+          <t>06:43:15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.97</v>
+        <v>4.21</v>
       </c>
       <c r="F37" t="n">
-        <v>14.64</v>
+        <v>11.73</v>
       </c>
       <c r="G37" t="n">
-        <v>244.2</v>
+        <v>264.2</v>
       </c>
       <c r="H37" t="n">
-        <v>65.90000000000001</v>
+        <v>37</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-91.01000000000001</v>
+        <v>-13.03</v>
       </c>
       <c r="K37" t="n">
-        <v>73.05</v>
+        <v>150.77</v>
       </c>
       <c r="L37" t="n">
-        <v>116.7</v>
+        <v>151.34</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:42:12</t>
+          <t>06:48:02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.89</v>
+        <v>4.44</v>
       </c>
       <c r="F38" t="n">
-        <v>15.87</v>
+        <v>13.96</v>
       </c>
       <c r="G38" t="n">
-        <v>267</v>
+        <v>234.1</v>
       </c>
       <c r="H38" t="n">
-        <v>30.6</v>
+        <v>44.6</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-202.87</v>
+        <v>-119.43</v>
       </c>
       <c r="K38" t="n">
-        <v>-156.22</v>
+        <v>212.54</v>
       </c>
       <c r="L38" t="n">
-        <v>256.05</v>
+        <v>243.79</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:44:05</t>
+          <t>06:49:05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>5.01</v>
+        <v>4.49</v>
       </c>
       <c r="F39" t="n">
-        <v>14.79</v>
+        <v>11.95</v>
       </c>
       <c r="G39" t="n">
-        <v>244.9</v>
+        <v>265.5</v>
       </c>
       <c r="H39" t="n">
-        <v>37.3</v>
+        <v>35.4</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>49.02</v>
+        <v>-2.36</v>
       </c>
       <c r="K39" t="n">
-        <v>-196.41</v>
+        <v>-238.64</v>
       </c>
       <c r="L39" t="n">
-        <v>202.44</v>
+        <v>238.65</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:46:23</t>
+          <t>06:50:45</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.23</v>
+        <v>4.22</v>
       </c>
       <c r="F40" t="n">
-        <v>13.04</v>
+        <v>11.6</v>
       </c>
       <c r="G40" t="n">
-        <v>263</v>
+        <v>243.4</v>
       </c>
       <c r="H40" t="n">
-        <v>10.8</v>
+        <v>48.1</v>
       </c>
       <c r="I40" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>-145.22</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>96.52</v>
+        <v>-209.53</v>
       </c>
       <c r="L40" t="n">
-        <v>174.36</v>
+        <v>219.22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:50:51</t>
+          <t>06:54:55</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.91</v>
+        <v>4.77</v>
       </c>
       <c r="F41" t="n">
-        <v>12.54</v>
+        <v>12.86</v>
       </c>
       <c r="G41" t="n">
-        <v>249.3</v>
+        <v>254.3</v>
       </c>
       <c r="H41" t="n">
-        <v>77.3</v>
+        <v>45.3</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-105.17</v>
+        <v>-279.42</v>
       </c>
       <c r="K41" t="n">
-        <v>316.12</v>
+        <v>5.91</v>
       </c>
       <c r="L41" t="n">
-        <v>333.16</v>
+        <v>279.49</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:52:02</t>
+          <t>06:57:10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.46</v>
+        <v>4.17</v>
       </c>
       <c r="F42" t="n">
-        <v>13.53</v>
+        <v>12.89</v>
       </c>
       <c r="G42" t="n">
-        <v>259.4</v>
+        <v>250.9</v>
       </c>
       <c r="H42" t="n">
-        <v>51</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>-112.34</v>
+        <v>49.67</v>
       </c>
       <c r="K42" t="n">
-        <v>-333.57</v>
+        <v>200.16</v>
       </c>
       <c r="L42" t="n">
-        <v>351.98</v>
+        <v>206.23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:54:32</t>
+          <t>06:59:01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.5</v>
+        <v>4.51</v>
       </c>
       <c r="F43" t="n">
-        <v>12.27</v>
+        <v>12.67</v>
       </c>
       <c r="G43" t="n">
-        <v>266.5</v>
+        <v>253.2</v>
       </c>
       <c r="H43" t="n">
-        <v>91.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>22.94</v>
+        <v>315.12</v>
       </c>
       <c r="K43" t="n">
-        <v>306.6</v>
+        <v>82.05</v>
       </c>
       <c r="L43" t="n">
-        <v>307.46</v>
+        <v>325.62</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:07:03</t>
+          <t>07:08:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.41</v>
+        <v>4.3</v>
       </c>
       <c r="F44" t="n">
         <v>15.87</v>
       </c>
       <c r="G44" t="n">
-        <v>258.2</v>
+        <v>258.5</v>
       </c>
       <c r="H44" t="n">
-        <v>29.2</v>
+        <v>49.2</v>
       </c>
       <c r="I44" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-8.710000000000001</v>
+        <v>38.67</v>
       </c>
       <c r="K44" t="n">
-        <v>109.58</v>
+        <v>-51.67</v>
       </c>
       <c r="L44" t="n">
-        <v>109.93</v>
+        <v>64.53</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:07:49</t>
+          <t>07:08:57</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.54</v>
+        <v>3.83</v>
       </c>
       <c r="F45" t="n">
-        <v>15.87</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>244.9</v>
+        <v>252.1</v>
       </c>
       <c r="H45" t="n">
-        <v>56.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-29.26</v>
+        <v>-32.26</v>
       </c>
       <c r="K45" t="n">
-        <v>-63.49</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>69.90000000000001</v>
+        <v>74.13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:10:10</t>
+          <t>07:10:55</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.32</v>
+        <v>4.39</v>
       </c>
       <c r="F46" t="n">
-        <v>12.01</v>
+        <v>14.58</v>
       </c>
       <c r="G46" t="n">
-        <v>248.3</v>
+        <v>268</v>
       </c>
       <c r="H46" t="n">
-        <v>64.3</v>
+        <v>41.4</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>4.89</v>
+        <v>-16.13</v>
       </c>
       <c r="K46" t="n">
-        <v>-97.83</v>
+        <v>-71.94</v>
       </c>
       <c r="L46" t="n">
-        <v>97.95</v>
+        <v>73.72</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:14:16</t>
+          <t>07:15:24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>5.29</v>
+        <v>4.97</v>
       </c>
       <c r="F47" t="n">
         <v>15.87</v>
       </c>
       <c r="G47" t="n">
-        <v>259.5</v>
+        <v>247.8</v>
       </c>
       <c r="H47" t="n">
-        <v>69.40000000000001</v>
+        <v>60.8</v>
       </c>
       <c r="I47" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>121.14</v>
+        <v>-130.8</v>
       </c>
       <c r="K47" t="n">
-        <v>49.25</v>
+        <v>33.42</v>
       </c>
       <c r="L47" t="n">
-        <v>130.77</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:15:56</t>
+          <t>07:17:15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.42</v>
+        <v>5.3</v>
       </c>
       <c r="F48" t="n">
-        <v>11.11</v>
+        <v>14.58</v>
       </c>
       <c r="G48" t="n">
-        <v>254.5</v>
+        <v>257.8</v>
       </c>
       <c r="H48" t="n">
-        <v>62.1</v>
+        <v>29.2</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J48" t="n">
-        <v>78.31999999999999</v>
+        <v>35.79</v>
       </c>
       <c r="K48" t="n">
-        <v>76.5</v>
+        <v>-151.5</v>
       </c>
       <c r="L48" t="n">
-        <v>109.48</v>
+        <v>155.67</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:18:02</t>
+          <t>07:19:20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>5.67</v>
+        <v>4.59</v>
       </c>
       <c r="F49" t="n">
-        <v>15.87</v>
+        <v>11.11</v>
       </c>
       <c r="G49" t="n">
-        <v>233.6</v>
+        <v>268.4</v>
       </c>
       <c r="H49" t="n">
-        <v>17.6</v>
+        <v>70.7</v>
       </c>
       <c r="I49" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>44.65</v>
+        <v>55.99</v>
       </c>
       <c r="K49" t="n">
-        <v>152.9</v>
+        <v>93.75</v>
       </c>
       <c r="L49" t="n">
-        <v>159.29</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:22:42</t>
+          <t>07:22:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5.59</v>
+        <v>5.3</v>
       </c>
       <c r="F50" t="n">
-        <v>15.6</v>
+        <v>15.45</v>
       </c>
       <c r="G50" t="n">
-        <v>253.3</v>
+        <v>256.7</v>
       </c>
       <c r="H50" t="n">
-        <v>84.8</v>
+        <v>67.7</v>
       </c>
       <c r="I50" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-129.19</v>
+        <v>95.95</v>
       </c>
       <c r="K50" t="n">
-        <v>-189.8</v>
+        <v>188.08</v>
       </c>
       <c r="L50" t="n">
-        <v>229.6</v>
+        <v>211.14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:23:44</t>
+          <t>07:24:15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.52</v>
+        <v>4.3</v>
       </c>
       <c r="F51" t="n">
-        <v>7.93</v>
+        <v>12.61</v>
       </c>
       <c r="G51" t="n">
-        <v>269.2</v>
+        <v>244.4</v>
       </c>
       <c r="H51" t="n">
-        <v>81.8</v>
+        <v>48.1</v>
       </c>
       <c r="I51" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-144.97</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.27</v>
+        <v>178.61</v>
       </c>
       <c r="L51" t="n">
-        <v>144.99</v>
+        <v>178.83</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:24:51</t>
+          <t>07:26:41</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.65</v>
+        <v>4.51</v>
       </c>
       <c r="F52" t="n">
         <v>15.87</v>
       </c>
       <c r="G52" t="n">
-        <v>266.5</v>
+        <v>268.2</v>
       </c>
       <c r="H52" t="n">
-        <v>31.3</v>
+        <v>56.2</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-207.81</v>
+        <v>-130.18</v>
       </c>
       <c r="K52" t="n">
-        <v>-85.25</v>
+        <v>177.18</v>
       </c>
       <c r="L52" t="n">
-        <v>224.61</v>
+        <v>219.86</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:29:30</t>
+          <t>07:30:47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.04</v>
+        <v>5.16</v>
       </c>
       <c r="F53" t="n">
-        <v>11.81</v>
+        <v>15.16</v>
       </c>
       <c r="G53" t="n">
-        <v>253</v>
+        <v>263.3</v>
       </c>
       <c r="H53" t="n">
-        <v>53.1</v>
+        <v>88.3</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>-67.63</v>
+        <v>-258.21</v>
       </c>
       <c r="K53" t="n">
-        <v>-165.51</v>
+        <v>-270.73</v>
       </c>
       <c r="L53" t="n">
-        <v>178.79</v>
+        <v>374.12</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:30:09</t>
+          <t>07:31:55</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.93</v>
+        <v>4.4</v>
       </c>
       <c r="F54" t="n">
-        <v>13.08</v>
+        <v>11.97</v>
       </c>
       <c r="G54" t="n">
-        <v>252.3</v>
+        <v>251.1</v>
       </c>
       <c r="H54" t="n">
-        <v>49.6</v>
+        <v>72</v>
       </c>
       <c r="I54" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-150.76</v>
+        <v>-73.18000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>74.27</v>
+        <v>257.14</v>
       </c>
       <c r="L54" t="n">
-        <v>168.06</v>
+        <v>267.35</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:31:45</t>
+          <t>07:33:34</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,28 +2347,28 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.52</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
-        <v>15.11</v>
+        <v>11.05</v>
       </c>
       <c r="G55" t="n">
-        <v>254.8</v>
+        <v>259</v>
       </c>
       <c r="H55" t="n">
-        <v>40.1</v>
+        <v>54.7</v>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>174.01</v>
+        <v>-180.47</v>
       </c>
       <c r="K55" t="n">
-        <v>54.1</v>
+        <v>-221.91</v>
       </c>
       <c r="L55" t="n">
-        <v>182.22</v>
+        <v>286.03</v>
       </c>
     </row>
     <row r="56">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.92</v>
+        <v>4.73</v>
       </c>
       <c r="F56" t="n">
-        <v>15.87</v>
+        <v>14.55</v>
       </c>
       <c r="G56" t="n">
-        <v>254.4</v>
+        <v>249.8</v>
       </c>
       <c r="H56" t="n">
-        <v>36.6</v>
+        <v>58</v>
       </c>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-298.25</v>
+        <v>-171.11</v>
       </c>
       <c r="K56" t="n">
-        <v>-199.77</v>
+        <v>267.55</v>
       </c>
       <c r="L56" t="n">
-        <v>358.97</v>
+        <v>317.59</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:39:26</t>
+          <t>07:38:45</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>5.18</v>
       </c>
       <c r="F57" t="n">
-        <v>11.52</v>
+        <v>15.87</v>
       </c>
       <c r="G57" t="n">
-        <v>243.7</v>
+        <v>250.9</v>
       </c>
       <c r="H57" t="n">
-        <v>50.5</v>
+        <v>6</v>
       </c>
       <c r="I57" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>-245.36</v>
+        <v>-38.09</v>
       </c>
       <c r="K57" t="n">
-        <v>54.19</v>
+        <v>-392.79</v>
       </c>
       <c r="L57" t="n">
-        <v>251.27</v>
+        <v>394.63</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:41:08</t>
+          <t>07:40:28</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.13</v>
+        <v>4.73</v>
       </c>
       <c r="F58" t="n">
-        <v>11</v>
+        <v>13.21</v>
       </c>
       <c r="G58" t="n">
-        <v>242.9</v>
+        <v>253.3</v>
       </c>
       <c r="H58" t="n">
-        <v>61.3</v>
+        <v>84.8</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>-184.76</v>
+        <v>-123.37</v>
       </c>
       <c r="K58" t="n">
-        <v>205.63</v>
+        <v>-368.03</v>
       </c>
       <c r="L58" t="n">
-        <v>276.45</v>
+        <v>388.15</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:51:59</t>
+          <t>07:52:22</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.53</v>
+        <v>4.64</v>
       </c>
       <c r="F59" t="n">
-        <v>13.46</v>
+        <v>8.51</v>
       </c>
       <c r="G59" t="n">
-        <v>249.6</v>
+        <v>269.2</v>
       </c>
       <c r="H59" t="n">
-        <v>16.7</v>
+        <v>81.8</v>
       </c>
       <c r="I59" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>36.47</v>
+        <v>-83.08</v>
       </c>
       <c r="K59" t="n">
-        <v>114.31</v>
+        <v>-1.35</v>
       </c>
       <c r="L59" t="n">
-        <v>119.99</v>
+        <v>83.09</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:53:55</t>
+          <t>07:53:16</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.11</v>
+        <v>5.76</v>
       </c>
       <c r="F60" t="n">
         <v>15.87</v>
       </c>
       <c r="G60" t="n">
-        <v>268.9</v>
+        <v>266.5</v>
       </c>
       <c r="H60" t="n">
-        <v>91.3</v>
+        <v>31.3</v>
       </c>
       <c r="I60" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-97.98999999999999</v>
+        <v>-121.11</v>
       </c>
       <c r="K60" t="n">
-        <v>-24.24</v>
+        <v>-68.36</v>
       </c>
       <c r="L60" t="n">
-        <v>100.95</v>
+        <v>139.07</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:55:21</t>
+          <t>07:54:56</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.46</v>
+        <v>4.14</v>
       </c>
       <c r="F61" t="n">
-        <v>9.25</v>
+        <v>12.28</v>
       </c>
       <c r="G61" t="n">
-        <v>257.7</v>
+        <v>253</v>
       </c>
       <c r="H61" t="n">
-        <v>52.7</v>
+        <v>53.1</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>83.06</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="K61" t="n">
-        <v>-53.45</v>
+        <v>-61.38</v>
       </c>
       <c r="L61" t="n">
-        <v>98.77</v>
+        <v>62.13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:59:22</t>
+          <t>07:58:48</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.89</v>
+        <v>4.04</v>
       </c>
       <c r="F62" t="n">
-        <v>12.69</v>
+        <v>13.61</v>
       </c>
       <c r="G62" t="n">
-        <v>265.7</v>
+        <v>252.3</v>
       </c>
       <c r="H62" t="n">
-        <v>51.4</v>
+        <v>49.6</v>
       </c>
       <c r="I62" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>24.97</v>
+        <v>-61.27</v>
       </c>
       <c r="K62" t="n">
-        <v>137.48</v>
+        <v>47.99</v>
       </c>
       <c r="L62" t="n">
-        <v>139.73</v>
+        <v>77.83</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:01:01</t>
+          <t>08:00:03</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.55</v>
+        <v>4.63</v>
       </c>
       <c r="F63" t="n">
-        <v>11.58</v>
+        <v>15.66</v>
       </c>
       <c r="G63" t="n">
-        <v>245.2</v>
+        <v>254.8</v>
       </c>
       <c r="H63" t="n">
-        <v>65.2</v>
+        <v>40.1</v>
       </c>
       <c r="I63" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-65.39</v>
+        <v>90.45</v>
       </c>
       <c r="K63" t="n">
-        <v>-66.06999999999999</v>
+        <v>27.21</v>
       </c>
       <c r="L63" t="n">
-        <v>92.95</v>
+        <v>94.45999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:02:44</t>
+          <t>08:01:37</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.82</v>
+        <v>5.01</v>
       </c>
       <c r="F64" t="n">
         <v>15.87</v>
       </c>
       <c r="G64" t="n">
-        <v>245.7</v>
+        <v>254.4</v>
       </c>
       <c r="H64" t="n">
-        <v>50.9</v>
+        <v>36.6</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>98.5</v>
+        <v>-113.78</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.22</v>
+        <v>-96.31999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>98.51000000000001</v>
+        <v>149.07</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:06:02</t>
+          <t>08:06:10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.48</v>
+        <v>4.1</v>
       </c>
       <c r="F65" t="n">
-        <v>10.72</v>
+        <v>12</v>
       </c>
       <c r="G65" t="n">
-        <v>252.7</v>
+        <v>243.7</v>
       </c>
       <c r="H65" t="n">
         <v>50.5</v>
       </c>
       <c r="I65" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>-99.55</v>
+        <v>-120.91</v>
       </c>
       <c r="K65" t="n">
-        <v>104</v>
+        <v>52.31</v>
       </c>
       <c r="L65" t="n">
-        <v>143.97</v>
+        <v>131.74</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:07:50</t>
+          <t>08:07:46</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.48</v>
+        <v>4.23</v>
       </c>
       <c r="F66" t="n">
-        <v>15.18</v>
+        <v>11.48</v>
       </c>
       <c r="G66" t="n">
-        <v>255.1</v>
+        <v>242.9</v>
       </c>
       <c r="H66" t="n">
-        <v>59</v>
+        <v>61.3</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-119.75</v>
+        <v>-64.48999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>190.47</v>
+        <v>132</v>
       </c>
       <c r="L66" t="n">
-        <v>224.99</v>
+        <v>146.91</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:08:41</t>
+          <t>08:10:18</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5.05</v>
+        <v>4.6</v>
       </c>
       <c r="F67" t="n">
-        <v>15.87</v>
+        <v>13.81</v>
       </c>
       <c r="G67" t="n">
-        <v>250.4</v>
+        <v>249.6</v>
       </c>
       <c r="H67" t="n">
-        <v>49</v>
+        <v>16.7</v>
       </c>
       <c r="I67" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>57.24</v>
+        <v>120.32</v>
       </c>
       <c r="K67" t="n">
-        <v>-147.94</v>
+        <v>239.15</v>
       </c>
       <c r="L67" t="n">
-        <v>158.63</v>
+        <v>267.71</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:12:39</t>
+          <t>08:14:35</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.35</v>
+        <v>5.19</v>
       </c>
       <c r="F68" t="n">
         <v>15.87</v>
       </c>
       <c r="G68" t="n">
-        <v>255.2</v>
+        <v>268.9</v>
       </c>
       <c r="H68" t="n">
-        <v>48.6</v>
+        <v>91.3</v>
       </c>
       <c r="I68" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J68" t="n">
-        <v>-279.5</v>
+        <v>-262.08</v>
       </c>
       <c r="K68" t="n">
-        <v>88.42</v>
+        <v>-88.16</v>
       </c>
       <c r="L68" t="n">
-        <v>293.15</v>
+        <v>276.52</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:15:22</t>
+          <t>08:16:44</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.09</v>
+        <v>4.54</v>
       </c>
       <c r="F69" t="n">
-        <v>15.87</v>
+        <v>9.65</v>
       </c>
       <c r="G69" t="n">
-        <v>249.5</v>
+        <v>257.7</v>
       </c>
       <c r="H69" t="n">
-        <v>100</v>
+        <v>52.7</v>
       </c>
       <c r="I69" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>271.8</v>
+        <v>288.1</v>
       </c>
       <c r="K69" t="n">
-        <v>-147.18</v>
+        <v>-116.7</v>
       </c>
       <c r="L69" t="n">
-        <v>309.1</v>
+        <v>310.84</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:16:09</t>
+          <t>08:18:51</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.56</v>
+        <v>4.96</v>
       </c>
       <c r="F70" t="n">
-        <v>15.87</v>
+        <v>13.05</v>
       </c>
       <c r="G70" t="n">
-        <v>253.4</v>
+        <v>265.7</v>
       </c>
       <c r="H70" t="n">
-        <v>13.9</v>
+        <v>51.4</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-242.96</v>
+        <v>131.21</v>
       </c>
       <c r="K70" t="n">
-        <v>232.06</v>
+        <v>262.17</v>
       </c>
       <c r="L70" t="n">
-        <v>335.98</v>
+        <v>293.17</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:19:35</t>
+          <t>08:22:37</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.86</v>
+        <v>4.63</v>
       </c>
       <c r="F71" t="n">
-        <v>11.18</v>
+        <v>11.98</v>
       </c>
       <c r="G71" t="n">
-        <v>263.9</v>
+        <v>245.2</v>
       </c>
       <c r="H71" t="n">
-        <v>63.9</v>
+        <v>65.2</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-123.35</v>
+        <v>-161.33</v>
       </c>
       <c r="K71" t="n">
-        <v>251.51</v>
+        <v>-207.73</v>
       </c>
       <c r="L71" t="n">
-        <v>280.12</v>
+        <v>263.02</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:21:20</t>
+          <t>08:23:59</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="F72" t="n">
-        <v>13.97</v>
+        <v>15.87</v>
       </c>
       <c r="G72" t="n">
-        <v>240.6</v>
+        <v>245.7</v>
       </c>
       <c r="H72" t="n">
-        <v>36.2</v>
+        <v>50.9</v>
       </c>
       <c r="I72" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-318.97</v>
+        <v>263.66</v>
       </c>
       <c r="K72" t="n">
-        <v>-24.02</v>
+        <v>26.63</v>
       </c>
       <c r="L72" t="n">
-        <v>319.88</v>
+        <v>265.01</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:23:25</t>
+          <t>08:25:58</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.81</v>
+        <v>4.56</v>
       </c>
       <c r="F73" t="n">
-        <v>15.87</v>
+        <v>11.1</v>
       </c>
       <c r="G73" t="n">
-        <v>262.4</v>
+        <v>252.7</v>
       </c>
       <c r="H73" t="n">
-        <v>68.5</v>
+        <v>50.5</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>-321.48</v>
+        <v>-139.12</v>
       </c>
       <c r="K73" t="n">
-        <v>-112.68</v>
+        <v>264.12</v>
       </c>
       <c r="L73" t="n">
-        <v>340.66</v>
+        <v>298.52</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:33:40</t>
+          <t>08:37:34</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.44</v>
+        <v>5.59</v>
       </c>
       <c r="F74" t="n">
-        <v>14.06</v>
+        <v>15.77</v>
       </c>
       <c r="G74" t="n">
-        <v>255.7</v>
+        <v>255.1</v>
       </c>
       <c r="H74" t="n">
-        <v>54.9</v>
+        <v>59</v>
       </c>
       <c r="I74" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>90.02</v>
+        <v>-36.99</v>
       </c>
       <c r="K74" t="n">
-        <v>-27.04</v>
+        <v>150.88</v>
       </c>
       <c r="L74" t="n">
-        <v>94</v>
+        <v>155.35</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:34:24</t>
+          <t>08:39:53</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.08</v>
+        <v>5.17</v>
       </c>
       <c r="F75" t="n">
         <v>15.87</v>
       </c>
       <c r="G75" t="n">
-        <v>247.9</v>
+        <v>250.4</v>
       </c>
       <c r="H75" t="n">
-        <v>41.1</v>
+        <v>49</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-48.69</v>
+        <v>65.73</v>
       </c>
       <c r="K75" t="n">
-        <v>-96.91</v>
+        <v>-82.09999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>108.46</v>
+        <v>105.17</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:36:18</t>
+          <t>08:41:04</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>6.04</v>
+        <v>5.45</v>
       </c>
       <c r="F76" t="n">
         <v>15.87</v>
       </c>
       <c r="G76" t="n">
-        <v>257.5</v>
+        <v>255.2</v>
       </c>
       <c r="H76" t="n">
-        <v>100</v>
+        <v>48.6</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-120.21</v>
+        <v>-119.88</v>
       </c>
       <c r="K76" t="n">
-        <v>-19.4</v>
+        <v>66.03</v>
       </c>
       <c r="L76" t="n">
-        <v>121.77</v>
+        <v>136.87</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:41:20</t>
+          <t>08:45:55</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.66</v>
+        <v>5.19</v>
       </c>
       <c r="F77" t="n">
         <v>15.87</v>
       </c>
       <c r="G77" t="n">
-        <v>259</v>
+        <v>249.5</v>
       </c>
       <c r="H77" t="n">
-        <v>48.3</v>
+        <v>100</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-70.83</v>
+        <v>180.78</v>
       </c>
       <c r="K77" t="n">
-        <v>203.9</v>
+        <v>-52.72</v>
       </c>
       <c r="L77" t="n">
-        <v>215.85</v>
+        <v>188.31</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:41:58</t>
+          <t>08:48:25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.01</v>
+        <v>5.67</v>
       </c>
       <c r="F78" t="n">
-        <v>15.29</v>
+        <v>15.87</v>
       </c>
       <c r="G78" t="n">
-        <v>250.8</v>
+        <v>253.4</v>
       </c>
       <c r="H78" t="n">
-        <v>61.6</v>
+        <v>13.9</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-95.84999999999999</v>
+        <v>-103.6</v>
       </c>
       <c r="K78" t="n">
-        <v>-121.84</v>
+        <v>187.88</v>
       </c>
       <c r="L78" t="n">
-        <v>155.02</v>
+        <v>214.55</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:43:47</t>
+          <t>08:49:47</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.75</v>
+        <v>3.97</v>
       </c>
       <c r="F79" t="n">
-        <v>15.87</v>
+        <v>11.69</v>
       </c>
       <c r="G79" t="n">
-        <v>266.5</v>
+        <v>263.9</v>
       </c>
       <c r="H79" t="n">
-        <v>47.4</v>
+        <v>63.9</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J79" t="n">
-        <v>17.23</v>
+        <v>-21.86</v>
       </c>
       <c r="K79" t="n">
-        <v>-170.55</v>
+        <v>110.9</v>
       </c>
       <c r="L79" t="n">
-        <v>171.41</v>
+        <v>113.03</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:48:17</t>
+          <t>08:55:10</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.12</v>
+        <v>4.71</v>
       </c>
       <c r="F80" t="n">
-        <v>15.87</v>
+        <v>14.54</v>
       </c>
       <c r="G80" t="n">
-        <v>258.9</v>
+        <v>240.6</v>
       </c>
       <c r="H80" t="n">
-        <v>61.2</v>
+        <v>36.2</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>133.04</v>
+        <v>-194.97</v>
       </c>
       <c r="K80" t="n">
-        <v>95.68000000000001</v>
+        <v>13.54</v>
       </c>
       <c r="L80" t="n">
-        <v>163.87</v>
+        <v>195.44</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:49:56</t>
+          <t>08:56:24</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.67</v>
+        <v>4.92</v>
       </c>
       <c r="F81" t="n">
-        <v>13.44</v>
+        <v>15.87</v>
       </c>
       <c r="G81" t="n">
-        <v>260.8</v>
+        <v>262.4</v>
       </c>
       <c r="H81" t="n">
-        <v>36.9</v>
+        <v>68.5</v>
       </c>
       <c r="I81" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-114.31</v>
+        <v>205.15</v>
       </c>
       <c r="K81" t="n">
-        <v>-139.86</v>
+        <v>-47.49</v>
       </c>
       <c r="L81" t="n">
-        <v>180.63</v>
+        <v>210.57</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:51:16</t>
+          <t>08:57:40</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.55</v>
+        <v>4.57</v>
       </c>
       <c r="F82" t="n">
         <v>15.87</v>
       </c>
       <c r="G82" t="n">
-        <v>251.7</v>
+        <v>242.1</v>
       </c>
       <c r="H82" t="n">
-        <v>57.9</v>
+        <v>60.9</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-197.8</v>
+        <v>-20.13</v>
       </c>
       <c r="K82" t="n">
-        <v>8.779999999999999</v>
+        <v>145.25</v>
       </c>
       <c r="L82" t="n">
-        <v>198</v>
+        <v>146.64</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:56:01</t>
+          <t>09:02:43</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.83</v>
+        <v>5.09</v>
       </c>
       <c r="F83" t="n">
-        <v>13.44</v>
+        <v>15.87</v>
       </c>
       <c r="G83" t="n">
-        <v>259.3</v>
+        <v>251</v>
       </c>
       <c r="H83" t="n">
-        <v>59.6</v>
+        <v>67.5</v>
       </c>
       <c r="I83" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-148.89</v>
+        <v>-211.29</v>
       </c>
       <c r="K83" t="n">
-        <v>203.27</v>
+        <v>-21.06</v>
       </c>
       <c r="L83" t="n">
-        <v>251.96</v>
+        <v>212.34</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:57:43</t>
+          <t>09:05:08</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>5.24</v>
+        <v>5.09</v>
       </c>
       <c r="F84" t="n">
-        <v>15.87</v>
+        <v>15.11</v>
       </c>
       <c r="G84" t="n">
-        <v>262.6</v>
+        <v>274.2</v>
       </c>
       <c r="H84" t="n">
-        <v>50.4</v>
+        <v>50.1</v>
       </c>
       <c r="I84" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>149.45</v>
+        <v>453.02</v>
       </c>
       <c r="K84" t="n">
-        <v>259.53</v>
+        <v>-90.13</v>
       </c>
       <c r="L84" t="n">
-        <v>299.49</v>
+        <v>461.9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:00:05</t>
+          <t>09:07:40</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.82</v>
+        <v>5.28</v>
       </c>
       <c r="F85" t="n">
-        <v>15.87</v>
+        <v>15.69</v>
       </c>
       <c r="G85" t="n">
-        <v>235.4</v>
+        <v>261.9</v>
       </c>
       <c r="H85" t="n">
-        <v>65.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="I85" t="n">
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-240.39</v>
+        <v>-280.7</v>
       </c>
       <c r="K85" t="n">
-        <v>-85.26000000000001</v>
+        <v>-208.68</v>
       </c>
       <c r="L85" t="n">
-        <v>255.06</v>
+        <v>349.77</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:05:03</t>
+          <t>09:11:48</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.6</v>
+        <v>5.42</v>
       </c>
       <c r="F86" t="n">
-        <v>12.62</v>
+        <v>15.87</v>
       </c>
       <c r="G86" t="n">
-        <v>254.9</v>
+        <v>244.1</v>
       </c>
       <c r="H86" t="n">
-        <v>55.1</v>
+        <v>59.9</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-276.92</v>
+        <v>-166.8</v>
       </c>
       <c r="K86" t="n">
-        <v>40.16</v>
+        <v>-351.49</v>
       </c>
       <c r="L86" t="n">
-        <v>279.82</v>
+        <v>389.06</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:06:37</t>
+          <t>09:14:24</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.55</v>
+        <v>5.35</v>
       </c>
       <c r="F87" t="n">
-        <v>15.87</v>
+        <v>14.3</v>
       </c>
       <c r="G87" t="n">
-        <v>249.8</v>
+        <v>253.5</v>
       </c>
       <c r="H87" t="n">
-        <v>65.59999999999999</v>
+        <v>54.3</v>
       </c>
       <c r="I87" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-306.75</v>
+        <v>108.97</v>
       </c>
       <c r="K87" t="n">
-        <v>-291.05</v>
+        <v>-491.88</v>
       </c>
       <c r="L87" t="n">
-        <v>422.85</v>
+        <v>503.8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:08:15</t>
+          <t>09:16:39</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3739,22 +3739,22 @@
         <v>15.87</v>
       </c>
       <c r="G88" t="n">
-        <v>249.4</v>
+        <v>250.6</v>
       </c>
       <c r="H88" t="n">
-        <v>36.8</v>
+        <v>63.9</v>
       </c>
       <c r="I88" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-225.29</v>
+        <v>-322.53</v>
       </c>
       <c r="K88" t="n">
-        <v>239.75</v>
+        <v>-312.33</v>
       </c>
       <c r="L88" t="n">
-        <v>328.99</v>
+        <v>448.97</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-30.xlsx
+++ b/output/2024-04-30.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>-21.43</v>
+        <v>-25.15</v>
       </c>
       <c r="K14" t="n">
-        <v>60.03</v>
+        <v>70.47</v>
       </c>
       <c r="L14" t="n">
-        <v>63.74</v>
+        <v>74.81999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-81.73999999999999</v>
+        <v>-90.65000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>81.73999999999999</v>
+        <v>90.65000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-48.89</v>
+        <v>-53.27</v>
       </c>
       <c r="K16" t="n">
-        <v>86.37</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>99.23999999999999</v>
+        <v>108.13</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>74.3</v>
+        <v>91.16</v>
       </c>
       <c r="K17" t="n">
-        <v>-26.47</v>
+        <v>-32.48</v>
       </c>
       <c r="L17" t="n">
-        <v>78.88</v>
+        <v>96.78</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-27.27</v>
+        <v>-32.86</v>
       </c>
       <c r="K18" t="n">
-        <v>-77.44</v>
+        <v>-93.28</v>
       </c>
       <c r="L18" t="n">
-        <v>82.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>29.75</v>
+        <v>33.52</v>
       </c>
       <c r="K19" t="n">
-        <v>94.59</v>
+        <v>106.6</v>
       </c>
       <c r="L19" t="n">
-        <v>99.15000000000001</v>
+        <v>111.74</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>-107.4</v>
+        <v>-135.8</v>
       </c>
       <c r="K20" t="n">
-        <v>-58.92</v>
+        <v>-74.5</v>
       </c>
       <c r="L20" t="n">
-        <v>122.5</v>
+        <v>154.89</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>94.40000000000001</v>
+        <v>109.38</v>
       </c>
       <c r="K21" t="n">
-        <v>-165.96</v>
+        <v>-192.29</v>
       </c>
       <c r="L21" t="n">
-        <v>190.93</v>
+        <v>221.22</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-53.71</v>
+        <v>-71.23999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>5.14</v>
+        <v>6.82</v>
       </c>
       <c r="L22" t="n">
-        <v>53.95</v>
+        <v>71.56999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>-34.01</v>
+        <v>-43.75</v>
       </c>
       <c r="K23" t="n">
-        <v>-225.5</v>
+        <v>-290.09</v>
       </c>
       <c r="L23" t="n">
-        <v>228.05</v>
+        <v>293.37</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>112.11</v>
+        <v>138.96</v>
       </c>
       <c r="K24" t="n">
-        <v>287.07</v>
+        <v>355.83</v>
       </c>
       <c r="L24" t="n">
-        <v>308.18</v>
+        <v>382</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>20</v>
       </c>
       <c r="J25" t="n">
-        <v>140.67</v>
+        <v>172.77</v>
       </c>
       <c r="K25" t="n">
-        <v>-199.85</v>
+        <v>-245.46</v>
       </c>
       <c r="L25" t="n">
-        <v>244.4</v>
+        <v>300.17</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>14.9</v>
+        <v>20.71</v>
       </c>
       <c r="K26" t="n">
-        <v>208.7</v>
+        <v>289.94</v>
       </c>
       <c r="L26" t="n">
-        <v>209.23</v>
+        <v>290.67</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>18</v>
       </c>
       <c r="J27" t="n">
-        <v>252.2</v>
+        <v>330.75</v>
       </c>
       <c r="K27" t="n">
-        <v>186.98</v>
+        <v>245.22</v>
       </c>
       <c r="L27" t="n">
-        <v>313.95</v>
+        <v>411.74</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>16</v>
       </c>
       <c r="J28" t="n">
-        <v>-233.96</v>
+        <v>-303.41</v>
       </c>
       <c r="K28" t="n">
-        <v>-257.35</v>
+        <v>-333.74</v>
       </c>
       <c r="L28" t="n">
-        <v>347.8</v>
+        <v>451.05</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>53.64</v>
+        <v>61.91</v>
       </c>
       <c r="K29" t="n">
-        <v>-41.88</v>
+        <v>-48.33</v>
       </c>
       <c r="L29" t="n">
-        <v>68.05</v>
+        <v>78.54000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>37.47</v>
+        <v>42.59</v>
       </c>
       <c r="K30" t="n">
-        <v>59.77</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>70.54000000000001</v>
+        <v>80.18000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>41.73</v>
+        <v>51.07</v>
       </c>
       <c r="K31" t="n">
-        <v>-38.73</v>
+        <v>-47.4</v>
       </c>
       <c r="L31" t="n">
-        <v>56.94</v>
+        <v>69.68000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-81.59</v>
+        <v>-95.68000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>29.16</v>
+        <v>34.2</v>
       </c>
       <c r="L32" t="n">
-        <v>86.64</v>
+        <v>101.61</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>4.39</v>
+        <v>4.53</v>
       </c>
       <c r="K33" t="n">
-        <v>155.42</v>
+        <v>160.57</v>
       </c>
       <c r="L33" t="n">
-        <v>155.48</v>
+        <v>160.64</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>90.51000000000001</v>
+        <v>100.81</v>
       </c>
       <c r="K34" t="n">
-        <v>48.92</v>
+        <v>54.48</v>
       </c>
       <c r="L34" t="n">
-        <v>102.89</v>
+        <v>114.59</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>62.05</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>77.90000000000001</v>
+        <v>97.73</v>
       </c>
       <c r="L35" t="n">
-        <v>99.59</v>
+        <v>124.95</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>83.61</v>
+        <v>99.31</v>
       </c>
       <c r="K36" t="n">
-        <v>111.92</v>
+        <v>132.94</v>
       </c>
       <c r="L36" t="n">
-        <v>139.7</v>
+        <v>165.94</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>147.92</v>
+        <v>164.75</v>
       </c>
       <c r="K37" t="n">
-        <v>-122.34</v>
+        <v>-136.26</v>
       </c>
       <c r="L37" t="n">
-        <v>191.95</v>
+        <v>213.8</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>18</v>
       </c>
       <c r="J38" t="n">
-        <v>-139.97</v>
+        <v>-183.48</v>
       </c>
       <c r="K38" t="n">
-        <v>133.35</v>
+        <v>174.81</v>
       </c>
       <c r="L38" t="n">
-        <v>193.33</v>
+        <v>253.42</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>-103.25</v>
+        <v>-152</v>
       </c>
       <c r="K39" t="n">
-        <v>213.84</v>
+        <v>314.8</v>
       </c>
       <c r="L39" t="n">
-        <v>237.46</v>
+        <v>349.58</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>222.32</v>
+        <v>283.21</v>
       </c>
       <c r="K40" t="n">
-        <v>15.07</v>
+        <v>19.2</v>
       </c>
       <c r="L40" t="n">
-        <v>222.83</v>
+        <v>283.86</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-58.27</v>
+        <v>-79.48</v>
       </c>
       <c r="K41" t="n">
-        <v>259.35</v>
+        <v>353.72</v>
       </c>
       <c r="L41" t="n">
-        <v>265.81</v>
+        <v>362.54</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-234.5</v>
+        <v>-316.79</v>
       </c>
       <c r="K42" t="n">
-        <v>-237.75</v>
+        <v>-321.17</v>
       </c>
       <c r="L42" t="n">
-        <v>333.94</v>
+        <v>451.12</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>118.2</v>
+        <v>175.95</v>
       </c>
       <c r="K43" t="n">
-        <v>168.05</v>
+        <v>250.15</v>
       </c>
       <c r="L43" t="n">
-        <v>205.46</v>
+        <v>305.83</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>76.03</v>
+        <v>86.78</v>
       </c>
       <c r="K44" t="n">
-        <v>12.63</v>
+        <v>14.42</v>
       </c>
       <c r="L44" t="n">
-        <v>77.06999999999999</v>
+        <v>87.97</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>59.34</v>
+        <v>72.64</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.31</v>
+        <v>-6.49</v>
       </c>
       <c r="L45" t="n">
-        <v>59.58</v>
+        <v>72.93000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-102.5</v>
+        <v>-110.99</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.64</v>
+        <v>-3.94</v>
       </c>
       <c r="L46" t="n">
-        <v>102.56</v>
+        <v>111.06</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>113.46</v>
+        <v>123.57</v>
       </c>
       <c r="K47" t="n">
-        <v>-32.18</v>
+        <v>-35.05</v>
       </c>
       <c r="L47" t="n">
-        <v>117.93</v>
+        <v>128.44</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-86.23999999999999</v>
+        <v>-109.28</v>
       </c>
       <c r="K48" t="n">
-        <v>8.050000000000001</v>
+        <v>10.21</v>
       </c>
       <c r="L48" t="n">
-        <v>86.62</v>
+        <v>109.75</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>92.43000000000001</v>
+        <v>106.69</v>
       </c>
       <c r="K49" t="n">
-        <v>-54.38</v>
+        <v>-62.77</v>
       </c>
       <c r="L49" t="n">
-        <v>107.24</v>
+        <v>123.79</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-127.14</v>
+        <v>-156.24</v>
       </c>
       <c r="K50" t="n">
-        <v>-34.35</v>
+        <v>-42.21</v>
       </c>
       <c r="L50" t="n">
-        <v>131.7</v>
+        <v>161.84</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>45.51</v>
+        <v>56.87</v>
       </c>
       <c r="K51" t="n">
-        <v>161.97</v>
+        <v>202.41</v>
       </c>
       <c r="L51" t="n">
-        <v>168.24</v>
+        <v>210.25</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>16.71</v>
+        <v>20.17</v>
       </c>
       <c r="K52" t="n">
-        <v>133.16</v>
+        <v>160.77</v>
       </c>
       <c r="L52" t="n">
-        <v>134.21</v>
+        <v>162.03</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>163.86</v>
+        <v>207.61</v>
       </c>
       <c r="K53" t="n">
-        <v>-232.02</v>
+        <v>-293.97</v>
       </c>
       <c r="L53" t="n">
-        <v>284.05</v>
+        <v>359.89</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>-144.32</v>
+        <v>-210.21</v>
       </c>
       <c r="K54" t="n">
-        <v>-50.05</v>
+        <v>-72.90000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>152.75</v>
+        <v>222.49</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>25.57</v>
+        <v>34.35</v>
       </c>
       <c r="K55" t="n">
-        <v>-213.41</v>
+        <v>-286.68</v>
       </c>
       <c r="L55" t="n">
-        <v>214.93</v>
+        <v>288.73</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>218.4</v>
+        <v>333.02</v>
       </c>
       <c r="K56" t="n">
-        <v>-81.98</v>
+        <v>-125.01</v>
       </c>
       <c r="L56" t="n">
-        <v>233.28</v>
+        <v>355.71</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>272.04</v>
+        <v>361.08</v>
       </c>
       <c r="K57" t="n">
-        <v>21.23</v>
+        <v>28.18</v>
       </c>
       <c r="L57" t="n">
-        <v>272.86</v>
+        <v>362.17</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>-393.58</v>
+        <v>-502</v>
       </c>
       <c r="K58" t="n">
-        <v>225.47</v>
+        <v>287.57</v>
       </c>
       <c r="L58" t="n">
-        <v>453.58</v>
+        <v>578.53</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>36.4</v>
+        <v>42.6</v>
       </c>
       <c r="K59" t="n">
-        <v>63.69</v>
+        <v>74.52</v>
       </c>
       <c r="L59" t="n">
-        <v>73.34999999999999</v>
+        <v>85.84</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-52.2</v>
+        <v>-64.33</v>
       </c>
       <c r="K60" t="n">
-        <v>31.58</v>
+        <v>38.91</v>
       </c>
       <c r="L60" t="n">
-        <v>61.01</v>
+        <v>75.19</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.75</v>
+        <v>-0.84</v>
       </c>
       <c r="K61" t="n">
-        <v>84.70999999999999</v>
+        <v>94.98</v>
       </c>
       <c r="L61" t="n">
-        <v>84.72</v>
+        <v>94.98</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-17.88</v>
+        <v>-19.44</v>
       </c>
       <c r="K62" t="n">
-        <v>-135.72</v>
+        <v>-147.52</v>
       </c>
       <c r="L62" t="n">
-        <v>136.9</v>
+        <v>148.8</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-75.79000000000001</v>
+        <v>-89.7</v>
       </c>
       <c r="K63" t="n">
-        <v>-47.31</v>
+        <v>-55.99</v>
       </c>
       <c r="L63" t="n">
-        <v>89.34</v>
+        <v>105.74</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-87.66</v>
+        <v>-99.08</v>
       </c>
       <c r="K64" t="n">
-        <v>10.96</v>
+        <v>12.38</v>
       </c>
       <c r="L64" t="n">
-        <v>88.34</v>
+        <v>99.84999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.77</v>
+        <v>-5.81</v>
       </c>
       <c r="K65" t="n">
-        <v>165.83</v>
+        <v>201.78</v>
       </c>
       <c r="L65" t="n">
-        <v>165.9</v>
+        <v>201.87</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-34.55</v>
+        <v>-42.34</v>
       </c>
       <c r="K66" t="n">
-        <v>-173.74</v>
+        <v>-212.89</v>
       </c>
       <c r="L66" t="n">
-        <v>177.14</v>
+        <v>217.06</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>32.21</v>
+        <v>40.41</v>
       </c>
       <c r="K67" t="n">
-        <v>-175.01</v>
+        <v>-219.56</v>
       </c>
       <c r="L67" t="n">
-        <v>177.95</v>
+        <v>223.24</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>66.62</v>
+        <v>84.91</v>
       </c>
       <c r="K68" t="n">
-        <v>-186.87</v>
+        <v>-238.16</v>
       </c>
       <c r="L68" t="n">
-        <v>198.39</v>
+        <v>252.84</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>-84.34</v>
+        <v>-118.57</v>
       </c>
       <c r="K69" t="n">
-        <v>132.51</v>
+        <v>186.31</v>
       </c>
       <c r="L69" t="n">
-        <v>157.08</v>
+        <v>220.84</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-164.79</v>
+        <v>-202.65</v>
       </c>
       <c r="K70" t="n">
-        <v>173.23</v>
+        <v>213.03</v>
       </c>
       <c r="L70" t="n">
-        <v>239.09</v>
+        <v>294.02</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-288.6</v>
+        <v>-440.71</v>
       </c>
       <c r="K71" t="n">
-        <v>113.24</v>
+        <v>172.93</v>
       </c>
       <c r="L71" t="n">
-        <v>310.02</v>
+        <v>473.43</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>80.14</v>
+        <v>117.41</v>
       </c>
       <c r="K72" t="n">
-        <v>-261.75</v>
+        <v>-383.47</v>
       </c>
       <c r="L72" t="n">
-        <v>273.74</v>
+        <v>401.04</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>-26.21</v>
+        <v>-37.89</v>
       </c>
       <c r="K73" t="n">
-        <v>-238.81</v>
+        <v>-345.28</v>
       </c>
       <c r="L73" t="n">
-        <v>240.25</v>
+        <v>347.36</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>40.16</v>
+        <v>48.68</v>
       </c>
       <c r="K74" t="n">
-        <v>50.89</v>
+        <v>61.69</v>
       </c>
       <c r="L74" t="n">
-        <v>64.81999999999999</v>
+        <v>78.58</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>58.2</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>35.7</v>
+        <v>42.82</v>
       </c>
       <c r="L75" t="n">
-        <v>68.28</v>
+        <v>81.88</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>60.21</v>
+        <v>68.75</v>
       </c>
       <c r="K76" t="n">
-        <v>-47.65</v>
+        <v>-54.41</v>
       </c>
       <c r="L76" t="n">
-        <v>76.78</v>
+        <v>87.68000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>23.2</v>
+        <v>24.76</v>
       </c>
       <c r="K77" t="n">
-        <v>139.76</v>
+        <v>149.13</v>
       </c>
       <c r="L77" t="n">
-        <v>141.68</v>
+        <v>151.18</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-193.41</v>
+        <v>-193.33</v>
       </c>
       <c r="K78" t="n">
-        <v>28.4</v>
+        <v>28.39</v>
       </c>
       <c r="L78" t="n">
-        <v>195.49</v>
+        <v>195.4</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>32.14</v>
+        <v>38.65</v>
       </c>
       <c r="K79" t="n">
-        <v>97.59999999999999</v>
+        <v>117.38</v>
       </c>
       <c r="L79" t="n">
-        <v>102.76</v>
+        <v>123.58</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>99.13</v>
+        <v>115.2</v>
       </c>
       <c r="K80" t="n">
-        <v>-199.25</v>
+        <v>-231.55</v>
       </c>
       <c r="L80" t="n">
-        <v>222.55</v>
+        <v>258.63</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>80.23999999999999</v>
+        <v>101.69</v>
       </c>
       <c r="K81" t="n">
-        <v>-92.13</v>
+        <v>-116.74</v>
       </c>
       <c r="L81" t="n">
-        <v>122.17</v>
+        <v>154.82</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>41.07</v>
+        <v>55.86</v>
       </c>
       <c r="K82" t="n">
-        <v>-95.23</v>
+        <v>-129.51</v>
       </c>
       <c r="L82" t="n">
-        <v>103.71</v>
+        <v>141.04</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>-171.8</v>
+        <v>-238.19</v>
       </c>
       <c r="K83" t="n">
-        <v>77.04000000000001</v>
+        <v>106.81</v>
       </c>
       <c r="L83" t="n">
-        <v>188.28</v>
+        <v>261.04</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>13.05</v>
+        <v>17.99</v>
       </c>
       <c r="K84" t="n">
-        <v>177.75</v>
+        <v>245.13</v>
       </c>
       <c r="L84" t="n">
-        <v>178.23</v>
+        <v>245.79</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>16</v>
       </c>
       <c r="J85" t="n">
-        <v>194.09</v>
+        <v>253.71</v>
       </c>
       <c r="K85" t="n">
-        <v>84.97</v>
+        <v>111.07</v>
       </c>
       <c r="L85" t="n">
-        <v>211.87</v>
+        <v>276.95</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>399.45</v>
+        <v>514.73</v>
       </c>
       <c r="K86" t="n">
-        <v>35.83</v>
+        <v>46.17</v>
       </c>
       <c r="L86" t="n">
-        <v>401.05</v>
+        <v>516.79</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-314.48</v>
+        <v>-425.95</v>
       </c>
       <c r="K87" t="n">
-        <v>50.83</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="L87" t="n">
-        <v>318.57</v>
+        <v>431.48</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>32.58</v>
+        <v>41.82</v>
       </c>
       <c r="K88" t="n">
-        <v>532.15</v>
+        <v>683.13</v>
       </c>
       <c r="L88" t="n">
-        <v>533.15</v>
+        <v>684.41</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-04-30.xlsx
+++ b/output/2024-04-30.xlsx
@@ -640,13 +640,13 @@
         <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>-25.15</v>
+        <v>-31.46</v>
       </c>
       <c r="K14" t="n">
-        <v>70.47</v>
+        <v>88.16</v>
       </c>
       <c r="L14" t="n">
-        <v>74.81999999999999</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-90.65000000000001</v>
+        <v>-126.66</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="L15" t="n">
-        <v>90.65000000000001</v>
+        <v>126.66</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-53.27</v>
+        <v>-69.55</v>
       </c>
       <c r="K16" t="n">
-        <v>94.09999999999999</v>
+        <v>122.85</v>
       </c>
       <c r="L16" t="n">
-        <v>108.13</v>
+        <v>141.17</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>91.16</v>
+        <v>115.6</v>
       </c>
       <c r="K17" t="n">
-        <v>-32.48</v>
+        <v>-41.19</v>
       </c>
       <c r="L17" t="n">
-        <v>96.78</v>
+        <v>122.72</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-32.86</v>
+        <v>-38.21</v>
       </c>
       <c r="K18" t="n">
-        <v>-93.28</v>
+        <v>-108.49</v>
       </c>
       <c r="L18" t="n">
-        <v>98.90000000000001</v>
+        <v>115.02</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>33.52</v>
+        <v>41.48</v>
       </c>
       <c r="K19" t="n">
-        <v>106.6</v>
+        <v>131.88</v>
       </c>
       <c r="L19" t="n">
-        <v>111.74</v>
+        <v>138.25</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>61.91</v>
+        <v>69.09</v>
       </c>
       <c r="K29" t="n">
-        <v>-48.33</v>
+        <v>-53.94</v>
       </c>
       <c r="L29" t="n">
-        <v>78.54000000000001</v>
+        <v>87.65000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>42.59</v>
+        <v>53.07</v>
       </c>
       <c r="K30" t="n">
-        <v>67.93000000000001</v>
+        <v>84.64</v>
       </c>
       <c r="L30" t="n">
-        <v>80.18000000000001</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>51.07</v>
+        <v>55.43</v>
       </c>
       <c r="K31" t="n">
-        <v>-47.4</v>
+        <v>-51.44</v>
       </c>
       <c r="L31" t="n">
-        <v>69.68000000000001</v>
+        <v>75.62</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>-95.68000000000001</v>
+        <v>-123.4</v>
       </c>
       <c r="K32" t="n">
-        <v>34.2</v>
+        <v>44.1</v>
       </c>
       <c r="L32" t="n">
-        <v>101.61</v>
+        <v>131.05</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>4.53</v>
+        <v>5.25</v>
       </c>
       <c r="K33" t="n">
-        <v>160.57</v>
+        <v>185.89</v>
       </c>
       <c r="L33" t="n">
-        <v>160.64</v>
+        <v>185.96</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>100.81</v>
+        <v>132.01</v>
       </c>
       <c r="K34" t="n">
-        <v>54.48</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>114.59</v>
+        <v>150.06</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>86.78</v>
+        <v>135.04</v>
       </c>
       <c r="K44" t="n">
-        <v>14.42</v>
+        <v>22.44</v>
       </c>
       <c r="L44" t="n">
-        <v>87.97</v>
+        <v>136.9</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>72.64</v>
+        <v>99.7</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.49</v>
+        <v>-8.91</v>
       </c>
       <c r="L45" t="n">
-        <v>72.93000000000001</v>
+        <v>100.1</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>16</v>
       </c>
       <c r="J46" t="n">
-        <v>-110.99</v>
+        <v>-142.58</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.94</v>
+        <v>-5.06</v>
       </c>
       <c r="L46" t="n">
-        <v>111.06</v>
+        <v>142.67</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>123.57</v>
+        <v>150.53</v>
       </c>
       <c r="K47" t="n">
-        <v>-35.05</v>
+        <v>-42.7</v>
       </c>
       <c r="L47" t="n">
-        <v>128.44</v>
+        <v>156.47</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>-109.28</v>
+        <v>-154.98</v>
       </c>
       <c r="K48" t="n">
-        <v>10.21</v>
+        <v>14.47</v>
       </c>
       <c r="L48" t="n">
-        <v>109.75</v>
+        <v>155.65</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>16</v>
       </c>
       <c r="J49" t="n">
-        <v>106.69</v>
+        <v>142.51</v>
       </c>
       <c r="K49" t="n">
-        <v>-62.77</v>
+        <v>-83.84</v>
       </c>
       <c r="L49" t="n">
-        <v>123.79</v>
+        <v>165.34</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>42.6</v>
+        <v>62.98</v>
       </c>
       <c r="K59" t="n">
-        <v>74.52</v>
+        <v>110.18</v>
       </c>
       <c r="L59" t="n">
-        <v>85.84</v>
+        <v>126.91</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>-64.33</v>
+        <v>-102.19</v>
       </c>
       <c r="K60" t="n">
-        <v>38.91</v>
+        <v>61.81</v>
       </c>
       <c r="L60" t="n">
-        <v>75.19</v>
+        <v>119.43</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.84</v>
+        <v>-1.07</v>
       </c>
       <c r="K61" t="n">
-        <v>94.98</v>
+        <v>121.27</v>
       </c>
       <c r="L61" t="n">
-        <v>94.98</v>
+        <v>121.27</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-19.44</v>
+        <v>-26.51</v>
       </c>
       <c r="K62" t="n">
-        <v>-147.52</v>
+        <v>-201.26</v>
       </c>
       <c r="L62" t="n">
-        <v>148.8</v>
+        <v>203</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-89.7</v>
+        <v>-114.45</v>
       </c>
       <c r="K63" t="n">
-        <v>-55.99</v>
+        <v>-71.44</v>
       </c>
       <c r="L63" t="n">
-        <v>105.74</v>
+        <v>134.91</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-99.08</v>
+        <v>-110.23</v>
       </c>
       <c r="K64" t="n">
-        <v>12.38</v>
+        <v>13.78</v>
       </c>
       <c r="L64" t="n">
-        <v>99.84999999999999</v>
+        <v>111.09</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>16</v>
       </c>
       <c r="J74" t="n">
-        <v>48.68</v>
+        <v>75.19</v>
       </c>
       <c r="K74" t="n">
-        <v>61.69</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>78.58</v>
+        <v>121.38</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>69.79000000000001</v>
+        <v>103.78</v>
       </c>
       <c r="K75" t="n">
-        <v>42.82</v>
+        <v>63.67</v>
       </c>
       <c r="L75" t="n">
-        <v>81.88</v>
+        <v>121.76</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>18</v>
       </c>
       <c r="J76" t="n">
-        <v>68.75</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>-54.41</v>
+        <v>-78.29000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>87.68000000000001</v>
+        <v>126.16</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>24.76</v>
+        <v>31.3</v>
       </c>
       <c r="K77" t="n">
-        <v>149.13</v>
+        <v>188.54</v>
       </c>
       <c r="L77" t="n">
-        <v>151.18</v>
+        <v>191.12</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>20</v>
       </c>
       <c r="J78" t="n">
-        <v>-193.33</v>
+        <v>-259.8</v>
       </c>
       <c r="K78" t="n">
-        <v>28.39</v>
+        <v>38.15</v>
       </c>
       <c r="L78" t="n">
-        <v>195.4</v>
+        <v>262.58</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>18</v>
       </c>
       <c r="J79" t="n">
-        <v>38.65</v>
+        <v>58.2</v>
       </c>
       <c r="K79" t="n">
-        <v>117.38</v>
+        <v>176.75</v>
       </c>
       <c r="L79" t="n">
-        <v>123.58</v>
+        <v>186.08</v>
       </c>
     </row>
     <row r="80">
